--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942AAB01-F3CD-42CD-BD38-7139A05BD794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC2140A-26BA-4894-A1DE-2EE73181FD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>5.5682178910641304E-2</v>
+        <v>5.7029099355293308E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0900000000000001</v>
+        <v>1.0946661899999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>0.47913596335358838</v>
+        <v>0.48118710045527707</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>0.27020597566722598</v>
+        <v>0.27115120013805027</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>0.33356534172635238</v>
+        <v>0.33475011405945776</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>0.40856596580118759</v>
+        <v>0.41003613963632124</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>0.45892308270659687</v>
+        <v>0.46058574017626652</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.9160985615358244E-2</v>
+        <v>9.9585484697439441E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.30654971472191445</v>
+        <v>-0.30786202592681183</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.24706940234497918</v>
+        <v>0.24812708378950032</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.4682579005399395E-4</v>
+        <v>3.4831051944233529E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-5.9133486586881272E-2</v>
+        <v>-5.9386631617869189E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.57857707915918921</v>
+        <v>0.58105391455460365</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.5973806250734216</v>
+        <v>0.59993795672379879</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.80255581782783703</v>
+        <v>0.80181888533152224</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.6589902323256646E-2</v>
+        <v>-4.6786896600302622E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>-2.2273894563101741E-2</v>
+        <v>-2.2480608044182077E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.2277003155832433</v>
+        <v>0.22737563899691779</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-6.9490293479996024E-2</v>
+        <v>-6.9678403917928067E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.47913596335358838</v>
+        <v>0.48118710045527707</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>0.22079998311225277</v>
+        <v>0.22174520758307703</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>0.27020597566722598</v>
+        <v>0.27115120013805027</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>0.27675723515008727</v>
+        <v>0.27794200748319264</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>0.33356534172635238</v>
+        <v>0.33475011405945776</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>0.34342568140084406</v>
+        <v>0.34489585523597771</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>0.40856596580118759</v>
+        <v>0.41003613963632124</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>0.38838895157292541</v>
+        <v>0.39005160904259506</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>0.45892308270659687</v>
+        <v>0.46058574017626652</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10176,11 +10176,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8648259617667573</v>
+        <v>1.8728091106241298</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.57857707915918921</v>
+        <v>0.58105391455460365</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10586,11 +10586,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>1589066.31</v>
+        <v>1595868.9570872099</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.30654971472191445</v>
+        <v>0.30786202592681189</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1280737.3311516403</v>
+        <v>1286220.0501674626</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.24706940234497912</v>
+        <v>0.24812708378950032</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10620,11 +10620,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>1797.846</v>
+        <v>1805.5424137859995</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>3.46825790053994E-4</v>
+        <v>3.4831051944233529E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10637,11 +10637,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2871601.4871516405</v>
+        <v>2883894.5496684583</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>0.55396594285694756</v>
+        <v>0.5563374202357545</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15365,50 +15365,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>4.7597273095371963E-2</v>
+        <v>4.7801032654770939E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.8874002144165663E-2</v>
+        <v>3.9040418180922618E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.7555344906984714E-2</v>
+        <v>3.7716115893087022E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.3878341926249539E-2</v>
+        <v>-5.4108990165068649E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3837693239880851E-2</v>
+        <v>1.3896931135127638E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.0142130850289608E-2</v>
+        <v>4.0313975629695395E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.14791402911763751</v>
+        <v>0.14854723550619567</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>8.5390763647627391E-2</v>
+        <v>8.5756313672787854E-2</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>5.876503984515561E-2</v>
+        <v>5.9016607589444652E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>8.9289452245536388E-2</v>
+        <v>8.9671692198906638E-2</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1353950139296388E-2</v>
+        <v>1.1402555358195912E-2</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15422,50 +15422,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.9160985615358244E-2</v>
+        <v>9.9585484697439441E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.0987504467011806E-2</v>
+        <v>8.1334204543588792E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.8240301889551486E-2</v>
+        <v>7.8575241443931299E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.11224654567968655</v>
+        <v>-0.11272706284389303</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.8828527583085108E-2</v>
+        <v>2.8951939864849247E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>8.3629439271436692E-2</v>
+        <v>8.3987449228532074E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.30815422732841152</v>
+        <v>0.30947340730457434</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.17789742426589039</v>
+        <v>0.17865898681830802</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12242716634407419</v>
+        <v>0.12295126581134302</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.1860196921782008</v>
+        <v>0.18681602541438883</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>2.3654062790200811E-2</v>
+        <v>2.375532366290815E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-5.9133486586881272E-2</v>
+        <v>-5.9386631617869189E-2</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0900000000000001</v>
+        <v>1.0946661899999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>3096650.8202822809</v>
+        <v>3109907.2983475034</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.5973806250734216</v>
+        <v>0.59993795672379879</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16599,7 +16599,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.60023254495544254</v>
+        <v>0.6028020854131908</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18790,23 +18790,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.5973806250734216</v>
+        <v>0.59993795672379879</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.5973806250734216</v>
+        <v>0.59993795672379879</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.5973806250734216</v>
+        <v>0.59993795672379879</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.5973806250734216</v>
+        <v>0.59993795672379879</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.5973806250734216</v>
+        <v>0.59993795672379879</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18821,23 +18821,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.62866179216682161</v>
+        <v>0.63135303562369394</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.48007624847318064</v>
+        <v>0.48213141084920175</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.59738062507342315</v>
+        <v>0.59993795672380046</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.61302120862012244</v>
+        <v>0.6156454961737472</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.36277187187293825</v>
+        <v>0.36432486497460309</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18852,23 +18852,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.65899504510587414</v>
+        <v>0.66181614243571119</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.38710774487392063</v>
+        <v>0.38876491761525378</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.59738062507342315</v>
+        <v>0.59993795672380046</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.62789616919600355</v>
+        <v>0.63058413509117839</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.20964727770945155</v>
+        <v>0.21054475847163046</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18883,23 +18883,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.68840910856192539</v>
+        <v>0.69135612479887987</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.31342641335003174</v>
+        <v>0.31476816307086636</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.59738062507342315</v>
+        <v>0.59993795672380046</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.6420429848485909</v>
+        <v>0.64479151196370144</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.10970581764936689</v>
+        <v>0.11017545818996989</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18914,23 +18914,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.71693183676173233</v>
+        <v>0.72000095618134619</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.255030952468628</v>
+        <v>0.25612271657881108</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.59738062507342304</v>
+        <v>0.59993795672380035</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.65549729903566611</v>
+        <v>0.65830342283547083</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>4.4475960267493307E-2</v>
+        <v>4.4666357773035112E-2</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18945,23 +18945,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.74459023986457584</v>
+        <v>0.74777776237040483</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.20875016762089532</v>
+        <v>0.20964380793708881</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.59738062507342315</v>
+        <v>0.59993795672380046</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.66829301043036748</v>
+        <v>0.67115391149673442</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>1.9016943772262385E-3</v>
+        <v>1.9098353563877697E-3</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18976,23 +18976,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.77141050954006041</v>
+        <v>0.77471284715979483</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.1720707577182635</v>
+        <v>0.17280737684574732</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.59738062507342304</v>
+        <v>0.59993795672380035</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.68046235833022306</v>
+        <v>0.68337535525849535</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>-2.5885705271432902E-2</v>
+        <v>-2.5996519600864555E-2</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19008,23 +19008,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.79741804377083303</v>
+        <v>0.80083171725859714</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.14300082912410306</v>
+        <v>0.14361300255424117</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.59738062507342315</v>
+        <v>0.59993795672380046</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.69203600388533071</v>
+        <v>0.69499854652842208</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>-4.4022003410417877E-2</v>
+        <v>-4.4210457568301963E-2</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19039,23 +19039,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.82263747090370376</v>
+        <v>0.82615910644531476</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.11996172487698285</v>
+        <v>0.12047527001551836</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.59738062507342315</v>
+        <v>0.59993795672380046</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.70304310735032782</v>
+        <v>0.70605277039352676</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>-5.5859214316981508E-2</v>
+        <v>-5.6098342488773933E-2</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19071,23 +19071,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.8470926729719418</v>
+        <v>0.85071899899001036</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.10170229493754021</v>
+        <v>0.10213767313168202</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.59738062507342304</v>
+        <v>0.59993795672380035</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.71351140155480064</v>
+        <v>0.716565878405095</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>-6.3585132857396004E-2</v>
+        <v>-6.3857334977660066E-2</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19103,23 +19103,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.87080680831083923</v>
+        <v>0.87453465236668493</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>8.723095186199134E-2</v>
+        <v>8.7604379564072882E-2</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.59738062507342315</v>
+        <v>0.59993795672380046</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.72346726177723664</v>
+        <v>0.72656435875176162</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>-6.8627690412911294E-2</v>
+        <v>-6.8921479259450566E-2</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19135,23 +19135,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>0.97902407504950428</v>
+        <v>0.9832151872960686</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>4.9233621710730889E-2</v>
+        <v>4.9444386328428493E-2</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.59738062507342304</v>
+        <v>0.59993795672380035</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.76639626488951706</v>
+        <v>0.76967713698792506</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>-7.6981292635343451E-2</v>
+        <v>-7.7310842486611436E-2</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19167,23 +19167,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.0718088573055153</v>
+        <v>1.0763971726925523</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>3.7352397086236909E-2</v>
+        <v>3.751229927133766E-2</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.59738062507342304</v>
+        <v>0.59993795672380035</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.79979770239391168</v>
+        <v>0.80322156298192382</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>-7.7970705350316999E-2</v>
+        <v>-7.8304490786645975E-2</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19199,23 +19199,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.1513619275108948</v>
+        <v>1.156290802293034</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>3.3637307157135705E-2</v>
+        <v>3.3781305383083916E-2</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.59738062507342304</v>
+        <v>0.59993795672380035</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.82578610059738233</v>
+        <v>0.82932121513384682</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>-7.808789282160003E-2</v>
+        <v>-7.8422179926742427E-2</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19231,23 +19231,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.2195702136675621</v>
+        <v>1.2247910818650973</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>3.2475651383634382E-2</v>
+        <v>3.2614676667790159E-2</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.59738062507342304</v>
+        <v>0.59993795672380035</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.84600669263307771</v>
+        <v>0.84962836966894684</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>-7.8101772674989717E-2</v>
+        <v>-7.8436119198511081E-2</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.10970581764936689</v>
+        <v>0.11017545818996989</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19322,7 +19322,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.6420429848485909</v>
+        <v>0.64479151196370144</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.59738062507342315</v>
+        <v>0.59993795672380046</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19378,7 +19378,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.31342641335003174</v>
+        <v>0.31476816307086636</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.68840910856192539</v>
+        <v>0.69135612479887987</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>0.6420429848485909</v>
+        <v>0.64479151196370144</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>0.59738062507342315</v>
+        <v>0.59993795672380046</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19813,7 +19813,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>0.31342641335003174</v>
+        <v>0.31476816307086636</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.53532454409760888</v>
+        <v>0.53761621935854709</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>0.10970581764936689</v>
+        <v>0.11017545818996989</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19899,7 +19899,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>0.68840910856192539</v>
+        <v>0.69135612479887987</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>5.5682178910641304E-2</v>
+        <v>5.7029099355293308E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>0.5973806250734216</v>
+        <v>0.59993795672379879</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19975,7 +19975,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-2.2273894563100857E-2</v>
+        <v>-2.2480608044181147E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.47913596335358838</v>
+        <v>0.48118710045527707</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.60023254495544254</v>
+        <v>0.6028020854131908</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>1.1561769210134136</v>
+        <v>1.1561769210134138</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20228,11 +20228,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.22079998311225277</v>
+        <v>0.22174520758307703</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>0.27020597566722598</v>
+        <v>0.27115120013805027</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.43605574130568481</v>
+        <v>0.43649528451303143</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20253,11 +20253,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.27675723515008727</v>
+        <v>0.27794200748319264</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>0.33356534172635238</v>
+        <v>0.33475011405945776</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20265,7 +20265,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.30381902583215015</v>
+        <v>0.30432442236557755</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20299,11 +20299,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.34342568140084406</v>
+        <v>0.34489585523597771</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>0.40856596580118759</v>
+        <v>0.41003613963632124</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20311,7 +20311,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.14728595419651724</v>
+        <v>0.14786547842125464</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20324,11 +20324,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.38838895157292541</v>
+        <v>0.39005160904259506</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>0.45892308270659687</v>
+        <v>0.46058574017626652</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20336,7 +20336,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>4.2186106226543063E-2</v>
+        <v>4.2813617113838909E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20472,7 +20472,7 @@
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>5.5682178910641304E-2</v>
+        <v>5.7029099355293308E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20480,13 +20480,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0900000000000001</v>
+        <v>1.0946661899999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20550,7 +20550,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>0.47913596335358838</v>
+        <v>0.48118710045527707</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20602,7 +20602,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>0.27020597566722598</v>
+        <v>0.27115120013805027</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20618,7 +20618,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>0.33356534172635238</v>
+        <v>0.33475011405945776</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20634,7 +20634,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>0.40856596580118759</v>
+        <v>0.41003613963632124</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>0.45892308270659687</v>
+        <v>0.46058574017626652</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20671,22 +20671,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20876,10 +20876,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20895,22 +20895,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.9160985615358244E-2</v>
+        <v>9.9585484697439441E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -21045,22 +21045,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21068,13 +21068,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21095,7 +21095,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.30654971472191445</v>
+        <v>-0.30786202592681183</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.24706940234497918</v>
+        <v>0.24812708378950032</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21188,7 +21188,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.4682579005399395E-4</v>
+        <v>3.4831051944233529E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21201,7 +21201,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-5.9133486586881272E-2</v>
+        <v>-5.9386631617869189E-2</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21223,33 +21223,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21312,23 +21312,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21346,7 +21346,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>0.57857707915918921</v>
+        <v>0.58105391455460365</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21360,7 +21360,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>0.5973806250734216</v>
+        <v>0.59993795672379879</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21372,13 +21372,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21534,7 +21534,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>0.47913596335358838</v>
+        <v>0.48118710045527707</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21542,13 +21542,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21561,22 +21561,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21641,11 +21641,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>0.22079998311225277</v>
+        <v>0.22174520758307703</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>0.27020597566722598</v>
+        <v>0.27115120013805027</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21662,11 +21662,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>0.27675723515008727</v>
+        <v>0.27794200748319264</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>0.33356534172635238</v>
+        <v>0.33475011405945776</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21702,11 +21702,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>0.34342568140084406</v>
+        <v>0.34489585523597771</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>0.40856596580118759</v>
+        <v>0.41003613963632124</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21723,11 +21723,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>0.38838895157292541</v>
+        <v>0.39005160904259506</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>0.45892308270659687</v>
+        <v>0.46058574017626652</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21745,13 +21745,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21759,13 +21759,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21802,22 +21802,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21841,15 +21841,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21864,12 +21861,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC2140A-26BA-4894-A1DE-2EE73181FD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6B0A36-998A-419B-B12F-CB9562FC6464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>5.7029099355293308E-2</v>
+        <v>0.15148912164034103</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>0.48118710045527707</v>
+        <v>0.63896931637895027</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>0.27115120013805027</v>
+        <v>0.34386189872038819</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>0.33475011405945776</v>
+        <v>0.42588785610923291</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>0.41003613963632124</v>
+        <v>0.5231281827325196</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>0.46058574017626652</v>
+        <v>0.58848444556779833</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="C34" s="289">
         <f>Normalized_FCF!C8</f>
-        <v>379710.97209007666</v>
+        <v>410704.412090078</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>15191.436227966604</v>
+        <v>15165.608361299935</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-57701.513772033395</v>
+        <v>-57727.341638700062</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-80502.364579510817</v>
+        <v>-88244.267612844487</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>184873.15815414075</v>
+        <v>184825.24568659026</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>226358.43266235912</v>
+        <v>249584.14176236014</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.9585484697439441E-2</v>
+        <v>0.10980354227524289</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.68701414752223544</v>
+        <v>0.62308223812580676</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5917,11 +5917,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>3.586906730443893E-2</v>
+        <v>3.931859133292645E-2</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>4.2505173365498042E-2</v>
+        <v>4.2499836331200143E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5931,11 +5931,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>1.7449376932917909E-2</v>
+        <v>1.9127481481925439E-2</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>2.0677671525677264E-2</v>
+        <v>2.0675075196021478E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C81" s="342">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>3.8393912927387319</v>
+        <v>3.5496550732945478</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>1174988.3772033397</v>
+        <v>1177571.1638700066</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.24812708378950032</v>
+        <v>0.2486725013749711</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-5.9386631617869189E-2</v>
+        <v>-5.8841214032398434E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.59993795672379879</v>
+        <v>0.6681339624105892</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6341,11 +6341,11 @@
       </c>
       <c r="C118" s="206">
         <f>DCF!C90</f>
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>0.11 HKD</v>
+        <v>0.45 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.80181888533152224</v>
+        <v>0.17672737131882851</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>0.64 HKD</v>
+        <v>0.72 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.6786896600302622E-2</v>
+        <v>1.5028267395837255E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>0.6 HKD</v>
+        <v>0.67 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>-2.2480608044182077E-2</v>
+        <v>2.6235909176885886E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6407,11 +6407,11 @@
       </c>
       <c r="C121" s="198">
         <f>DCF!C93</f>
-        <v>-0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>0.31 HKD</v>
+        <v>0.62 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.22737563899691779</v>
+        <v>5.2494022835921784E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>0.69 HKD</v>
+        <v>0.77 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-6.9678403917928067E-2</v>
+        <v>-2.1853207340008177E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.48118710045527707</v>
+        <v>0.63896931637895027</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>0.22174520758307703</v>
+        <v>0.29445590616541495</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>0.27115120013805027</v>
+        <v>0.34386189872038819</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>0.27794200748319264</v>
+        <v>0.36907974953296779</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>0.33475011405945776</v>
+        <v>0.42588785610923291</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>0.34489585523597771</v>
+        <v>0.45798789833217612</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>0.41003613963632124</v>
+        <v>0.5231281827325196</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>0.39005160904259506</v>
+        <v>0.51795031443412687</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>0.46058574017626652</v>
+        <v>0.58848444556779833</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="C50" s="92">
         <f>G31/Normalized_FCF!C8</f>
-        <v>3.8393912927387319</v>
+        <v>3.5496550732945478</v>
       </c>
       <c r="D50" s="92">
         <f>G31/Normalized_FCF!G8</f>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="C54" s="89">
         <f>Normalized_FCF!C8/G35</f>
-        <v>3.8377712915114597E-2</v>
+        <v>4.1510246420861471E-2</v>
       </c>
       <c r="D54" s="89">
         <f>Normalized_FCF!G8/G35</f>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>1174988.3772033397</v>
+        <v>1177571.1638700066</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-1519143.6227966603</v>
+        <v>-1516560.8361299934</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10458,7 +10458,7 @@
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>1.773454438126298</v>
+        <v>1.7764747287520419</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10471,7 +10471,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1519143.6227966603</v>
+        <v>1516560.8361299934</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1286220.0501674626</v>
+        <v>1289047.3394074456</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.24812708378950032</v>
+        <v>0.2486725013749711</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10637,11 +10637,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2883894.5496684583</v>
+        <v>2886721.8389084414</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>0.5563374202357545</v>
+        <v>0.55688283782122527</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="C5" s="270">
         <f>C26</f>
-        <v>-17322566.027909923</v>
+        <v>-17291572.587909922</v>
       </c>
       <c r="E5" s="238"/>
       <c r="G5" s="274">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="C6" s="271">
         <f>C4+C5</f>
-        <v>1131356.9720900767</v>
+        <v>1162350.412090078</v>
       </c>
       <c r="E6" s="238"/>
       <c r="G6" s="271">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C8" s="272">
         <f>C6+C7</f>
-        <v>379710.97209007666</v>
+        <v>410704.412090078</v>
       </c>
       <c r="D8" s="56"/>
       <c r="E8" s="244"/>
@@ -11122,24 +11122,24 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-57701.513772033395</v>
+        <v>-57727.341638700062</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>-39614.841845859264</v>
+        <v>-39662.754313409729</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>-71124.982312857581</v>
+        <v>-71161.042728778804</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>-154221.32239070552</v>
+        <v>-154242.63844408872</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>-187099.05870962987</v>
+        <v>-187125.97723730904</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
@@ -11177,24 +11177,24 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>322009.45831804327</v>
+        <v>352977.07045137795</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>381584.15815414075</v>
+        <v>381536.24568659026</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>344886.01768714242</v>
+        <v>344849.95727122121</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>-82530.322390705522</v>
+        <v>-82551.63844408872</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>283340.94129037013</v>
+        <v>283314.02276269096</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-80502.364579510817</v>
+        <v>-88244.267612844487</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11344,26 +11344,26 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>226358.43266235912</v>
+        <v>249584.14176236014</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>184873.15815414075</v>
+        <v>184825.24568659026</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>178602.01768714242</v>
+        <v>178565.95727122121</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>-256229.32239070552</v>
+        <v>-256250.63844408872</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>65807.94129037013</v>
+        <v>65781.022762690962</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
@@ -11562,26 +11562,26 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>226358.43266235912</v>
+        <v>249584.14176236014</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>184873.15815414075</v>
+        <v>184825.24568659026</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>178602.01768714242</v>
+        <v>178565.95727122121</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>-256229.32239070552</v>
+        <v>-256250.63844408872</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>65807.94129037013</v>
+        <v>65781.022762690962</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C24" s="270">
         <f>-C4*C30</f>
-        <v>-5167098.4400000004</v>
+        <v>-5136105</v>
       </c>
       <c r="D24" s="26"/>
       <c r="E24" s="235"/>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="C26" s="271">
         <f>SUM(C23:C25)</f>
-        <v>-17322566.027909923</v>
+        <v>-17291572.587909922</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="243"/>
@@ -11978,7 +11978,8 @@
         <v>Selling Expenses</v>
       </c>
       <c r="C30" s="60">
-        <v>0.28000000000000003</v>
+        <f>G30</f>
+        <v>0.2783204958642127</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="236"/>
@@ -12092,7 +12093,7 @@
       </c>
       <c r="C32" s="68">
         <f>ABS(C26/$C$4)</f>
-        <v>0.93869287456710004</v>
+        <v>0.93701337043131272</v>
       </c>
       <c r="E32" s="238"/>
       <c r="G32" s="29">
@@ -12300,19 +12301,19 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>0.49893580729599801</v>
+        <v>0.49899846253766145</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>0.4450774810454794</v>
+        <v>0.44512402209542085</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.9704878799590713</v>
+        <v>-1.969979070859315</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>0.70009296608044336</v>
+        <v>0.70015948404415607</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
@@ -12438,24 +12439,24 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>15191.436227966604</v>
+        <v>15165.608361299935</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>28181.158154140736</v>
+        <v>28133.245686590271</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>21210.017687142419</v>
+        <v>21173.957271221196</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>12537.677609294475</v>
+        <v>12516.361555911293</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>15832.941290370118</v>
+        <v>15806.022762690947</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
@@ -12550,24 +12551,24 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-57701.513772033395</v>
+        <v>-57727.341638700062</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>-39614.841845859264</v>
+        <v>-39662.754313409729</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>-71124.982312857581</v>
+        <v>-71161.042728778804</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>-154221.32239070552</v>
+        <v>-154242.63844408872</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>-187099.05870962987</v>
+        <v>-187125.97723730904</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
@@ -12667,7 +12668,7 @@
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
-        <v>5.2091590762903222</v>
+        <v>5.6343502641898571</v>
       </c>
       <c r="E53" s="238"/>
       <c r="G53" s="40">
@@ -13230,7 +13231,7 @@
       </c>
       <c r="C71" s="74">
         <f t="shared" ref="C71:C76" si="22">ABS(C5/C$4)</f>
-        <v>0.93869287456710004</v>
+        <v>0.93701337043131272</v>
       </c>
       <c r="D71" s="26"/>
       <c r="E71" s="235"/>
@@ -13287,7 +13288,7 @@
       </c>
       <c r="C72" s="75">
         <f t="shared" si="22"/>
-        <v>6.1307125432899914E-2</v>
+        <v>6.2986629568687266E-2</v>
       </c>
       <c r="D72" s="26"/>
       <c r="E72" s="235"/>
@@ -13401,7 +13402,7 @@
       </c>
       <c r="C74" s="75">
         <f t="shared" si="22"/>
-        <v>2.0576165408844323E-2</v>
+        <v>2.2255669544631675E-2</v>
       </c>
       <c r="D74" s="26"/>
       <c r="E74" s="235"/>
@@ -13515,26 +13516,26 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>3.1267884759264139E-3</v>
+        <v>3.1281880627062365E-3</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>2.1466894516607264E-3</v>
+        <v>2.149285781316511E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.5448176105714276E-3</v>
+        <v>3.5466148355863996E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>8.2745545994773548E-3</v>
+        <v>8.2756982859976767E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>8.0127270115110134E-3</v>
+        <v>8.0138798276466611E-3</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
@@ -13572,26 +13573,26 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>1.7449376932917909E-2</v>
+        <v>1.9127481481925439E-2</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>2.0677671525677264E-2</v>
+        <v>2.0675075196021478E-2</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>1.7188869359004735E-2</v>
+        <v>1.7187072133989765E-2</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>-4.4280625282429676E-3</v>
+        <v>-4.4292062147632903E-3</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>1.2134393563506754E-2</v>
+        <v>1.2133240747371106E-2</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
@@ -13629,7 +13630,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>4.3623442332294772E-3</v>
+        <v>4.7818703704813597E-3</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13744,26 +13745,26 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>1.2266141603731582E-2</v>
+        <v>1.352472001548723E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>1.0018095239377597E-2</v>
+        <v>1.0015498909721811E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>8.9013952199819626E-3</v>
+        <v>8.8995979949669912E-3</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>1.3747667866170208E-2</v>
+        <v>1.374881155269053E-2</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>2.8182988860870192E-3</v>
+        <v>2.8171460699513715E-3</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
@@ -13967,26 +13968,26 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>1.2266141603731582E-2</v>
+        <v>1.352472001548723E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>1.0018095239377597E-2</v>
+        <v>1.0015498909721811E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>8.9013952199819626E-3</v>
+        <v>8.8995979949669912E-3</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>1.3747667866170208E-2</v>
+        <v>1.374881155269053E-2</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>2.8182988860870192E-3</v>
+        <v>2.8171460699513715E-3</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
@@ -14147,12 +14148,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.68701414752223544</v>
+        <v>0.62308223812580676</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.84117914792335635</v>
+        <v>0.84139720779109406</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14360,26 +14361,26 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>-0.15612466755507259</v>
+        <v>-7.4853111750415424E-2</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>0.10640657662233344</v>
+        <v>0.10638333467014371</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>-5.1789006476240678</v>
+        <v>-5.1773847711670085</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>-1.2912756695691492</v>
+        <v>-1.2913785828145734</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>-0.11764504345625726</v>
+        <v>-0.11772887072178551</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
@@ -14971,19 +14972,19 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>6.4075986575202437</v>
+        <v>6.4092597069164698</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>19.060019836747152</v>
+        <v>19.063868903239346</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>-10.40643192247197</v>
+        <v>-10.405566269766734</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>27.919092498170237</v>
+        <v>27.930517386878648</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -15079,24 +15080,24 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>1.7449376932917909E-2</v>
+        <v>1.9127481481925439E-2</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>2.0677671525677264E-2</v>
+        <v>2.0675075196021478E-2</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>1.7188869359004735E-2</v>
+        <v>1.7187072133989765E-2</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>-4.4280625282429676E-3</v>
+        <v>-4.4292062147632903E-3</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>1.2134393563506754E-2</v>
+        <v>1.2133240747371106E-2</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
@@ -15244,26 +15245,26 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>3.586906730443893E-2</v>
+        <v>3.931859133292645E-2</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>4.2505173365498042E-2</v>
+        <v>4.2499836331200143E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>4.0053745233584404E-2</v>
+        <v>4.0049557314566948E-2</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>-1.0072141586774769E-2</v>
+        <v>-1.0074743034358246E-2</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>3.4544522136555886E-2</v>
+        <v>3.45412402681783E-2</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
@@ -15365,26 +15366,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>4.7801032654770939E-2</v>
+        <v>5.2705700292116596E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.9040418180922618E-2</v>
+        <v>3.9030300309902691E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.7716115893087022E-2</v>
+        <v>3.7708500868107744E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.4108990165068649E-2</v>
+        <v>-5.4113491562926275E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3896931135127638E-2</v>
+        <v>1.3891246639942385E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
@@ -15422,26 +15423,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.9585484697439441E-2</v>
+        <v>0.10980354227524289</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.1334204543588792E-2</v>
+        <v>8.1313125645630605E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.8575241443931299E-2</v>
+        <v>7.8559376808557804E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.11272706284389303</v>
+        <v>-0.11273644075609641</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.8951939864849247E-2</v>
+        <v>2.8940097166546636E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -16270,7 +16271,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>226358.43266235912</v>
+        <v>249584.14176236014</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16309,7 +16310,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>1174988.3772033397</v>
+        <v>1177571.1638700066</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16330,7 +16331,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3122185.2781015052</v>
+        <v>3442539.8863773816</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16352,7 +16353,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-57701.513772033395</v>
+        <v>-57727.341638700062</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16363,14 +16364,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>-281221.22279666027</v>
+        <v>-278638.43612999341</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>-281221.22279666027</v>
+        <v>-278638.43612999341</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16393,7 +16394,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>2840964.0553048449</v>
+        <v>3163901.4502473883</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16404,7 +16405,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-5.9386631617869189E-2</v>
+        <v>-5.8841214032398434E-2</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16416,7 +16417,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-57701.513772033395</v>
+        <v>-57727.341638700062</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16454,7 +16455,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>3109907.2983475034</v>
+        <v>3463415.9460777827</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16477,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.59993795672379879</v>
+        <v>0.6681339624105892</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16550,14 +16551,14 @@
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
-        <v>1.2999999999999999E-3</v>
+        <v>-1.1861621958951121E-2</v>
       </c>
       <c r="E16" s="312" t="s">
         <v>401</v>
       </c>
       <c r="F16" s="315">
         <f>Scenarios!C41</f>
-        <v>1.2999999999999999E-3</v>
+        <v>-1.1861621958951121E-2</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
@@ -16566,14 +16567,14 @@
       </c>
       <c r="C17" s="310">
         <f>Normalized_FCF!C32</f>
-        <v>0.93869287456710004</v>
+        <v>0.93701337043131272</v>
       </c>
       <c r="E17" s="312" t="s">
         <v>402</v>
       </c>
       <c r="F17" s="315">
         <f>Scenarios!C40</f>
-        <v>0.93869287456710004</v>
+        <v>0.93701337043131272</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>414</v>
@@ -16599,7 +16600,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.6028020854131908</v>
+        <v>0.64010231245821247</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16658,23 +16659,23 @@
       </c>
       <c r="C21" s="281">
         <f>I4*(1+D21)</f>
-        <v>18477913.0999</v>
+        <v>18235029.541714408</v>
       </c>
       <c r="D21" s="303">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
-        <v>1.2999999999999999E-3</v>
+        <v>-1.1861621958951121E-2</v>
       </c>
       <c r="E21" s="303">
         <f>$C$17</f>
-        <v>0.93869287456710004</v>
+        <v>0.93701337043131272</v>
       </c>
       <c r="F21" s="281">
         <f>I5*(1+D21)</f>
-        <v>-752623.1398</v>
+        <v>-742730.25930104218</v>
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>322503.08258176106</v>
+        <v>348105.44997829251</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16682,11 +16683,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>226708.95760074846</v>
+        <v>246110.11409841591</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>1.548539342080435E-3</v>
+        <v>-1.3919264418858823E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16694,7 +16695,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>211383.64345058129</v>
+        <v>229473.29985866285</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16707,23 +16708,23 @@
       </c>
       <c r="C22" s="281">
         <f t="shared" ref="C22:C50" si="5">IF(A22="",0,C21*(1+D22))</f>
-        <v>18501934.38692987</v>
+        <v>18018732.514880285</v>
       </c>
       <c r="D22" s="303">
         <f t="shared" si="1"/>
-        <v>1.2999999999999999E-3</v>
+        <v>-1.1861621958951121E-2</v>
       </c>
       <c r="E22" s="303">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>0.93869287456710004</v>
+        <v>0.93701337043131272</v>
       </c>
       <c r="F22" s="281">
         <f t="shared" ref="F22:F50" si="7">IF(A22="",0,F21*(1+D22))</f>
-        <v>-753601.54988174001</v>
+        <v>-733920.2737477395</v>
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>322997.348557021</v>
+        <v>343291.6148255858</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16731,11 +16732,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>227059.93822155715</v>
+        <v>242677.29403729591</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>1.5481550641982533E-3</v>
+        <v>-1.3948309575555484E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16743,7 +16744,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>197399.43879597017</v>
+        <v>210976.72282788806</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16756,23 +16757,23 @@
       </c>
       <c r="C23" s="281">
         <f t="shared" si="5"/>
-        <v>18525986.901632879</v>
+        <v>17805001.121609315</v>
       </c>
       <c r="D23" s="303">
         <f t="shared" si="1"/>
-        <v>1.2999999999999999E-3</v>
+        <v>-1.1861621958951121E-2</v>
       </c>
       <c r="E23" s="303">
         <f t="shared" si="6"/>
-        <v>0.93869287456710004</v>
+        <v>0.93701337043131272</v>
       </c>
       <c r="F23" s="281">
         <f t="shared" si="7"/>
-        <v>-754581.23189658637</v>
+        <v>-725214.7889125339</v>
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>323492.25707804866</v>
+        <v>338534.87956563354</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16780,11 +16781,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>227411.37511717284</v>
+        <v>239285.19278999433</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>1.5477714755334215E-3</v>
+        <v>-1.3977827059421077E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16792,7 +16793,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>184340.29651899755</v>
+        <v>193965.24632413653</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -18208,7 +18209,7 @@
       </c>
       <c r="C51" s="281">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>18525986.901632879</v>
+        <v>17805001.121609315</v>
       </c>
       <c r="D51" s="305">
         <f>Terminal_Growth</f>
@@ -18216,15 +18217,15 @@
       </c>
       <c r="E51" s="305">
         <f>F17</f>
-        <v>0.93869287456710004</v>
+        <v>0.93701337043131272</v>
       </c>
       <c r="F51" s="281">
         <f>VLOOKUP(C15,B21:F50,5,FALSE)*(1+Terminal_Growth)</f>
-        <v>-754581.23189658637</v>
+        <v>-725214.7889125339</v>
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>323492.25707804866</v>
+        <v>338534.87956563354</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18232,7 +18233,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>3136708.6223058323</v>
+        <v>3300485.4177930253</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18244,7 +18245,7 @@
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>2542624.7795723798</v>
+        <v>2675382.707919125</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18257,7 +18258,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>3135748.1583379288</v>
+        <v>3309797.9769298127</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18281,7 +18282,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>3135748.1583379288</v>
+        <v>3309797.9769298127</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18289,7 +18290,7 @@
       </c>
       <c r="C55" s="123">
         <f>C93</f>
-        <v>-0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="D55" s="123">
         <f>C92</f>
@@ -18301,7 +18302,7 @@
       </c>
       <c r="F55" s="123">
         <f>C90</f>
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="G55" s="123"/>
       <c r="H55" s="123"/>
@@ -18316,19 +18317,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>3270949.1776829683</v>
+        <v>3604128.6576829767</v>
       </c>
       <c r="C56" s="118">
-        <v>2564320.6546710618</v>
+        <v>3361745.5007245881</v>
       </c>
       <c r="D56" s="118">
-        <v>3122185.2781015127</v>
+        <v>3442539.886377384</v>
       </c>
       <c r="E56" s="118">
-        <v>3196567.2278922405</v>
+        <v>3523334.2720301813</v>
       </c>
       <c r="F56" s="118">
-        <v>2006456.0312406113</v>
+        <v>3038567.9581134049</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18342,19 +18343,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>3415205.0803074073</v>
+        <v>3760820.7995550651</v>
       </c>
       <c r="C57" s="118">
-        <v>2122190.1838870202</v>
+        <v>3287919.3954194691</v>
       </c>
       <c r="D57" s="118">
-        <v>3122185.2781015127</v>
+        <v>3442539.886377384</v>
       </c>
       <c r="E57" s="118">
-        <v>3267308.1032176856</v>
+        <v>3600173.6877559153</v>
       </c>
       <c r="F57" s="118">
-        <v>1278241.1381845449</v>
+        <v>2699570.5357939806</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18368,19 +18369,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>3555089.5919432291</v>
+        <v>3912764.6947037606</v>
       </c>
       <c r="C58" s="118">
-        <v>1771783.7501654034</v>
+        <v>3220460.5765858879</v>
       </c>
       <c r="D58" s="118">
-        <v>3122185.2781015127</v>
+        <v>3442539.886377384</v>
       </c>
       <c r="E58" s="118">
-        <v>3334586.1384922382</v>
+        <v>3673251.7334810914</v>
       </c>
       <c r="F58" s="118">
-        <v>802949.36649293941</v>
+        <v>2415097.1744070523</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18394,19 +18395,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>3690735.1789840241</v>
+        <v>4060104.2293934007</v>
       </c>
       <c r="C59" s="118">
-        <v>1494072.3574722805</v>
+        <v>3158819.8843183736</v>
       </c>
       <c r="D59" s="118">
-        <v>3122185.2781015122</v>
+        <v>3442539.886377384</v>
       </c>
       <c r="E59" s="118">
-        <v>3398570.8433687333</v>
+        <v>3742752.5322127272</v>
       </c>
       <c r="F59" s="118">
-        <v>492735.62273151788</v>
+        <v>2176378.2697466919</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18420,19 +18421,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>3822270.2936902521</v>
+        <v>4202978.9296985082</v>
       </c>
       <c r="C60" s="118">
-        <v>1273974.7502096649</v>
+        <v>3102495.5221531838</v>
       </c>
       <c r="D60" s="118">
-        <v>3122185.2781015127</v>
+        <v>3442539.886377384</v>
       </c>
       <c r="E60" s="118">
-        <v>3459423.429824702</v>
+        <v>3808851.193943515</v>
       </c>
       <c r="F60" s="118">
-        <v>290265.11398280488</v>
+        <v>1976054.713388348</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18446,19 +18447,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>3949819.4958296237</v>
+        <v>4341524.093630733</v>
       </c>
       <c r="C61" s="118">
-        <v>1099538.4181134203</v>
+        <v>3051028.9721094687</v>
       </c>
       <c r="D61" s="118">
-        <v>3122185.2781015122</v>
+        <v>3442539.886377384</v>
       </c>
       <c r="E61" s="118">
-        <v>3517297.218342266</v>
+        <v>3871714.2568483185</v>
       </c>
       <c r="F61" s="118">
-        <v>158116.53018411115</v>
+        <v>1807951.0297309966</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18472,19 +18473,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>4073503.5706314379</v>
+        <v>4475870.9192619827</v>
       </c>
       <c r="C62" s="118">
-        <v>961290.50922595337</v>
+        <v>3004001.2620462133</v>
       </c>
       <c r="D62" s="118">
-        <v>3122185.2781015127</v>
+        <v>3442539.886377384</v>
       </c>
       <c r="E62" s="118">
-        <v>3572338.0242051254</v>
+        <v>3931500.1068836572</v>
       </c>
       <c r="F62" s="118">
-        <v>71865.706259555853</v>
+        <v>1666885.0014870649</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18498,19 +18499,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>4193439.6431665309</v>
+        <v>4606146.6289650109</v>
       </c>
       <c r="C63" s="118">
-        <v>851723.40194917307</v>
+        <v>2961029.5549487863</v>
       </c>
       <c r="D63" s="118">
-        <v>3122185.2781015127</v>
+        <v>3442539.886377384</v>
       </c>
       <c r="E63" s="118">
-        <v>3624684.524885884</v>
+        <v>3988359.3768473351</v>
       </c>
       <c r="F63" s="118">
-        <v>15571.462206233002</v>
+        <v>1548507.9148488005</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18524,19 +18525,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>4309741.289261166</v>
+        <v>4732474.5898891594</v>
       </c>
       <c r="C64" s="118">
-        <v>764886.99991163134</v>
+        <v>2921764.032379576</v>
       </c>
       <c r="D64" s="118">
-        <v>3122185.2781015122</v>
+        <v>3442539.886377384</v>
       </c>
       <c r="E64" s="118">
-        <v>3674468.6094494034</v>
+        <v>4042435.3259036988</v>
       </c>
       <c r="F64" s="118">
-        <v>-21170.701744653692</v>
+        <v>1449170.4994880194</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18550,19 +18551,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>4422518.6430499032</v>
+        <v>4854974.4307853039</v>
       </c>
       <c r="C65" s="118">
-        <v>696065.60901940742</v>
+        <v>2885885.0467219292</v>
       </c>
       <c r="D65" s="118">
-        <v>3122185.2781015127</v>
+        <v>3442539.886377384</v>
       </c>
       <c r="E65" s="118">
-        <v>3721815.7108524721</v>
+        <v>4093864.2005307321</v>
       </c>
       <c r="F65" s="118">
-        <v>-45151.601293018</v>
+        <v>1365810.4306537975</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18576,19 +18577,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>4937167.6826468892</v>
+        <v>5413991.1424744604</v>
       </c>
       <c r="C66" s="281">
-        <v>515361.64135387697</v>
+        <v>2747902.7626349656</v>
       </c>
       <c r="D66" s="118">
-        <v>3122185.2781015122</v>
+        <v>3442539.8863773835</v>
       </c>
       <c r="E66" s="118">
-        <v>3925973.2440116191</v>
+        <v>4315622.0667118626</v>
       </c>
       <c r="F66" s="118">
-        <v>-84878.841598690065</v>
+        <v>1111871.2218098568</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18611,19 +18612,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>5378424.4295261782</v>
+        <v>5893288.4434939595</v>
       </c>
       <c r="C67" s="281">
-        <v>458858.08118728868</v>
+        <v>2660007.1487042448</v>
       </c>
       <c r="D67" s="118">
-        <v>3122185.2781015122</v>
+        <v>3442539.8863773835</v>
       </c>
       <c r="E67" s="118">
-        <v>4084820.5171949985</v>
+        <v>4488163.4949156307</v>
       </c>
       <c r="F67" s="118">
-        <v>-89584.19333110677</v>
+        <v>1006200.2247800706</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18646,19 +18647,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>5756755.1008880902</v>
+        <v>6304234.8391221398</v>
       </c>
       <c r="C68" s="281">
-        <v>441190.22168899252</v>
+        <v>2604017.0699823326</v>
       </c>
       <c r="D68" s="118">
-        <v>3122185.2781015122</v>
+        <v>3442539.886377383</v>
       </c>
       <c r="E68" s="118">
-        <v>4208413.5867592059</v>
+        <v>4622411.4697869252</v>
       </c>
       <c r="F68" s="118">
-        <v>-90141.501987721305</v>
+        <v>962227.65487208369</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18681,19 +18682,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>6081133.3634425923</v>
+        <v>6656577.6120119076</v>
       </c>
       <c r="C69" s="281">
-        <v>435665.73335000599</v>
+        <v>2568351.0250559403</v>
       </c>
       <c r="D69" s="118">
-        <v>3122185.2781015122</v>
+        <v>3442539.8863773826</v>
       </c>
       <c r="E69" s="118">
-        <v>4304576.6907154713</v>
+        <v>4726864.7535267528</v>
       </c>
       <c r="F69" s="118">
-        <v>-90207.510430107795</v>
+        <v>943929.47506246413</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18763,7 +18764,7 @@
       </c>
       <c r="C72" s="124">
         <f>C55</f>
-        <v>-0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="D72" s="124">
         <f>D55</f>
@@ -18775,7 +18776,7 @@
       </c>
       <c r="F72" s="124">
         <f>F55</f>
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="G72" s="124"/>
       <c r="H72" s="124"/>
@@ -18790,23 +18791,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.59993795672379879</v>
+        <v>0.6681339624105892</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.59993795672379879</v>
+        <v>0.6681339624105892</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.59993795672379879</v>
+        <v>0.6681339624105892</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.59993795672379879</v>
+        <v>0.6681339624105892</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.59993795672379879</v>
+        <v>0.6681339624105892</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18821,23 +18822,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.63135303562369394</v>
+        <v>0.70225732173488931</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.48213141084920175</v>
+        <v>0.65107228274843998</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.59993795672380046</v>
+        <v>0.66813396241058964</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.6156454961737472</v>
+        <v>0.68519564207273964</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.36432486497460309</v>
+        <v>0.58282556409984132</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18852,23 +18853,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.66181614243571119</v>
+        <v>0.73534663986754312</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.38876491761525378</v>
+        <v>0.63548212324363196</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.59993795672380046</v>
+        <v>0.66813396241058964</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.63058413509117839</v>
+        <v>0.70142213461855996</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.21054475847163046</v>
+        <v>0.51123809698592637</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18883,23 +18884,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.69135612479887987</v>
+        <v>0.7674332513901172</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.31476816307086636</v>
+        <v>0.62123656957024087</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.59993795672380046</v>
+        <v>0.66813396241058964</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.64479151196370144</v>
+        <v>0.71685432333346644</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.11017545818996989</v>
+        <v>0.45116469800921466</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18914,23 +18915,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.72000095618134619</v>
+        <v>0.79854754135140049</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.25612271657881108</v>
+        <v>0.60821965339315642</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.59993795672380035</v>
+        <v>0.66813396241058964</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.65830342283547083</v>
+        <v>0.73153109022316776</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>4.4666357773035112E-2</v>
+        <v>0.40075345411267327</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18945,23 +18946,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.74777776237040483</v>
+        <v>0.82871897404113004</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.20964380793708881</v>
+        <v>0.59632540830826775</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.59993795672380046</v>
+        <v>0.66813396241058964</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.67115391149673442</v>
+        <v>0.7454894139784084</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>1.9098353563877697E-3</v>
+        <v>0.35845031238130992</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18976,23 +18977,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.77471284715979483</v>
+        <v>0.85797612089177677</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.17280737684574732</v>
+        <v>0.58545700720505967</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.59993795672380035</v>
+        <v>0.66813396241058964</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.68337535525849535</v>
+        <v>0.75876446314423129</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>-2.5996519600864555E-2</v>
+        <v>0.32295117246687921</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19008,23 +19009,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.80083171725859714</v>
+        <v>0.88634668753482826</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.14361300255424117</v>
+        <v>0.57552597402916783</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.59993795672380046</v>
+        <v>0.66813396241058964</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.69499854652842208</v>
+        <v>0.77138968472851066</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>-4.4210457568301963E-2</v>
+        <v>0.2931616844267973</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19039,23 +19040,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.82615910644531476</v>
+        <v>0.91385754003718112</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.12047527001551836</v>
+        <v>0.5664514635281197</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.59993795672380046</v>
+        <v>0.66813396241058964</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.70605277039352676</v>
+        <v>0.78339688847300004</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>-5.6098342488773933E-2</v>
+        <v>0.2681635126449104</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19071,23 +19072,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.85071899899001036</v>
+        <v>0.9405347303424928</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.10213767313168202</v>
+        <v>0.55815960311690582</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.59993795672380035</v>
+        <v>0.66813396241058964</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.716565878405095</v>
+        <v>0.79481632699922722</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>-6.3857334977660066E-2</v>
+        <v>0.24718602583493551</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19103,23 +19104,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.87453465236668493</v>
+        <v>0.96640352094158322</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>8.7604379564072882E-2</v>
+        <v>0.55058289150572648</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.59993795672380046</v>
+        <v>0.66813396241058964</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.72656435875176162</v>
+        <v>0.80567677203116406</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>-6.8921479259450566E-2</v>
+        <v>0.22958254039999146</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19135,23 +19136,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>0.9832151872960686</v>
+        <v>1.0844533579886284</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>4.9444386328428493E-2</v>
+        <v>0.52144461028578581</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.59993795672380035</v>
+        <v>0.66813396241058953</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.76967713698792506</v>
+        <v>0.85250628431440256</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>-7.7310842486611436E-2</v>
+        <v>0.17595716284499652</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19167,23 +19168,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.0763971726925523</v>
+        <v>1.1856685222213257</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>3.751229927133766E-2</v>
+        <v>0.50288333531009022</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.59993795672380035</v>
+        <v>0.66813396241058953</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.80322156298192382</v>
+        <v>0.88894256082887846</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>-7.8304490786645975E-2</v>
+        <v>0.15364218778410507</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19199,23 +19200,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.156290802293034</v>
+        <v>1.2724497472269076</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>3.3781305383083916E-2</v>
+        <v>0.49105968222215135</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.59993795672380035</v>
+        <v>0.66813396241058953</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.82932121513384682</v>
+        <v>0.9172922527541254</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>-7.8422179926742427E-2</v>
+        <v>0.14435632100475179</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19231,23 +19232,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.2247910818650973</v>
+        <v>1.3468554064041769</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>3.2614676667790159E-2</v>
+        <v>0.48352793817294226</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.59993795672380035</v>
+        <v>0.66813396241058942</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.84962836966894684</v>
+        <v>0.93935007833729312</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>-7.8436119198511081E-2</v>
+        <v>0.14049221980774815</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19286,7 +19287,7 @@
       </c>
       <c r="C90" s="130">
         <f>Scenarios!C29</f>
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D90" s="133">
         <f>Scenarios!D29</f>
@@ -19294,7 +19295,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.11017545818996989</v>
+        <v>0.45116469800921466</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19322,7 +19323,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.64479151196370144</v>
+        <v>0.71685432333346644</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19350,7 +19351,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.59993795672380046</v>
+        <v>0.66813396241058964</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19370,7 +19371,7 @@
       </c>
       <c r="C93" s="130">
         <f>Scenarios!C24</f>
-        <v>-0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="D93" s="133">
         <f>Scenarios!D24</f>
@@ -19378,7 +19379,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.31476816307086636</v>
+        <v>0.62123656957024087</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19406,7 +19407,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.69135612479887987</v>
+        <v>0.7674332513901172</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19615,7 +19616,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>184873.15815414075</v>
+        <v>184825.24568659026</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19628,7 +19629,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>226358.43266235912</v>
+        <v>249584.14176236014</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19766,7 +19767,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>0.64479151196370144</v>
+        <v>0.71685432333346644</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19790,7 +19791,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>0.59993795672380046</v>
+        <v>0.66813396241058964</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19805,7 +19806,7 @@
         <v>449</v>
       </c>
       <c r="C24" s="328">
-        <v>-0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="D24" s="329">
         <f>C18</f>
@@ -19813,7 +19814,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>0.31476816307086636</v>
+        <v>0.62123656957024087</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19829,7 +19830,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.53761621935854709</v>
+        <v>0.66615368638507777</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19868,7 +19869,7 @@
         <v>447</v>
       </c>
       <c r="C29" s="328">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D29" s="329">
         <f>C18</f>
@@ -19876,7 +19877,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>0.11017545818996989</v>
+        <v>0.45116469800921466</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19899,7 +19900,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>0.69135612479887987</v>
+        <v>0.7674332513901172</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19955,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>5.7029099355293308E-2</v>
+        <v>0.15148912164034103</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19964,7 +19965,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>0.59993795672379879</v>
+        <v>0.6681339624105892</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19975,7 +19976,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-2.2480608044181147E-2</v>
+        <v>2.6235909176886167E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19984,7 +19985,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.48118710045527707</v>
+        <v>0.63896931637895027</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20022,7 +20023,7 @@
       </c>
       <c r="C40" s="138">
         <f>DCF!C17</f>
-        <v>0.93869287456710004</v>
+        <v>0.93701337043131272</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>403</v>
@@ -20034,7 +20035,7 @@
       </c>
       <c r="C41" s="138">
         <f>DCF!C16</f>
-        <v>1.2999999999999999E-3</v>
+        <v>-1.1861621958951121E-2</v>
       </c>
       <c r="E41" s="97"/>
     </row>
@@ -20074,7 +20075,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="138">
-        <v>1.2999999999999999E-3</v>
+        <v>-1.1861621958951121E-2</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="221" t="s">
@@ -20087,7 +20088,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.6028020854131908</v>
+        <v>0.64010231245821247</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20150,7 +20151,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>1.1561769210134138</v>
+        <v>0.87153298843376326</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20228,11 +20229,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.22174520758307703</v>
+        <v>0.29445590616541495</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>0.27115120013805027</v>
+        <v>0.34386189872038819</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20240,7 +20241,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.43649528451303143</v>
+        <v>0.46184912184976379</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20253,11 +20254,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.27794200748319264</v>
+        <v>0.36907974953296779</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>0.33475011405945776</v>
+        <v>0.42588785610923291</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20265,7 +20266,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.30432442236557755</v>
+        <v>0.33347682714602567</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20299,11 +20300,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.34489585523597771</v>
+        <v>0.45798789833217612</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>0.41003613963632124</v>
+        <v>0.5231281827325196</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20311,7 +20312,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.14786547842125464</v>
+        <v>0.18129373457696574</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20324,11 +20325,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.39005160904259506</v>
+        <v>0.51795031443412687</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>0.46058574017626652</v>
+        <v>0.58848444556779833</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20336,7 +20337,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>4.2813617113838909E-2</v>
+        <v>7.9009851517206742E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20472,7 +20473,7 @@
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>5.7029099355293308E-2</v>
+        <v>0.15148912164034103</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20480,13 +20481,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20550,7 +20551,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>0.48118710045527707</v>
+        <v>0.63896931637895027</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20602,7 +20603,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>0.27115120013805027</v>
+        <v>0.34386189872038819</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20618,7 +20619,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>0.33475011405945776</v>
+        <v>0.42588785610923291</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20634,7 +20635,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>0.41003613963632124</v>
+        <v>0.5231281827325196</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20650,7 +20651,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>0.46058574017626652</v>
+        <v>0.58848444556779833</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20671,22 +20672,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20712,7 +20713,7 @@
       </c>
       <c r="C34" s="377">
         <f>Normalized_FCF!C8</f>
-        <v>379710.97209007666</v>
+        <v>410704.412090078</v>
       </c>
       <c r="D34" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20795,7 +20796,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>15191.436227966604</v>
+        <v>15165.608361299935</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20825,7 +20826,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-57701.513772033395</v>
+        <v>-57727.341638700062</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20865,7 +20866,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-80502.364579510817</v>
+        <v>-88244.267612844487</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20876,10 +20877,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20895,22 +20896,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20918,7 +20919,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>184873.15815414075</v>
+        <v>184825.24568659026</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20931,7 +20932,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>226358.43266235912</v>
+        <v>249584.14176236014</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20944,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.9585484697439441E-2</v>
+        <v>0.10980354227524289</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20961,7 +20962,7 @@
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>0.68701414752223544</v>
+        <v>0.62308223812580676</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -20981,11 +20982,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>3.586906730443893E-2</v>
+        <v>3.931859133292645E-2</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>4.2505173365498042E-2</v>
+        <v>4.2499836331200143E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -20995,11 +20996,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>1.7449376932917909E-2</v>
+        <v>1.9127481481925439E-2</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>2.0677671525677264E-2</v>
+        <v>2.0675075196021478E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21045,22 +21046,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21068,13 +21069,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21117,7 +21118,7 @@
       </c>
       <c r="C81" s="393">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>3.8393912927387319</v>
+        <v>3.5496550732945478</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -21131,7 +21132,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>1174988.3772033397</v>
+        <v>1177571.1638700066</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21157,7 +21158,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.24812708378950032</v>
+        <v>0.2486725013749711</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21201,7 +21202,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-5.9386631617869189E-2</v>
+        <v>-5.8841214032398434E-2</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21223,33 +21224,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21312,23 +21313,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21360,7 +21361,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>0.59993795672379879</v>
+        <v>0.6681339624105892</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21372,13 +21373,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21415,7 +21416,7 @@
       </c>
       <c r="C118" s="400">
         <f>DCF!C90</f>
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D118" s="401">
         <f>DCF!D90</f>
@@ -21423,7 +21424,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>0.11 HKD</v>
+        <v>0.45 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21446,7 +21447,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>0.64 HKD</v>
+        <v>0.72 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21468,7 +21469,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>0.6 HKD</v>
+        <v>0.67 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21482,7 +21483,7 @@
       </c>
       <c r="C121" s="405">
         <f>DCF!C93</f>
-        <v>-0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="D121" s="406">
         <f>DCF!D93</f>
@@ -21490,7 +21491,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>0.31 HKD</v>
+        <v>0.62 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21512,7 +21513,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>0.69 HKD</v>
+        <v>0.77 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21534,7 +21535,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>0.48118710045527707</v>
+        <v>0.63896931637895027</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21542,13 +21543,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21561,22 +21562,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21641,11 +21642,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>0.22174520758307703</v>
+        <v>0.29445590616541495</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>0.27115120013805027</v>
+        <v>0.34386189872038819</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21662,11 +21663,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>0.27794200748319264</v>
+        <v>0.36907974953296779</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>0.33475011405945776</v>
+        <v>0.42588785610923291</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21702,11 +21703,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>0.34489585523597771</v>
+        <v>0.45798789833217612</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>0.41003613963632124</v>
+        <v>0.5231281827325196</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21723,11 +21724,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>0.39005160904259506</v>
+        <v>0.51795031443412687</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>0.46058574017626652</v>
+        <v>0.58848444556779833</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21745,13 +21746,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21759,13 +21760,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21802,22 +21803,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21841,12 +21842,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21861,15 +21865,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6B0A36-998A-419B-B12F-CB9562FC6464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE59656-8DB3-4D65-9A26-EFE949611A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>0.48</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>2488.1831304000002</v>
+        <v>2462.2645561250001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.15148912164034103</v>
+        <v>0.15467039222643886</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0946661899999999</v>
+        <v>1.0914274799999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>0.63896931637895027</v>
+        <v>0.63707884389194525</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>0.34386189872038819</v>
+        <v>0.34299071324250568</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>0.42588785610923291</v>
+        <v>0.42479588644164878</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>0.5231281827325196</v>
+        <v>0.52177316692975029</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>0.58848444556779833</v>
+        <v>0.5869520232840143</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10980354227524289</v>
+        <v>0.11063108154403639</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6250000000000001E-2</v>
+        <v>5.6842105263157895E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.30786202592681183</v>
+        <v>-0.30695117672812655</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.2486725013749711</v>
+        <v>0.24793677195874775</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.4831051944233529E-4</v>
+        <v>3.4727999819966939E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-5.8841214032398434E-2</v>
+        <v>-5.8667124771179115E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.58105391455460365</v>
+        <v>0.57933479219493056</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.6681339624105892</v>
+        <v>0.66615720258630085</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.17672737131882851</v>
+        <v>0.17688735102676695</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>0.72 HKD</v>
+        <v>0.71 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.5028267395837255E-3</v>
+        <v>1.6187835994120056E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.6235909176885886E-2</v>
+        <v>2.6357534088034516E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.2494022835921784E-2</v>
+        <v>5.2621857061811952E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-2.1853207340008177E-2</v>
+        <v>-2.1742444432095099E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.63896931637895027</v>
+        <v>0.63707884389194525</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>0.29445590616541495</v>
+        <v>0.29358472068753244</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>0.34386189872038819</v>
+        <v>0.34299071324250568</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>0.36907974953296779</v>
+        <v>0.36798777986538367</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>0.42588785610923291</v>
+        <v>0.42479588644164878</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>0.45798789833217612</v>
+        <v>0.45663288252940676</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>0.5231281827325196</v>
+        <v>0.52177316692975029</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>0.51795031443412687</v>
+        <v>0.51641789215034284</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>0.58848444556779833</v>
+        <v>0.5869520232840143</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10176,11 +10176,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8728091106241298</v>
+        <v>1.8672681652198788</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.58105391455460365</v>
+        <v>0.57933479219493056</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10586,11 +10586,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>1595868.9570872099</v>
+        <v>1591147.3745653199</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.30786202592681189</v>
+        <v>0.30695117672812655</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1289047.3394074456</v>
+        <v>1285233.5279033082</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.2486725013749711</v>
+        <v>0.24793677195874775</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10620,11 +10620,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>1805.5424137859995</v>
+        <v>1800.2004855119997</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>3.4831051944233529E-4</v>
+        <v>3.4727999819966939E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10637,11 +10637,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2886721.8389084414</v>
+        <v>2878181.1029541404</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>0.55688283782122527</v>
+        <v>0.55523522868507402</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14224,12 +14224,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6250000000000001E-2</v>
+        <v>5.6842105263157895E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.6250000000000001E-2</v>
+        <v>5.6842105263157895E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -15366,50 +15366,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2705700292116596E-2</v>
+        <v>5.2549763733417292E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.9030300309902691E-2</v>
+        <v>3.891482417199741E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.7708500868107744E-2</v>
+        <v>3.7596935442992578E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.4113491562926275E-2</v>
+        <v>-5.3953389873606934E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3891246639942385E-2</v>
+        <v>1.3850147609191059E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.0313975629695395E-2</v>
+        <v>4.0194701574093432E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.14854723550619567</v>
+        <v>0.14810773950138503</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>8.5756313672787854E-2</v>
+        <v>8.5502592645142705E-2</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>5.9016607589444652E-2</v>
+        <v>5.8841999403942906E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>8.9671692198906638E-2</v>
+        <v>8.9406387022867975E-2</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1402555358195912E-2</v>
+        <v>1.1368819439062297E-2</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10980354227524289</v>
+        <v>0.11063108154403639</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.1313125645630605E-2</v>
+        <v>8.1925945625257707E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.8559376808557804E-2</v>
+        <v>7.9151443037879118E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.11273644075609641</v>
+        <v>-0.11358608394443566</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.8940097166546636E-2</v>
+        <v>2.9158205493033808E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>8.3987449228532074E-2</v>
+        <v>8.4620424366512487E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.30947340730457434</v>
+        <v>0.31180576737133692</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.17865898681830802</v>
+        <v>0.18000545820030045</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12295126581134302</v>
+        <v>0.12387789348198507</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.18681602541438883</v>
+        <v>0.18822397267972207</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>2.375532366290815E-2</v>
+        <v>2.3934356713815365E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20007450171883859</v>
+        <v>0.20218054910535269</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2022391333869</v>
+        <v>0.20436796636992</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0285619967162845E-2</v>
+        <v>4.0709679124711934E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15101581367107558</v>
+        <v>0.15260545381498167</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12646175281697022</v>
+        <v>0.12779292916241203</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.35363554605345537</v>
+        <v>0.35735802548559703</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22542311823721381</v>
+        <v>0.22779599316602658</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16680122734104363</v>
+        <v>0.16855702973410724</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22892647773414868</v>
+        <v>0.23133623013135027</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5061660147971235E-2</v>
+        <v>2.5325467096897251E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-5.8841214032398434E-2</v>
+        <v>-5.8667124771179115E-2</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0946661899999999</v>
+        <v>1.0914274799999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>3463415.9460777827</v>
+        <v>3453168.9868118521</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.6681339624105892</v>
+        <v>0.66615720258630085</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.64010231245821247</v>
+        <v>0.6382084878573252</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.6681339624105892</v>
+        <v>0.66615720258630085</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.6681339624105892</v>
+        <v>0.66615720258630085</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.6681339624105892</v>
+        <v>0.66615720258630085</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.6681339624105892</v>
+        <v>0.66615720258630085</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.6681339624105892</v>
+        <v>0.66615720258630085</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.70225732173488931</v>
+        <v>0.70017960358550901</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.65107228274843998</v>
+        <v>0.6491460020866977</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.66813396241058964</v>
+        <v>0.66615720258630129</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.68519564207273964</v>
+        <v>0.68316840308590532</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.58282556409984132</v>
+        <v>0.58110120008828292</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.73534663986754312</v>
+        <v>0.73317102273625545</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.63548212324363196</v>
+        <v>0.6336019680637498</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.66813396241058964</v>
+        <v>0.66615720258630129</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.70142213461855996</v>
+        <v>0.69934688747713647</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.51123809698592637</v>
+        <v>0.50972553365637896</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18884,23 +18884,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.7674332513901172</v>
+        <v>0.7651627019127375</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.62123656957024087</v>
+        <v>0.61939856168380669</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.66813396241058964</v>
+        <v>0.66615720258630129</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.71685432333346644</v>
+        <v>0.7147334180869791</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.45116469800921466</v>
+        <v>0.44982986951771864</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18915,23 +18915,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.79854754135140049</v>
+        <v>0.7961849362656892</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.60821965339315642</v>
+        <v>0.60642015771891722</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.66813396241058964</v>
+        <v>0.66615720258630129</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.73153109022316776</v>
+        <v>0.72936676188375249</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>0.40075345411267327</v>
+        <v>0.39956777373702446</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18946,23 +18946,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.82871897404113004</v>
+        <v>0.82626710291097605</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.59632540830826775</v>
+        <v>0.59456110328013667</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.66813396241058964</v>
+        <v>0.66615720258630129</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.7454894139784084</v>
+        <v>0.7432837881520129</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>0.35845031238130992</v>
+        <v>0.35738979126371473</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18977,23 +18977,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.85797612089177677</v>
+        <v>0.85543768874882964</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.58545700720505967</v>
+        <v>0.58372485773234672</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.66813396241058964</v>
+        <v>0.66615720258630129</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.75876446314423129</v>
+        <v>0.75651956138616216</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>0.32295117246687921</v>
+        <v>0.32199568009730101</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19009,23 +19009,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.88634668753482826</v>
+        <v>0.88372431744008195</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.57552597402916783</v>
+        <v>0.57382320678891163</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.66813396241058964</v>
+        <v>0.66615720258630129</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.77138968472851066</v>
+        <v>0.76910742963682188</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>0.2931616844267973</v>
+        <v>0.29229432806954114</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19040,23 +19040,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.91385754003718112</v>
+        <v>0.91115377556493238</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.5664514635281197</v>
+        <v>0.56477554438838351</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.66813396241058964</v>
+        <v>0.66615720258630129</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.78339688847300004</v>
+        <v>0.78107910853255402</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>0.2681635126449104</v>
+        <v>0.26737011657771459</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19072,23 +19072,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.9405347303424928</v>
+        <v>0.93775203798902973</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.55815960311690582</v>
+        <v>0.55650821650724835</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.66813396241058964</v>
+        <v>0.66615720258630129</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.79481632699922722</v>
+        <v>0.79246476118863463</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>0.24718602583493551</v>
+        <v>0.24645469434681139</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19104,23 +19104,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.96640352094158322</v>
+        <v>0.96354429246088191</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>0.55058289150572648</v>
+        <v>0.54895392156691025</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.66813396241058964</v>
+        <v>0.66615720258630129</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.80567677203116406</v>
+        <v>0.80329307420420826</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>0.22958254039999146</v>
+        <v>0.22890329107612328</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19136,23 +19136,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>1.0844533579886284</v>
+        <v>1.0812448639589998</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>0.52144461028578581</v>
+        <v>0.51990184968058373</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.66813396241058953</v>
+        <v>0.66615720258630118</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.85250628431440256</v>
+        <v>0.8499840353829069</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>0.17595716284499652</v>
+        <v>0.17543657106269461</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19168,23 +19168,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.1856685222213257</v>
+        <v>1.1821605701765079</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>0.50288333531009022</v>
+        <v>0.50139549061206212</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.66813396241058953</v>
+        <v>0.66615720258630118</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.88894256082887846</v>
+        <v>0.88631251051081572</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>0.15364218778410507</v>
+        <v>0.15318761771101436</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19200,23 +19200,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.2724497472269076</v>
+        <v>1.2686850418231157</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>0.49105968222215135</v>
+        <v>0.48960681931477523</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.66813396241058953</v>
+        <v>0.66615720258630118</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.9172922527541254</v>
+        <v>0.91457832624478708</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>0.14435632100475179</v>
+        <v>0.14392922435677613</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19232,23 +19232,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.3468554064041769</v>
+        <v>1.3428705623365298</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>0.48352793817294226</v>
+        <v>0.48209735889412114</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.66813396241058942</v>
+        <v>0.66615720258630107</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.93935007833729312</v>
+        <v>0.9365708909283792</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>0.14049221980774815</v>
+        <v>0.14007655559762622</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.45116469800921466</v>
+        <v>0.44982986951771864</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.71685432333346644</v>
+        <v>0.7147334180869791</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.66813396241058964</v>
+        <v>0.66615720258630129</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.62123656957024087</v>
+        <v>0.61939856168380669</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.7674332513901172</v>
+        <v>0.7651627019127375</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>0.71685432333346644</v>
+        <v>0.7147334180869791</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>0.66813396241058964</v>
+        <v>0.66615720258630129</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>0.62123656957024087</v>
+        <v>0.61939856168380669</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.66615368638507777</v>
+        <v>0.66418278546081322</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>0.45116469800921466</v>
+        <v>0.44982986951771864</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>0.7674332513901172</v>
+        <v>0.7651627019127375</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>0.48</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15148912164034103</v>
+        <v>0.15467039222643886</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>0.6681339624105892</v>
+        <v>0.66615720258630085</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>2.6235909176886167E-2</v>
+        <v>2.6357534088034731E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.63896931637895027</v>
+        <v>0.63707884389194525</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.64010231245821247</v>
+        <v>0.6382084878573252</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.87153298843376326</v>
+        <v>0.87153298843376337</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20229,11 +20229,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.29445590616541495</v>
+        <v>0.29358472068753244</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>0.34386189872038819</v>
+        <v>0.34299071324250568</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46184912184976379</v>
+        <v>0.46161967779818436</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20254,11 +20254,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.36907974953296779</v>
+        <v>0.36798777986538367</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>0.42588785610923291</v>
+        <v>0.42479588644164878</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33347682714602567</v>
+        <v>0.33321300728407444</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20300,11 +20300,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.45798789833217612</v>
+        <v>0.45663288252940676</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>0.5231281827325196</v>
+        <v>0.52177316692975029</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.18129373457696574</v>
+        <v>0.18099121963898068</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20325,11 +20325,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.51795031443412687</v>
+        <v>0.51641789215034284</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>0.58848444556779833</v>
+        <v>0.5869520232840143</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>7.9009851517206742E-2</v>
+        <v>7.8682287268721396E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>0.48</v>
+        <v>0.47499999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>2488.1831304000002</v>
+        <v>2462.2645561250001</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.15148912164034103</v>
+        <v>0.15467039222643886</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20481,13 +20481,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0946661899999999</v>
+        <v>1.0914274799999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>0.63896931637895027</v>
+        <v>0.63707884389194525</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>0.34386189872038819</v>
+        <v>0.34299071324250568</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>0.42588785610923291</v>
+        <v>0.42479588644164878</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20635,7 +20635,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>0.5231281827325196</v>
+        <v>0.52177316692975029</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>0.58848444556779833</v>
+        <v>0.5869520232840143</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20672,22 +20672,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20877,10 +20877,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20896,22 +20896,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10980354227524289</v>
+        <v>0.11063108154403639</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.6250000000000001E-2</v>
+        <v>5.6842105263157895E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21046,22 +21046,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21069,13 +21069,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.30786202592681183</v>
+        <v>-0.30695117672812655</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.2486725013749711</v>
+        <v>0.24793677195874775</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.4831051944233529E-4</v>
+        <v>3.4727999819966939E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-5.8841214032398434E-2</v>
+        <v>-5.8667124771179115E-2</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21224,33 +21224,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21313,23 +21313,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21347,7 +21347,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>0.58105391455460365</v>
+        <v>0.57933479219493056</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>0.6681339624105892</v>
+        <v>0.66615720258630085</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21373,13 +21373,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>0.72 HKD</v>
+        <v>0.71 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>0.63896931637895027</v>
+        <v>0.63707884389194525</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21543,13 +21543,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21562,22 +21562,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21642,11 +21642,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>0.29445590616541495</v>
+        <v>0.29358472068753244</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>0.34386189872038819</v>
+        <v>0.34299071324250568</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21663,11 +21663,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>0.36907974953296779</v>
+        <v>0.36798777986538367</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>0.42588785610923291</v>
+        <v>0.42479588644164878</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21703,11 +21703,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>0.45798789833217612</v>
+        <v>0.45663288252940676</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>0.5231281827325196</v>
+        <v>0.52177316692975029</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21724,11 +21724,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>0.51795031443412687</v>
+        <v>0.51641789215034284</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>0.58848444556779833</v>
+        <v>0.5869520232840143</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21746,13 +21746,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21760,13 +21760,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21803,22 +21803,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21842,15 +21842,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21865,12 +21862,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE59656-8DB3-4D65-9A26-EFE949611A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1083046A-7A06-4DB1-88E9-34B58CCD215B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>0.47499999999999998</v>
+        <v>0.48</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>2462.2645561250001</v>
+        <v>2488.1831304000002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.15467039222643886</v>
+        <v>0.15077592809603155</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0914274799999999</v>
+        <v>1.0924437000000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>0.63707884389194525</v>
+        <v>0.63767202325988648</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>0.34299071324250568</v>
+        <v>0.34326406778994406</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>0.42479588644164878</v>
+        <v>0.4251385171234921</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>0.52177316692975029</v>
+        <v>0.52219833440664409</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>0.5869520232840143</v>
+        <v>0.58743285613821483</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11063108154403639</v>
+        <v>0.10958060922323069</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6842105263157895E-2</v>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.30695117672812655</v>
+        <v>-0.30723697668325939</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.24793677195874775</v>
+        <v>0.24816762404101345</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.4727999819966939E-4</v>
+        <v>3.4760334802019121E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-5.8667124771179115E-2</v>
+        <v>-5.8721749294225745E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.57933479219493056</v>
+        <v>0.5798742065062914</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.66615720258630085</v>
+        <v>0.66677745659750876</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.17688735102676695</v>
+        <v>0.17683705122730217</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>0.71 HKD</v>
+        <v>0.72 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.6187835994120056E-3</v>
+        <v>1.5823255105697613E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.6357534088034516E-2</v>
+        <v>2.6319293856835194E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.2621857061811952E-2</v>
+        <v>5.2581664500513041E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-2.1742444432095099E-2</v>
+        <v>-2.177726944772846E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.63707884389194525</v>
+        <v>0.63767202325988648</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>0.29358472068753244</v>
+        <v>0.29385807523497082</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>0.34299071324250568</v>
+        <v>0.34326406778994406</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>0.36798777986538367</v>
+        <v>0.36833041054722698</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>0.42479588644164878</v>
+        <v>0.4251385171234921</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>0.45663288252940676</v>
+        <v>0.45705805000630056</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>0.52177316692975029</v>
+        <v>0.52219833440664409</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>0.51641789215034284</v>
+        <v>0.51689872500454337</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>0.5869520232840143</v>
+        <v>0.58743285613821483</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10176,11 +10176,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8672681652198788</v>
+        <v>1.8690067647050781</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.57933479219493056</v>
+        <v>0.5798742065062914</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10586,11 +10586,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>1591147.3745653199</v>
+        <v>1592628.8800383003</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.30695117672812655</v>
+        <v>0.30723697668325939</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1285233.5279033082</v>
+        <v>1286430.1992714566</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.24793677195874775</v>
+        <v>0.24816762404101345</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10620,11 +10620,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>1800.2004855119997</v>
+        <v>1801.8766387800003</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>3.4727999819966939E-4</v>
+        <v>3.4760334802019126E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10637,11 +10637,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2878181.1029541404</v>
+        <v>2880860.9559485367</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>0.55523522868507402</v>
+        <v>0.55575220407229298</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14224,12 +14224,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6842105263157895E-2</v>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.6842105263157895E-2</v>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -15366,50 +15366,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2549763733417292E-2</v>
+        <v>5.2598692427150741E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.891482417199741E-2</v>
+        <v>3.8951057475029222E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.7596935442992578E-2</v>
+        <v>3.7631941669641643E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.3953389873606934E-2</v>
+        <v>-5.4003625473188301E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3850147609191059E-2</v>
+        <v>1.3863043378503571E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.0194701574093432E-2</v>
+        <v>4.0232126561444523E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.14810773950138503</v>
+        <v>0.14824564151484373</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>8.5502592645142705E-2</v>
+        <v>8.5582203472513371E-2</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>5.8841999403942906E-2</v>
+        <v>5.8896786751458013E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>8.9406387022867975E-2</v>
+        <v>8.9489632644116593E-2</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1368819439062297E-2</v>
+        <v>1.1379404862191252E-2</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11063108154403639</v>
+        <v>0.10958060922323069</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.1925945625257707E-2</v>
+        <v>8.1148036406310881E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.9151443037879118E-2</v>
+        <v>7.8399878478420088E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.11358608394443566</v>
+        <v>-0.1125075530691423</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.9158205493033808E-2</v>
+        <v>2.888134037188244E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>8.4620424366512487E-2</v>
+        <v>8.3816930336342757E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.31180576737133692</v>
+        <v>0.30884508648925779</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.18000545820030045</v>
+        <v>0.17829625723440287</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12387789348198507</v>
+        <v>0.12270163906553753</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.18822397267972207</v>
+        <v>0.18643673467524291</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>2.3934356713815365E-2</v>
+        <v>2.370709346289844E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20218054910535269</v>
+        <v>0.20007450171883859</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20436796636992</v>
+        <v>0.2022391333869</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0709679124711934E-2</v>
+        <v>4.0285619967162845E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15260545381498167</v>
+        <v>0.15101581367107558</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12779292916241203</v>
+        <v>0.12646175281697022</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.35735802548559703</v>
+        <v>0.35363554605345537</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22779599316602658</v>
+        <v>0.22542311823721381</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16855702973410724</v>
+        <v>0.16680122734104363</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23133623013135027</v>
+        <v>0.22892647773414868</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5325467096897251E-2</v>
+        <v>2.5061660147971235E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-5.8667124771179115E-2</v>
+        <v>-5.8721749294225745E-2</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0914274799999999</v>
+        <v>1.0924437000000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>3453168.9868118521</v>
+        <v>3456384.2067436236</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.66615720258630085</v>
+        <v>0.66677745659750876</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.6382084878573252</v>
+        <v>0.63880271902835151</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.66615720258630085</v>
+        <v>0.66677745659750876</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.66615720258630085</v>
+        <v>0.66677745659750876</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.66615720258630085</v>
+        <v>0.66677745659750876</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.66615720258630085</v>
+        <v>0.66677745659750876</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.66615720258630085</v>
+        <v>0.66677745659750876</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.70017960358550901</v>
+        <v>0.70083153560096079</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.6491460020866977</v>
+        <v>0.64975041709578352</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.66615720258630129</v>
+        <v>0.6667774565975092</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.68316840308590532</v>
+        <v>0.68380449609923522</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.58110120008828292</v>
+        <v>0.58164225908888079</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.73317102273625545</v>
+        <v>0.73385367281642877</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.6336019680637498</v>
+        <v>0.63419191013849574</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.66615720258630129</v>
+        <v>0.6667774565975092</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.69934688747713647</v>
+        <v>0.6999980441568201</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.50972553365637896</v>
+        <v>0.51020013530541619</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18884,23 +18884,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.7651627019127375</v>
+        <v>0.76587513920718608</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.61939856168380669</v>
+        <v>0.61997527907262895</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.66615720258630129</v>
+        <v>0.6667774565975092</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.7147334180869791</v>
+        <v>0.71539890105074744</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.44982986951771864</v>
+        <v>0.45024870275985163</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18915,23 +18915,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.7961849362656892</v>
+        <v>0.79692625813155626</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.60642015771891722</v>
+        <v>0.60698479101244329</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.66615720258630129</v>
+        <v>0.6667774565975092</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.72936676188375249</v>
+        <v>0.73004586984497211</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>0.39956777373702446</v>
+        <v>0.39993980831602111</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18946,23 +18946,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.82626710291097605</v>
+        <v>0.82703643405821858</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.59456110328013667</v>
+        <v>0.5951146946963759</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.66615720258630129</v>
+        <v>0.6667774565975092</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.7432837881520129</v>
+        <v>0.74397585415276646</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>0.35738979126371473</v>
+        <v>0.35772255423728228</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18977,23 +18977,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.85543768874882964</v>
+        <v>0.85623418041134547</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.58372485773234672</v>
+        <v>0.58426835960104162</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.66615720258630129</v>
+        <v>0.6667774565975092</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.75651956138616216</v>
+        <v>0.75722395111682217</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>0.32199568009730101</v>
+        <v>0.32229548787750151</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19009,23 +19009,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.88372431744008195</v>
+        <v>0.88454714657195355</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.57382320678891163</v>
+        <v>0.57435748930413955</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.66615720258630129</v>
+        <v>0.6667774565975092</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.76910742963682188</v>
+        <v>0.76982353983788232</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>0.29229432806954114</v>
+        <v>0.29256648114202094</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19040,23 +19040,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.91115377556493238</v>
+        <v>0.91200214406102786</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.56477554438838351</v>
+        <v>0.56530140269251794</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.66615720258630129</v>
+        <v>0.6667774565975092</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.78107910853255402</v>
+        <v>0.78180636547469484</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>0.26737011657771459</v>
+        <v>0.26761906290245685</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19072,23 +19072,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.93775203798902973</v>
+        <v>0.93862517192922112</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.55650821650724835</v>
+        <v>0.55702637716395009</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.66615720258630129</v>
+        <v>0.6667774565975092</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.79246476118863463</v>
+        <v>0.79320261922718738</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>0.24645469434681139</v>
+        <v>0.24668416647764796</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19104,23 +19104,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.96354429246088191</v>
+        <v>0.96444144137716625</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>0.54895392156691025</v>
+        <v>0.54946504847584132</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.66615720258630129</v>
+        <v>0.6667774565975092</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.80329307420420826</v>
+        <v>0.80404101440438358</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>0.22890329107612328</v>
+        <v>0.22911642122606002</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19136,23 +19136,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>1.0812448639589998</v>
+        <v>1.0822516030010227</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>0.51990184968058373</v>
+        <v>0.52038592642169945</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.66615720258630118</v>
+        <v>0.66677745659750909</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.8499840353829069</v>
+        <v>0.85077544918938086</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>0.17543657106269461</v>
+        <v>0.17559991874773312</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19168,23 +19168,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.1821605701765079</v>
+        <v>1.1832612710811847</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>0.50139549061206212</v>
+        <v>0.50186233622004517</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.66615720258630118</v>
+        <v>0.66677745659750909</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.88631251051081572</v>
+        <v>0.88713774948998414</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>0.15318761771101436</v>
+        <v>0.15333024956124991</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19200,23 +19200,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.2686850418231157</v>
+        <v>1.2698663050190928</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>0.48960681931477523</v>
+        <v>0.49006268857869029</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.66615720258630118</v>
+        <v>0.66677745659750909</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.91457832624478708</v>
+        <v>0.91542988331452191</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>0.14392922435677613</v>
+        <v>0.14406323578589636</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19232,23 +19232,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.3428705623365298</v>
+        <v>1.3441208991182811</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>0.48209735889412114</v>
+        <v>0.48254623615535297</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.66615720258630107</v>
+        <v>0.66677745659750898</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.9365708909283792</v>
+        <v>0.93744292511133709</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>0.14007655559762622</v>
+        <v>0.14020697983555128</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.44982986951771864</v>
+        <v>0.45024870275985163</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.7147334180869791</v>
+        <v>0.71539890105074744</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.66615720258630129</v>
+        <v>0.6667774565975092</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.61939856168380669</v>
+        <v>0.61997527907262895</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.7651627019127375</v>
+        <v>0.76587513920718608</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>0.7147334180869791</v>
+        <v>0.71539890105074744</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>0.66615720258630129</v>
+        <v>0.6667774565975092</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>0.61939856168380669</v>
+        <v>0.61997527907262895</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.66418278546081322</v>
+        <v>0.66480120110693675</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>0.44982986951771864</v>
+        <v>0.45024870275985163</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>0.7651627019127375</v>
+        <v>0.76587513920718608</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>0.47499999999999998</v>
+        <v>0.48</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15467039222643886</v>
+        <v>0.15077592809603155</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>0.66615720258630085</v>
+        <v>0.66677745659750876</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>2.6357534088034731E-2</v>
+        <v>2.6319293856835419E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.63707884389194525</v>
+        <v>0.63767202325988648</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.6382084878573252</v>
+        <v>0.63880271902835151</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.87153298843376337</v>
+        <v>0.87153298843376314</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20229,11 +20229,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.29358472068753244</v>
+        <v>0.29385807523497082</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>0.34299071324250568</v>
+        <v>0.34326406778994406</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46161967779818436</v>
+        <v>0.46169181762888001</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20254,11 +20254,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.36798777986538367</v>
+        <v>0.36833041054722698</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>0.42479588644164878</v>
+        <v>0.4251385171234921</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33321300728407444</v>
+        <v>0.33329595526221678</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20300,11 +20300,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.45663288252940676</v>
+        <v>0.45705805000630056</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>0.52177316692975029</v>
+        <v>0.52219833440664409</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.18099121963898068</v>
+        <v>0.18108633379103178</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20325,11 +20325,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.51641789215034284</v>
+        <v>0.51689872500454337</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>0.5869520232840143</v>
+        <v>0.58743285613821483</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>7.8682287268721396E-2</v>
+        <v>7.8785277210125293E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>0.47499999999999998</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>2462.2645561250001</v>
+        <v>2488.1831304000002</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.15467039222643886</v>
+        <v>0.15077592809603155</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20481,13 +20481,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0914274799999999</v>
+        <v>1.0924437000000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>0.63707884389194525</v>
+        <v>0.63767202325988648</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>0.34299071324250568</v>
+        <v>0.34326406778994406</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>0.42479588644164878</v>
+        <v>0.4251385171234921</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20635,7 +20635,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>0.52177316692975029</v>
+        <v>0.52219833440664409</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>0.5869520232840143</v>
+        <v>0.58743285613821483</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20672,22 +20672,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20877,10 +20877,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20896,22 +20896,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.11063108154403639</v>
+        <v>0.10958060922323069</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.6842105263157895E-2</v>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21046,22 +21046,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21069,13 +21069,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.30695117672812655</v>
+        <v>-0.30723697668325939</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.24793677195874775</v>
+        <v>0.24816762404101345</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.4727999819966939E-4</v>
+        <v>3.4760334802019121E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-5.8667124771179115E-2</v>
+        <v>-5.8721749294225745E-2</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21224,33 +21224,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21313,23 +21313,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21347,7 +21347,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>0.57933479219493056</v>
+        <v>0.5798742065062914</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>0.66615720258630085</v>
+        <v>0.66677745659750876</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21373,13 +21373,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>0.71 HKD</v>
+        <v>0.72 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>0.63707884389194525</v>
+        <v>0.63767202325988648</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21543,13 +21543,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21562,22 +21562,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21642,11 +21642,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>0.29358472068753244</v>
+        <v>0.29385807523497082</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>0.34299071324250568</v>
+        <v>0.34326406778994406</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21663,11 +21663,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>0.36798777986538367</v>
+        <v>0.36833041054722698</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>0.42479588644164878</v>
+        <v>0.4251385171234921</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21703,11 +21703,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>0.45663288252940676</v>
+        <v>0.45705805000630056</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>0.52177316692975029</v>
+        <v>0.52219833440664409</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21724,11 +21724,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>0.51641789215034284</v>
+        <v>0.51689872500454337</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>0.5869520232840143</v>
+        <v>0.58743285613821483</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21746,13 +21746,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21760,13 +21760,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21803,22 +21803,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21842,12 +21842,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21862,15 +21865,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1083046A-7A06-4DB1-88E9-34B58CCD215B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF43B9A1-59AB-414B-8200-46A6B6006EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>0.48</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>2488.1831304000002</v>
+        <v>2410.4274075750004</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.15077592809603155</v>
+        <v>0.16461424988614515</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0924437000000002</v>
+        <v>1.0954849</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>0.63767202325988648</v>
+        <v>0.63944720687542456</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>0.34326406778994406</v>
+        <v>0.34408212475562977</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>0.4251385171234921</v>
+        <v>0.42616389394113141</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>0.52219833440664409</v>
+        <v>0.52347071571259063</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>0.58743285613821483</v>
+        <v>0.58887182494043655</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10958060922323069</v>
+        <v>0.11343036414242963</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6250000000000001E-2</v>
+        <v>5.8064516129032254E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.30723697668325939</v>
+        <v>-0.3080922785111605</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.24816762404101345</v>
+        <v>0.2488584856188078</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.4760334802019121E-4</v>
+        <v>3.4857102379332164E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-5.8721749294225745E-2</v>
+        <v>-5.8885221868559406E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.5798742065062914</v>
+        <v>0.58148848963761146</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.66677745659750876</v>
+        <v>0.66863366538978253</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.17683705122730217</v>
+        <v>0.17668708052046878</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.5823255105697613E-3</v>
+        <v>1.4736225914358805E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.6319293856835194E-2</v>
+        <v>2.6205277576844144E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.2581664500513041E-2</v>
+        <v>5.2461827477559897E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-2.177726944772846E-2</v>
+        <v>-2.1881103429389998E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.63767202325988648</v>
+        <v>0.63944720687542456</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>0.29385807523497082</v>
+        <v>0.29467613220065653</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>0.34326406778994406</v>
+        <v>0.34408212475562977</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>0.36833041054722698</v>
+        <v>0.36935578736486629</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>0.4251385171234921</v>
+        <v>0.42616389394113141</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>0.45705805000630056</v>
+        <v>0.4583304313122471</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>0.52219833440664409</v>
+        <v>0.52347071571259063</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>0.51689872500454337</v>
+        <v>0.51833769380676509</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>0.58743285613821483</v>
+        <v>0.58887182494043655</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10176,11 +10176,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8690067647050781</v>
+        <v>1.8742098002233574</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.5798742065062914</v>
+        <v>0.58148848963761146</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10586,11 +10586,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>1592628.8800383003</v>
+        <v>1597062.5208290999</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.30723697668325939</v>
+        <v>0.3080922785111605</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1286430.1992714566</v>
+        <v>1290011.4286950177</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.24816762404101345</v>
+        <v>0.2488584856188078</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10620,11 +10620,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>1801.8766387800003</v>
+        <v>1806.8927940599999</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>3.4760334802019126E-4</v>
+        <v>3.4857102379332169E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10637,11 +10637,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2880860.9559485367</v>
+        <v>2888880.8423181777</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>0.55575220407229298</v>
+        <v>0.55729933515376162</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14224,12 +14224,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6250000000000001E-2</v>
+        <v>5.8064516129032254E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.6250000000000001E-2</v>
+        <v>5.8064516129032254E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -15366,50 +15366,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2598692427150741E-2</v>
+        <v>5.2745119326229786E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.8951057475029222E-2</v>
+        <v>3.9059491397979249E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.7631941669641643E-2</v>
+        <v>3.7736703371325404E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.4003625473188301E-2</v>
+        <v>-5.4153963495906586E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3863043378503571E-2</v>
+        <v>1.3901636019499808E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.0232126561444523E-2</v>
+        <v>4.0344126789281121E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.14824564151484373</v>
+        <v>0.14865833522617633</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>8.5582203472513371E-2</v>
+        <v>8.5820451537105241E-2</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>5.8896786751458013E-2</v>
+        <v>5.9060746603914041E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>8.9489632644116593E-2</v>
+        <v>8.973875840757449E-2</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1379404862191252E-2</v>
+        <v>1.1411083424726687E-2</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10958060922323069</v>
+        <v>0.11343036414242963</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.1148036406310881E-2</v>
+        <v>8.3998906232213427E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.8399878478420088E-2</v>
+        <v>8.115420079854925E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.1125075530691423</v>
+        <v>-0.11646013655033674</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.888134037188244E-2</v>
+        <v>2.9895991439784532E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>8.3816930336342757E-2</v>
+        <v>8.6761562987701324E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.30884508648925779</v>
+        <v>0.31969534457242221</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.17829625723440287</v>
+        <v>0.18456011083248439</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12270163906553753</v>
+        <v>0.12701235828798718</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.18643673467524291</v>
+        <v>0.19298657722059029</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>2.370709346289844E-2</v>
+        <v>2.4539964354250939E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20007450171883859</v>
+        <v>0.20652851790331725</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2022391333869</v>
+        <v>0.20876297639938063</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0285619967162845E-2</v>
+        <v>4.1585156095135835E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15101581367107558</v>
+        <v>0.15588729153143285</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12646175281697022</v>
+        <v>0.13054116419816281</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.35363554605345537</v>
+        <v>0.36504314431324425</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22542311823721381</v>
+        <v>0.23269483172873681</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16680122734104363</v>
+        <v>0.17218191209398051</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22892647773414868</v>
+        <v>0.23631120282234702</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5061660147971235E-2</v>
+        <v>2.587010079790579E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-5.8721749294225745E-2</v>
+        <v>-5.8885221868559406E-2</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0924437000000002</v>
+        <v>1.0954849</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>3456384.2067436236</v>
+        <v>3466006.2638341151</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.66677745659750876</v>
+        <v>0.66863366538978253</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.63880271902835151</v>
+        <v>0.64058105033193147</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.66677745659750876</v>
+        <v>0.66863366538978253</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.66677745659750876</v>
+        <v>0.66863366538978253</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.66677745659750876</v>
+        <v>0.66863366538978253</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.66677745659750876</v>
+        <v>0.66863366538978253</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.66677745659750876</v>
+        <v>0.66863366538978253</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.70083153560096079</v>
+        <v>0.70278254585995126</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.64975041709578352</v>
+        <v>0.65155922515469911</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.6667774565975092</v>
+        <v>0.66863366538978297</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.68380449609923522</v>
+        <v>0.68570810562486728</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.58164225908888079</v>
+        <v>0.5832614642143632</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.73385367281642877</v>
+        <v>0.7358966117704171</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.63419191013849574</v>
+        <v>0.63595740563919112</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.6667774565975092</v>
+        <v>0.66863366538978297</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.6999980441568201</v>
+        <v>0.70194673410019159</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.51020013530541619</v>
+        <v>0.51162045623498964</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18884,23 +18884,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.76587513920718608</v>
+        <v>0.76800722113814213</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.61997527907262895</v>
+        <v>0.62170119759704867</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.6667774565975092</v>
+        <v>0.66863366538978297</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.71539890105074744</v>
+        <v>0.71739046467812284</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.45024870275985163</v>
+        <v>0.45150212786069038</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18915,23 +18915,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.79692625813155626</v>
+        <v>0.79914478173714754</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.60698479101244329</v>
+        <v>0.60867454595947346</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.6667774565975092</v>
+        <v>0.66863366538978297</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.73004586984497211</v>
+        <v>0.73207820844454685</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>0.39993980831602111</v>
+        <v>0.40105318097316639</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18946,23 +18946,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.82703643405821858</v>
+        <v>0.82933877989375926</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.5951146946963759</v>
+        <v>0.59677140506919457</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.6667774565975092</v>
+        <v>0.66863366538978297</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.74397585415276646</v>
+        <v>0.74604697174688062</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>0.35772255423728228</v>
+        <v>0.35871840036825114</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18977,23 +18977,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.85623418041134547</v>
+        <v>0.85861780840926127</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.58426835960104162</v>
+        <v>0.58589487539789098</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.6667774565975092</v>
+        <v>0.66863366538978297</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.75722395111682217</v>
+        <v>0.75933194943301574</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>0.32229548787750151</v>
+        <v>0.32319271035014058</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19009,23 +19009,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.88454714657195355</v>
+        <v>0.88700959363641507</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.57435748930413955</v>
+        <v>0.57595641471921732</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.6667774565975092</v>
+        <v>0.66863366538978297</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.76982353983788232</v>
+        <v>0.7719666135261235</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>0.29256648114202094</v>
+        <v>0.29338094250277486</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19040,23 +19040,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.91200214406102786</v>
+        <v>0.91454102173547303</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.56530140269251794</v>
+        <v>0.56687511731586049</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.6667774565975092</v>
+        <v>0.66863366538978297</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.78180636547469484</v>
+        <v>0.78398279755872946</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>0.26761906290245685</v>
+        <v>0.26836407437911136</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19072,23 +19072,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.93862517192922112</v>
+        <v>0.94123816413455941</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.55702637716395009</v>
+        <v>0.55857705535288638</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.6667774565975092</v>
+        <v>0.66863366538978297</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.79320261922718738</v>
+        <v>0.79541077677854999</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>0.24668416647764796</v>
+        <v>0.24737089833128195</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19104,23 +19104,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.96444144137716625</v>
+        <v>0.96712630221852225</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>0.54946504847584132</v>
+        <v>0.55099467705571659</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.6667774565975092</v>
+        <v>0.66863366538978297</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.80404101440438358</v>
+        <v>0.80627934442817006</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>0.22911642122606002</v>
+        <v>0.22975424710233414</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19136,23 +19136,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>1.0822516030010227</v>
+        <v>1.0852644297261405</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>0.52038592642169945</v>
+        <v>0.52183460307151996</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.66677745659750909</v>
+        <v>0.66863366538978286</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.85077544918938086</v>
+        <v>0.85314388089535764</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>0.17559991874773312</v>
+        <v>0.1760887626789083</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19168,23 +19168,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.1832612710811847</v>
+        <v>1.1865552936267967</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>0.50186233622004517</v>
+        <v>0.50325944596301153</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.66677745659750909</v>
+        <v>0.66863366538978286</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.88713774948998414</v>
+        <v>0.88960740840581543</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>0.15333024956124991</v>
+        <v>0.15375709806151189</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19200,23 +19200,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.2698663050190928</v>
+        <v>1.273401423036455</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>0.49006268857869029</v>
+        <v>0.49142694986602747</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.66677745659750909</v>
+        <v>0.66863366538978286</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.91542988331452191</v>
+        <v>0.9179783033027884</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>0.14406323578589636</v>
+        <v>0.1444642863047213</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19232,23 +19232,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.3441208991182811</v>
+        <v>1.3478627308286</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>0.48254623615535297</v>
+        <v>0.4838895727624436</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.66677745659750898</v>
+        <v>0.66863366538978275</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.93744292511133709</v>
+        <v>0.94005262611821583</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>0.14020697983555128</v>
+        <v>0.14059729511411057</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.45024870275985163</v>
+        <v>0.45150212786069038</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.71539890105074744</v>
+        <v>0.71739046467812284</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.6667774565975092</v>
+        <v>0.66863366538978297</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.61997527907262895</v>
+        <v>0.62170119759704867</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.76587513920718608</v>
+        <v>0.76800722113814213</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>0.71539890105074744</v>
+        <v>0.71739046467812284</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>0.6667774565975092</v>
+        <v>0.66863366538978297</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>0.61997527907262895</v>
+        <v>0.62170119759704867</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.66480120110693675</v>
+        <v>0.66665190829926735</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>0.45024870275985163</v>
+        <v>0.45150212786069038</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>0.76587513920718608</v>
+        <v>0.76800722113814213</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>0.48</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15077592809603155</v>
+        <v>0.16461424988614515</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>0.66677745659750876</v>
+        <v>0.66863366538978253</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>2.6319293856835419E-2</v>
+        <v>2.6205277576844425E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.63767202325988648</v>
+        <v>0.63944720687542456</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.63880271902835151</v>
+        <v>0.64058105033193147</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.87153298843376314</v>
+        <v>0.87153298843376326</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20229,11 +20229,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.29385807523497082</v>
+        <v>0.29467613220065653</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>0.34326406778994406</v>
+        <v>0.34408212475562977</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46169181762888001</v>
+        <v>0.46190690794171696</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20254,11 +20254,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.36833041054722698</v>
+        <v>0.36935578736486629</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>0.4251385171234921</v>
+        <v>0.42616389394113141</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33329595526221678</v>
+        <v>0.33354327087684732</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20300,11 +20300,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.45705805000630056</v>
+        <v>0.4583304313122471</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>0.52219833440664409</v>
+        <v>0.52347071571259063</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.18108633379103178</v>
+        <v>0.18136992376515015</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20325,11 +20325,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.51689872500454337</v>
+        <v>0.51833769380676509</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>0.58743285613821483</v>
+        <v>0.58887182494043655</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>7.8785277210125293E-2</v>
+        <v>7.9092349440570753E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>0.48</v>
+        <v>0.46500000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>2488.1831304000002</v>
+        <v>2410.4274075750004</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.15077592809603155</v>
+        <v>0.16461424988614515</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20481,13 +20481,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0924437000000002</v>
+        <v>1.0954849</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>0.63767202325988648</v>
+        <v>0.63944720687542456</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>0.34326406778994406</v>
+        <v>0.34408212475562977</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>0.4251385171234921</v>
+        <v>0.42616389394113141</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20635,7 +20635,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>0.52219833440664409</v>
+        <v>0.52347071571259063</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>0.58743285613821483</v>
+        <v>0.58887182494043655</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20672,22 +20672,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20877,10 +20877,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20896,22 +20896,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10958060922323069</v>
+        <v>0.11343036414242963</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.6250000000000001E-2</v>
+        <v>5.8064516129032254E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21046,22 +21046,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21069,13 +21069,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.30723697668325939</v>
+        <v>-0.3080922785111605</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.24816762404101345</v>
+        <v>0.2488584856188078</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.4760334802019121E-4</v>
+        <v>3.4857102379332164E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-5.8721749294225745E-2</v>
+        <v>-5.8885221868559406E-2</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21224,33 +21224,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21313,23 +21313,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21347,7 +21347,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>0.5798742065062914</v>
+        <v>0.58148848963761146</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>0.66677745659750876</v>
+        <v>0.66863366538978253</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21373,13 +21373,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>0.63767202325988648</v>
+        <v>0.63944720687542456</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21543,13 +21543,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21562,22 +21562,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21642,11 +21642,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>0.29385807523497082</v>
+        <v>0.29467613220065653</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>0.34326406778994406</v>
+        <v>0.34408212475562977</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21663,11 +21663,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>0.36833041054722698</v>
+        <v>0.36935578736486629</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>0.4251385171234921</v>
+        <v>0.42616389394113141</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21703,11 +21703,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>0.45705805000630056</v>
+        <v>0.4583304313122471</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>0.52219833440664409</v>
+        <v>0.52347071571259063</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21724,11 +21724,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>0.51689872500454337</v>
+        <v>0.51833769380676509</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>0.58743285613821483</v>
+        <v>0.58887182494043655</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21746,13 +21746,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21760,13 +21760,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21803,22 +21803,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21842,15 +21842,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21865,12 +21862,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF43B9A1-59AB-414B-8200-46A6B6006EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B13B2A6-038C-45A1-920D-67F0744AD8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.16461424988614515</v>
+        <v>0.16399294422271254</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0954849</v>
+        <v>1.0935677000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>0.63944720687542456</v>
+        <v>0.63832811506044695</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>0.34408212475562977</v>
+        <v>0.34356641424181522</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>0.42616389394113141</v>
+        <v>0.42551748711659565</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>0.52347071571259063</v>
+        <v>0.52266859502346763</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>0.58887182494043655</v>
+        <v>0.58796468598620144</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11343036414242963</v>
+        <v>0.11323185050327873</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.3080922785111605</v>
+        <v>-0.30755308849917445</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.2488584856188078</v>
+        <v>0.24842296022851867</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.4857102379332164E-4</v>
+        <v>3.4796099222938445E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-5.8885221868559406E-2</v>
+        <v>-5.8782167278426403E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.58148848963761146</v>
+        <v>0.58047083094388308</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.66863366538978253</v>
+        <v>0.66746349457018916</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.17668708052046878</v>
+        <v>0.17678152590276955</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.4736225914358805E-3</v>
+        <v>1.5420795298620464E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.6205277576844144E-2</v>
+        <v>2.6277080623039323E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.2461827477559897E-2</v>
+        <v>5.2537296153108114E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-2.1881103429389998E-2</v>
+        <v>-2.181571272471805E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.63944720687542456</v>
+        <v>0.63832811506044695</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>0.29467613220065653</v>
+        <v>0.29416042168684198</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>0.34408212475562977</v>
+        <v>0.34356641424181522</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>0.36935578736486629</v>
+        <v>0.36870938054033053</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>0.42616389394113141</v>
+        <v>0.42551748711659565</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>0.4583304313122471</v>
+        <v>0.4575283106231241</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>0.52347071571259063</v>
+        <v>0.52266859502346763</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>0.51833769380676509</v>
+        <v>0.51743055485252998</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>0.58887182494043655</v>
+        <v>0.58796468598620144</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10176,11 +10176,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8742098002233574</v>
+        <v>1.8709297595500558</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.58148848963761146</v>
+        <v>0.58047083094388308</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10586,11 +10586,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>1597062.5208290999</v>
+        <v>1594267.5135543002</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.3080922785111605</v>
+        <v>0.3075530884991744</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1290011.4286950177</v>
+        <v>1287753.7892596463</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.2488584856188078</v>
+        <v>0.24842296022851867</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10620,11 +10620,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>1806.8927940599999</v>
+        <v>1803.73056438</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>3.4857102379332169E-4</v>
+        <v>3.4796099222938451E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10637,11 +10637,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2888880.8423181777</v>
+        <v>2883825.0333783263</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>0.55729933515376162</v>
+        <v>0.55632400971992235</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15366,50 +15366,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2745119326229786E-2</v>
+        <v>5.265281048402462E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.9059491397979249E-2</v>
+        <v>3.8991133671726519E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.7736703371325404E-2</v>
+        <v>3.7670660646589076E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.4153963495906586E-2</v>
+        <v>-5.4059189045967251E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3901636019499808E-2</v>
+        <v>1.3877306869388673E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.0344126789281121E-2</v>
+        <v>4.0273520832156198E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.14865833522617633</v>
+        <v>0.14839816937606229</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>8.5820451537105241E-2</v>
+        <v>8.5670257801265595E-2</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>5.9060746603914041E-2</v>
+        <v>5.8957384829243287E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>8.973875840757449E-2</v>
+        <v>8.9581707271936761E-2</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1411083424726687E-2</v>
+        <v>1.1391112972243149E-2</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11343036414242963</v>
+        <v>0.11323185050327873</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.3998906232213427E-2</v>
+        <v>8.3851900369304344E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.115420079854925E-2</v>
+        <v>8.1012173433524889E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.11646013655033674</v>
+        <v>-0.11625632052896183</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.9895991439784532E-2</v>
+        <v>2.9843670686857358E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>8.6761562987701324E-2</v>
+        <v>8.6609722219690738E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.31969534457242221</v>
+        <v>0.31913584812056406</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.18456011083248439</v>
+        <v>0.18423711355110881</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12701235828798718</v>
+        <v>0.12679007490159847</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.19298657722059029</v>
+        <v>0.19264883284287473</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>2.4539964354250939E-2</v>
+        <v>2.4497017144608921E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-5.8885221868559406E-2</v>
+        <v>-5.8782167278426403E-2</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0954849</v>
+        <v>1.0935677000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>3466006.2638341151</v>
+        <v>3459940.4319737013</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.66863366538978253</v>
+        <v>0.66746349457018916</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.64058105033193147</v>
+        <v>0.6394599741859287</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.66863366538978253</v>
+        <v>0.66746349457018916</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.66863366538978253</v>
+        <v>0.66746349457018916</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.66863366538978253</v>
+        <v>0.66746349457018916</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.66863366538978253</v>
+        <v>0.66746349457018916</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.66863366538978253</v>
+        <v>0.66746349457018916</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.70278254585995126</v>
+        <v>0.70155261133787561</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.65155922515469911</v>
+        <v>0.65041893618634683</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.66863366538978297</v>
+        <v>0.66746349457018961</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.68570810562486728</v>
+        <v>0.68450805295403283</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.5832614642143632</v>
+        <v>0.58224070265097549</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.7358966117704171</v>
+        <v>0.73460872456714654</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.63595740563919112</v>
+        <v>0.63484442129947871</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.66863366538978297</v>
+        <v>0.66746349457018961</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.70194673410019159</v>
+        <v>0.70071826232607881</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.51162045623498964</v>
+        <v>0.51072507306841775</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18884,23 +18884,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.76800722113814213</v>
+        <v>0.76666313739553105</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.62170119759704867</v>
+        <v>0.62061316294131497</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.66863366538978297</v>
+        <v>0.66746349457018961</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.71739046467812284</v>
+        <v>0.71613496494564743</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.45150212786069038</v>
+        <v>0.45071195733480324</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18915,23 +18915,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.79914478173714754</v>
+        <v>0.79774620438063049</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.60867454595947346</v>
+        <v>0.60760930915017242</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.66863366538978297</v>
+        <v>0.66746349457018961</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.73207820844454685</v>
+        <v>0.73079700380062185</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>0.40105318097316639</v>
+        <v>0.40035130077512648</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18946,23 +18946,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.82933877989375926</v>
+        <v>0.82788736024496978</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.59677140506919457</v>
+        <v>0.59572699985849875</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.66863366538978297</v>
+        <v>0.66746349457018961</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.74604697174688062</v>
+        <v>0.74474132047388453</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>0.35871840036825114</v>
+        <v>0.35809060995581737</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18977,23 +18977,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.85861780840926127</v>
+        <v>0.85711514774978337</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.58589487539789098</v>
+        <v>0.58486950512111879</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.66863366538978297</v>
+        <v>0.66746349457018961</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.75933194943301574</v>
+        <v>0.75800304821908493</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>0.32319271035014058</v>
+        <v>0.32262709318436927</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19009,23 +19009,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.88700959363641507</v>
+        <v>0.88545724472414833</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.57595641471921732</v>
+        <v>0.57494843766878101</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.66863366538978297</v>
+        <v>0.66746349457018961</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.7719666135261235</v>
+        <v>0.77061560048025479</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>0.29338094250277486</v>
+        <v>0.29286749869084622</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19040,23 +19040,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.91454102173547303</v>
+        <v>0.91294049027504742</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.56687511731586049</v>
+        <v>0.56588303337666801</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.66863366538978297</v>
+        <v>0.66746349457018961</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.78398279755872946</v>
+        <v>0.78261075507829048</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>0.26836407437911136</v>
+        <v>0.26789441240257511</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19072,23 +19072,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.94123816413455941</v>
+        <v>0.93959091020319208</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.55857705535288638</v>
+        <v>0.55759949379040163</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.66863366538978297</v>
+        <v>0.66746349457018961</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.79541077677854999</v>
+        <v>0.79401873427642178</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>0.24737089833128195</v>
+        <v>0.24693797635647363</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19104,23 +19104,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.96712630221852225</v>
+        <v>0.96543374164866569</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>0.55099467705571659</v>
+        <v>0.55003038535726312</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.66863366538978297</v>
+        <v>0.66746349457018961</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.80627934442817006</v>
+        <v>0.80486828092639329</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>0.22975424710233414</v>
+        <v>0.22935215589820657</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19136,23 +19136,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>1.0852644297261405</v>
+        <v>1.0833651164953777</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>0.52183460307151996</v>
+        <v>0.52092134420231184</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.66863366538978286</v>
+        <v>0.6674634945701895</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.85314388089535764</v>
+        <v>0.85165080011583028</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>0.1760887626789083</v>
+        <v>0.1757805910411176</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19168,23 +19168,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.1865552936267967</v>
+        <v>1.1844787120062366</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>0.50325944596301153</v>
+        <v>0.5023786953385162</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.66863366538978286</v>
+        <v>0.6674634945701895</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.88960740840581543</v>
+        <v>0.88805051307718474</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>0.15375709806151189</v>
+        <v>0.15348800890436923</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19200,23 +19200,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.273401423036455</v>
+        <v>1.2711728526488162</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>0.49142694986602747</v>
+        <v>0.4905669072052084</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.66863366538978286</v>
+        <v>0.6674634945701895</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.9179783033027884</v>
+        <v>0.9163717562813809</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>0.1444642863047213</v>
+        <v>0.14421146042852401</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19232,23 +19232,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.3478627308286</v>
+        <v>1.3455038462583568</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>0.4838895727624436</v>
+        <v>0.48304272120940067</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.66863366538978275</v>
+        <v>0.66746349457018939</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.94005262611821583</v>
+        <v>0.9384074469881396</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>0.14059729511411057</v>
+        <v>0.14035123683052056</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.45150212786069038</v>
+        <v>0.45071195733480324</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.71739046467812284</v>
+        <v>0.71613496494564743</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.66863366538978297</v>
+        <v>0.66746349457018961</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.62170119759704867</v>
+        <v>0.62061316294131497</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.76800722113814213</v>
+        <v>0.76666313739553105</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>0.71739046467812284</v>
+        <v>0.71613496494564743</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>0.66863366538978297</v>
+        <v>0.66746349457018961</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>0.62170119759704867</v>
+        <v>0.62061316294131497</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.66665190829926735</v>
+        <v>0.66548520573806247</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>0.45150212786069038</v>
+        <v>0.45071195733480324</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>0.76800722113814213</v>
+        <v>0.76666313739553105</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16461424988614515</v>
+        <v>0.16399294422271254</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>0.66863366538978253</v>
+        <v>0.66746349457018916</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>2.6205277576844425E-2</v>
+        <v>2.6277080623039458E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.63944720687542456</v>
+        <v>0.63832811506044695</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.64058105033193147</v>
+        <v>0.6394599741859287</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.87153298843376326</v>
+        <v>0.87153298843376314</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20229,11 +20229,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.29467613220065653</v>
+        <v>0.29416042168684198</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>0.34408212475562977</v>
+        <v>0.34356641424181522</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46190690794171696</v>
+        <v>0.46177145243041517</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20254,11 +20254,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.36935578736486629</v>
+        <v>0.36870938054033053</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>0.42616389394113141</v>
+        <v>0.42551748711659565</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33354327087684732</v>
+        <v>0.33338752112414638</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20300,11 +20300,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.4583304313122471</v>
+        <v>0.4575283106231241</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>0.52347071571259063</v>
+        <v>0.52266859502346763</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.18136992376515015</v>
+        <v>0.18119132983203612</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20325,11 +20325,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.51833769380676509</v>
+        <v>0.51743055485252998</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>0.58887182494043655</v>
+        <v>0.58796468598620144</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>7.9092349440570753E-2</v>
+        <v>7.8898967295959244E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20473,7 +20473,7 @@
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.16461424988614515</v>
+        <v>0.16399294422271254</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20481,13 +20481,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0954849</v>
+        <v>1.0935677000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>0.63944720687542456</v>
+        <v>0.63832811506044695</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>0.34408212475562977</v>
+        <v>0.34356641424181522</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>0.42616389394113141</v>
+        <v>0.42551748711659565</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20635,7 +20635,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>0.52347071571259063</v>
+        <v>0.52266859502346763</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>0.58887182494043655</v>
+        <v>0.58796468598620144</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20672,22 +20672,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20877,10 +20877,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20896,22 +20896,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.11343036414242963</v>
+        <v>0.11323185050327873</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -21046,22 +21046,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21069,13 +21069,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.3080922785111605</v>
+        <v>-0.30755308849917445</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.2488584856188078</v>
+        <v>0.24842296022851867</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.4857102379332164E-4</v>
+        <v>3.4796099222938445E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-5.8885221868559406E-2</v>
+        <v>-5.8782167278426403E-2</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21224,33 +21224,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21313,23 +21313,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21347,7 +21347,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>0.58148848963761146</v>
+        <v>0.58047083094388308</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>0.66863366538978253</v>
+        <v>0.66746349457018916</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21373,13 +21373,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>0.63944720687542456</v>
+        <v>0.63832811506044695</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21543,13 +21543,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21562,22 +21562,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21642,11 +21642,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>0.29467613220065653</v>
+        <v>0.29416042168684198</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>0.34408212475562977</v>
+        <v>0.34356641424181522</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21663,11 +21663,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>0.36935578736486629</v>
+        <v>0.36870938054033053</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>0.42616389394113141</v>
+        <v>0.42551748711659565</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21703,11 +21703,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>0.4583304313122471</v>
+        <v>0.4575283106231241</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>0.52347071571259063</v>
+        <v>0.52266859502346763</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21724,11 +21724,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>0.51833769380676509</v>
+        <v>0.51743055485252998</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>0.58887182494043655</v>
+        <v>0.58796468598620144</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21746,13 +21746,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21760,13 +21760,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21803,22 +21803,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21842,12 +21842,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21862,15 +21865,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B13B2A6-038C-45A1-920D-67F0744AD8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128E2A19-E02D-4210-B939-DAAB2B58C8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>0.46500000000000002</v>
+        <v>0.46</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>2410.4274075750004</v>
+        <v>2384.5088333000003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.16399294422271254</v>
+        <v>0.16883903788744581</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0935677000000001</v>
+        <v>1.0948992599999998</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>0.63832811506044695</v>
+        <v>0.63910536203371593</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>0.34356641424181522</v>
+        <v>0.34392459257051061</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>0.42551748711659565</v>
+        <v>0.42596643843689541</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>0.52266859502346763</v>
+        <v>0.52322569486949744</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>0.58796468598620144</v>
+        <v>0.58859472455593909</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11323185050327873</v>
+        <v>0.11460200453321724</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.8064516129032254E-2</v>
+        <v>5.8695652173913038E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.30755308849917445</v>
+        <v>-0.30792757413049093</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.24842296022851867</v>
+        <v>0.24872544728709015</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.4796099222938445E-4</v>
+        <v>3.4838467970553511E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-5.8782167278426403E-2</v>
+        <v>-5.8853742163695273E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.58047083094388308</v>
+        <v>0.58117762919665827</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.66746349457018916</v>
+        <v>0.66827621763326939</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.17678152590276955</v>
+        <v>0.17671589519605213</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.5420795298620464E-3</v>
+        <v>1.4945084730719894E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.6277080623039323E-2</v>
+        <v>2.6227184324110104E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.2537296153108114E-2</v>
+        <v>5.2484852571973169E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-2.181571272471805E-2</v>
+        <v>-2.1861153027630236E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.63832811506044695</v>
+        <v>0.63910536203371593</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>0.29416042168684198</v>
+        <v>0.29451860001553737</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>0.34356641424181522</v>
+        <v>0.34392459257051061</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>0.36870938054033053</v>
+        <v>0.3691583318606303</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>0.42551748711659565</v>
+        <v>0.42596643843689541</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>0.4575283106231241</v>
+        <v>0.45808541046915391</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>0.52266859502346763</v>
+        <v>0.52322569486949744</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>0.51743055485252998</v>
+        <v>0.51806059342226762</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>0.58796468598620144</v>
+        <v>0.58859472455593909</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -10176,11 +10176,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8709297595500558</v>
+        <v>1.8732078583185414</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.58047083094388308</v>
+        <v>0.58117762919665827</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10586,11 +10586,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>1594267.5135543002</v>
+        <v>1596208.7402843398</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.3075530884991744</v>
+        <v>0.30792757413049093</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1287753.7892596463</v>
+        <v>1289321.7959186088</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.24842296022851867</v>
+        <v>0.24872544728709015</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10620,11 +10620,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>1803.73056438</v>
+        <v>1805.9268394439996</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>3.4796099222938451E-4</v>
+        <v>3.4838467970553516E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10637,11 +10637,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2883825.0333783263</v>
+        <v>2887336.4630423924</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>0.55632400971992235</v>
+        <v>0.55700140609728666</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14224,12 +14224,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8064516129032254E-2</v>
+        <v>5.8695652173913038E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.8064516129032254E-2</v>
+        <v>5.8695652173913038E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -15366,50 +15366,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.265281048402462E-2</v>
+        <v>5.2716922085279935E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.8991133671726519E-2</v>
+        <v>3.9038610415920695E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.7670660646589076E-2</v>
+        <v>3.7716529544226197E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.4059189045967251E-2</v>
+        <v>-5.4125013094872526E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3877306869388673E-2</v>
+        <v>1.3894204283910881E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.0273520832156198E-2</v>
+        <v>4.0322559048445186E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.14839816937606229</v>
+        <v>0.14857886332524745</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>8.5670257801265595E-2</v>
+        <v>8.5774572411579916E-2</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>5.8957384829243287E-2</v>
+        <v>5.9029173064524196E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>8.9581707271936761E-2</v>
+        <v>8.9690784577470734E-2</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1391112972243149E-2</v>
+        <v>1.1404983124396797E-2</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11323185050327873</v>
+        <v>0.11460200453321724</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.3851900369304344E-2</v>
+        <v>8.4866544382436293E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.1012173433524889E-2</v>
+        <v>8.1992455530926517E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.11625632052896183</v>
+        <v>-0.11766307194537505</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.9843670686857358E-2</v>
+        <v>3.0204791921545394E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>8.6609722219690738E-2</v>
+        <v>8.7657737061837354E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.31913584812056406</v>
+        <v>0.32299752896792921</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.18423711355110881</v>
+        <v>0.18646646176430415</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12679007490159847</v>
+        <v>0.12832428927070477</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.19264883284287473</v>
+        <v>0.19497996647276244</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>2.4497017144608921E-2</v>
+        <v>2.4793441574775647E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20652851790331725</v>
+        <v>0.20877339309791851</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20876297639938063</v>
+        <v>0.21103213918633043</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.1585156095135835E-2</v>
+        <v>4.2037168661387313E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15588729153143285</v>
+        <v>0.15758171861329626</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13054116419816281</v>
+        <v>0.13196008989596891</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.36504314431324425</v>
+        <v>0.36901100457751862</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23269483172873681</v>
+        <v>0.23522412337796222</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17218191209398051</v>
+        <v>0.17405345461674115</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23631120282234702</v>
+        <v>0.23887980285302471</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.587010079790579E-2</v>
+        <v>2.6151297545709114E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-5.8782167278426403E-2</v>
+        <v>-5.8853742163695273E-2</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0935677000000001</v>
+        <v>1.0948992599999998</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>3459940.4319737013</v>
+        <v>3464153.3565887916</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.66746349457018916</v>
+        <v>0.66827621763326939</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.6394599741859287</v>
+        <v>0.64023859934395666</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.66746349457018916</v>
+        <v>0.66827621763326939</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.66746349457018916</v>
+        <v>0.66827621763326939</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.66746349457018916</v>
+        <v>0.66827621763326939</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.66746349457018916</v>
+        <v>0.66827621763326939</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.66746349457018916</v>
+        <v>0.66827621763326939</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.70155261133787561</v>
+        <v>0.70240684230606609</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.65041893618634683</v>
+        <v>0.65121090529687198</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.66746349457018961</v>
+        <v>0.66827621763326994</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.68450805295403283</v>
+        <v>0.68534152996966813</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.58224070265097549</v>
+        <v>0.58294965595128023</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.73460872456714654</v>
+        <v>0.73550320562514082</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.63484442129947871</v>
+        <v>0.63561742642538488</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.66746349457018961</v>
+        <v>0.66827621763326994</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.70071826232607881</v>
+        <v>0.70157147736652181</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.51072507306841775</v>
+        <v>0.51134694684751247</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18884,23 +18884,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.76666313739553105</v>
+        <v>0.7675966488436381</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.62061316294131497</v>
+        <v>0.62136883967101897</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.66746349457018961</v>
+        <v>0.66827621763326994</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.71613496494564743</v>
+        <v>0.71700695181387952</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.45071195733480324</v>
+        <v>0.45126075738980537</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18915,23 +18915,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.79774620438063049</v>
+        <v>0.79871756347975609</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.60760930915017242</v>
+        <v>0.60834915200735618</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.66746349457018961</v>
+        <v>0.66827621763326994</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.73079700380062185</v>
+        <v>0.73168684359598202</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>0.40035130077512648</v>
+        <v>0.40083878022249864</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18946,23 +18946,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.82788736024496978</v>
+        <v>0.82889542009659811</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.59572699985849875</v>
+        <v>0.59645237446853105</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.66746349457018961</v>
+        <v>0.66827621763326994</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.74474132047388453</v>
+        <v>0.74564813927686302</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>0.35809060995581737</v>
+        <v>0.35852663155063286</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18977,23 +18977,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.85711514774978337</v>
+        <v>0.85815879620989921</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.58486950512111879</v>
+        <v>0.58558165932815964</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.66746349457018961</v>
+        <v>0.66827621763326994</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.75800304821908493</v>
+        <v>0.75892601488944866</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>0.32262709318436927</v>
+        <v>0.32301993336445184</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19009,23 +19009,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.88545724472414833</v>
+        <v>0.88653540335007031</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.57494843766878101</v>
+        <v>0.57564851169406728</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.66746349457018961</v>
+        <v>0.66827621763326994</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.77061560048025479</v>
+        <v>0.77155392456295702</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>0.29286749869084622</v>
+        <v>0.29322410271870541</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19040,23 +19040,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.91294049027504742</v>
+        <v>0.91405211330417524</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.56588303337666801</v>
+        <v>0.56657206910067737</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.66746349457018961</v>
+        <v>0.66827621763326994</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.78261075507829048</v>
+        <v>0.78356368481188787</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>0.26789441240257511</v>
+        <v>0.26822060847052653</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19072,23 +19072,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.93959091020319208</v>
+        <v>0.94073498356270135</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.55759949379040163</v>
+        <v>0.55827844323445652</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.66746349457018961</v>
+        <v>0.66827621763326994</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.79401873427642178</v>
+        <v>0.79498555469898258</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>0.24693797635647363</v>
+        <v>0.24723865525527169</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19104,23 +19104,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.96543374164866569</v>
+        <v>0.96660928199521157</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>0.55003038535726312</v>
+        <v>0.55070011843362054</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.66746349457018961</v>
+        <v>0.66827621763326994</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.80486828092639329</v>
+        <v>0.80584831207412211</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>0.22935215589820657</v>
+        <v>0.22963142178792492</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19136,23 +19136,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>1.0833651164953777</v>
+        <v>1.084684253531448</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>0.52092134420231184</v>
+        <v>0.52155563325920873</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.6674634945701895</v>
+        <v>0.66827621763326983</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.85165080011583028</v>
+        <v>0.8526877950265267</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>0.1757805910411176</v>
+        <v>0.17599462662739787</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19168,23 +19168,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.1844787120062366</v>
+        <v>1.1859209679120746</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>0.5023786953385162</v>
+        <v>0.50299040632409564</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.6674634945701895</v>
+        <v>0.66827621763326983</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.88805051307718474</v>
+        <v>0.88913182934246282</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>0.15348800890436923</v>
+        <v>0.15367490039095633</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19200,23 +19200,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.2711728526488162</v>
+        <v>1.2727206698746474</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>0.4905669072052084</v>
+        <v>0.49116423581226037</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.6674634945701895</v>
+        <v>0.66827621763326983</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.9163717562813809</v>
+        <v>0.91748755732030485</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>0.14421146042852401</v>
+        <v>0.14438705651850378</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19232,23 +19232,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.3455038462583568</v>
+        <v>1.3471421710749396</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>0.48304272120940067</v>
+        <v>0.48363088814762811</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.66746349457018939</v>
+        <v>0.66827621763326972</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.9384074469881396</v>
+        <v>0.93955007932824186</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>0.14035123683052056</v>
+        <v>0.14052213259940072</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.45071195733480324</v>
+        <v>0.45126075738980537</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.71613496494564743</v>
+        <v>0.71700695181387952</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.66746349457018961</v>
+        <v>0.66827621763326994</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.62061316294131497</v>
+        <v>0.62136883967101897</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.76666313739553105</v>
+        <v>0.7675966488436381</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>0.71613496494564743</v>
+        <v>0.71700695181387952</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>0.66746349457018961</v>
+        <v>0.66827621763326994</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>0.62061316294131497</v>
+        <v>0.62136883967101897</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.66548520573806247</v>
+        <v>0.66629551997882908</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>0.45071195733480324</v>
+        <v>0.45126075738980537</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>0.76666313739553105</v>
+        <v>0.7675966488436381</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>0.46500000000000002</v>
+        <v>0.46</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16399294422271254</v>
+        <v>0.16883903788744581</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>0.66746349457018916</v>
+        <v>0.66827621763326939</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>2.6277080623039458E-2</v>
+        <v>2.6227184324110333E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.63832811506044695</v>
+        <v>0.63910536203371593</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.6394599741859287</v>
+        <v>0.64023859934395666</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.87153298843376314</v>
+        <v>0.87153298843376326</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20229,11 +20229,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.29416042168684198</v>
+        <v>0.29451860001553737</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>0.34356641424181522</v>
+        <v>0.34392459257051061</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46177145243041517</v>
+        <v>0.4618655811678718</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20254,11 +20254,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.36870938054033053</v>
+        <v>0.3691583318606303</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>0.42551748711659565</v>
+        <v>0.42596643843689541</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33338752112414638</v>
+        <v>0.33349575243522434</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20300,11 +20300,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.4575283106231241</v>
+        <v>0.45808541046915391</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>0.52266859502346763</v>
+        <v>0.52322569486949744</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.18119132983203612</v>
+        <v>0.18131543568258357</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20325,11 +20325,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.51743055485252998</v>
+        <v>0.51806059342226762</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>0.58796468598620144</v>
+        <v>0.58859472455593909</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>7.8898967295959244E-2</v>
+        <v>7.9033349551387633E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>0.46500000000000002</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>2410.4274075750004</v>
+        <v>2384.5088333000003</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.16399294422271254</v>
+        <v>0.16883903788744581</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0935677000000001</v>
+        <v>1.0948992599999998</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>0.63832811506044695</v>
+        <v>0.63910536203371593</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>0.34356641424181522</v>
+        <v>0.34392459257051061</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>0.42551748711659565</v>
+        <v>0.42596643843689541</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20635,7 +20635,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>0.52266859502346763</v>
+        <v>0.52322569486949744</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>0.58796468598620144</v>
+        <v>0.58859472455593909</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.11323185050327873</v>
+        <v>0.11460200453321724</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.8064516129032254E-2</v>
+        <v>5.8695652173913038E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.30755308849917445</v>
+        <v>-0.30792757413049093</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.24842296022851867</v>
+        <v>0.24872544728709015</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.4796099222938445E-4</v>
+        <v>3.4838467970553511E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-5.8782167278426403E-2</v>
+        <v>-5.8853742163695273E-2</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21347,7 +21347,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>0.58047083094388308</v>
+        <v>0.58117762919665827</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>0.66746349457018916</v>
+        <v>0.66827621763326939</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>0.63832811506044695</v>
+        <v>0.63910536203371593</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21642,11 +21642,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>0.29416042168684198</v>
+        <v>0.29451860001553737</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>0.34356641424181522</v>
+        <v>0.34392459257051061</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21663,11 +21663,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>0.36870938054033053</v>
+        <v>0.3691583318606303</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>0.42551748711659565</v>
+        <v>0.42596643843689541</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21703,11 +21703,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>0.4575283106231241</v>
+        <v>0.45808541046915391</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>0.52266859502346763</v>
+        <v>0.52322569486949744</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21724,11 +21724,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>0.51743055485252998</v>
+        <v>0.51806059342226762</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>0.58796468598620144</v>
+        <v>0.58859472455593909</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128E2A19-E02D-4210-B939-DAAB2B58C8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD831AC5-2E4A-4436-9379-E405BF330E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>2384.5088333000003</v>
+        <v>2332.6716847500002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.16883903788744581</v>
+        <v>0.17996939953838226</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0948992599999998</v>
+        <v>1.1013227999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>0.63910536203371593</v>
+        <v>0.64285485662853192</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>0.34392459257051061</v>
+        <v>0.34565247026397422</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>0.42596643843689541</v>
+        <v>0.42813221148805264</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>0.52322569486949744</v>
+        <v>0.52591318408888466</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>0.58859472455593909</v>
+        <v>0.59163407535819612</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11460200453321724</v>
+        <v>0.11783600222796822</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.8695652173913038E-2</v>
+        <v>0.06</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.30792757413049093</v>
+        <v>-0.30973411940985324</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.24872544728709015</v>
+        <v>0.25018466633859132</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.4838467970553511E-4</v>
+        <v>3.50428578178419E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-5.8853742163695273E-2</v>
+        <v>-5.9199024493083445E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.58117762919665827</v>
+        <v>0.58458727416093559</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.66827621763326939</v>
+        <v>0.67219685140465046</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.17671589519605213</v>
+        <v>0.1764015250562416</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.4945084730719894E-3</v>
+        <v>1.2666367030415219E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.6227184324110104E-2</v>
+        <v>2.5988175323388856E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>0.62 HKD</v>
+        <v>0.63 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.2484852571973169E-2</v>
+        <v>5.2233642926730453E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-2.1861153027630236E-2</v>
+        <v>-2.2078819036575568E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.63910536203371593</v>
+        <v>0.64285485662853192</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>0.29451860001553737</v>
+        <v>0.29624647770900098</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>0.34392459257051061</v>
+        <v>0.34565247026397422</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>0.3691583318606303</v>
+        <v>0.37132410491178752</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>0.42596643843689541</v>
+        <v>0.42813221148805264</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>0.45808541046915391</v>
+        <v>0.46077289968854113</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>0.52322569486949744</v>
+        <v>0.52591318408888466</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>0.51806059342226762</v>
+        <v>0.52109994422452466</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>0.58859472455593909</v>
+        <v>0.59163407535819612</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10176,11 +10176,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8732078583185414</v>
+        <v>1.8841975685556493</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.58117762919665827</v>
+        <v>0.58458727416093559</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10586,11 +10586,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>1596208.7402843398</v>
+        <v>1605573.3558852</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.30792757413049093</v>
+        <v>0.30973411940985324</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1289321.7959186088</v>
+        <v>1296885.9713925745</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.24872544728709015</v>
+        <v>0.25018466633859138</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10620,11 +10620,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>1805.9268394439996</v>
+        <v>1816.5218263199997</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>3.4838467970553516E-4</v>
+        <v>3.5042857817841905E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10637,11 +10637,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2887336.4630423924</v>
+        <v>2904275.8491040943</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>0.55700140609728666</v>
+        <v>0.56026921432662313</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14224,12 +14224,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8695652173913038E-2</v>
+        <v>0.06</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.8695652173913038E-2</v>
+        <v>0.06</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -15366,50 +15366,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2716922085279935E-2</v>
+        <v>5.3026201002585704E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.9038610415920695E-2</v>
+        <v>3.9267641601448293E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.7716529544226197E-2</v>
+        <v>3.7937804363782218E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.4125013094872526E-2</v>
+        <v>-5.4442552981250246E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3894204283910881E-2</v>
+        <v>1.3975718611526624E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.0322559048445186E-2</v>
+        <v>4.0559122886245254E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.14857886332524745</v>
+        <v>0.14945054376799821</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>8.5774572411579916E-2</v>
+        <v>8.627779349958091E-2</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>5.9029173064524196E-2</v>
+        <v>5.9375484609521405E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>8.9690784577470734E-2</v>
+        <v>9.0216981245431566E-2</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1404983124396797E-2</v>
+        <v>1.1471893723367236E-2</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11460200453321724</v>
+        <v>0.11783600222796822</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.4866544382436293E-2</v>
+        <v>8.7261425780996202E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.1992455530926517E-2</v>
+        <v>8.4306231919516042E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.11766307194537505</v>
+        <v>-0.12098345106944498</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.0204791921545394E-2</v>
+        <v>3.1057152470059163E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>8.7657737061837354E-2</v>
+        <v>9.0131384191656116E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.32299752896792921</v>
+        <v>0.33211231948444048</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.18646646176430415</v>
+        <v>0.19172842999906869</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12832428927070477</v>
+        <v>0.131945521354492</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.19497996647276244</v>
+        <v>0.20048218054540348</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>2.4793441574775647E-2</v>
+        <v>2.5493097163038301E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20877339309791851</v>
+        <v>0.21341280183342784</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21103213918633043</v>
+        <v>0.21572174227936</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2037168661387313E-2</v>
+        <v>4.2971327964973702E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15758171861329626</v>
+        <v>0.16108353458248065</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13196008989596891</v>
+        <v>0.13489253633810158</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.36901100457751862</v>
+        <v>0.37721124912368575</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23522412337796222</v>
+        <v>0.24045132611969475</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17405345461674115</v>
+        <v>0.17792130916377988</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23887980285302471</v>
+        <v>0.24418824291642527</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6151297545709114E-2</v>
+        <v>2.6732437491169318E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-5.8853742163695273E-2</v>
+        <v>-5.9199024493083445E-2</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0948992599999998</v>
+        <v>1.1013227999999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>3464153.3565887916</v>
+        <v>3484476.804110514</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.66827621763326939</v>
+        <v>0.67219685140465046</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.64023859934395666</v>
+        <v>0.64399474239992138</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.66827621763326939</v>
+        <v>0.67219685140465046</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.66827621763326939</v>
+        <v>0.67219685140465046</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.66827621763326939</v>
+        <v>0.67219685140465046</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.66827621763326939</v>
+        <v>0.67219685140465046</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.66827621763326939</v>
+        <v>0.67219685140465046</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.70240684230606609</v>
+        <v>0.70652771315935969</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.65121090529687198</v>
+        <v>0.65503142052729668</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827621763326994</v>
+        <v>0.67219685140465091</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.68534152996966813</v>
+        <v>0.68936228228200547</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.58294965595128023</v>
+        <v>0.58636969701787978</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.73550320562514082</v>
+        <v>0.73981824576998612</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.63561742642538488</v>
+        <v>0.63934645804729007</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827621763326994</v>
+        <v>0.67219685140465091</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.70157147736652181</v>
+        <v>0.70568744731221622</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.51134694684751247</v>
+        <v>0.51434691011988953</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18884,23 +18884,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.7675966488436381</v>
+        <v>0.7720999743621092</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.62136883967101897</v>
+        <v>0.62501427787907882</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827621763326994</v>
+        <v>0.67219685140465091</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.71700695181387952</v>
+        <v>0.72121347838989958</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.45126075738980537</v>
+        <v>0.45390820782787011</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18915,23 +18915,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.79871756347975609</v>
+        <v>0.80340346875447044</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.60834915200735618</v>
+        <v>0.61191820648994422</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827621763326994</v>
+        <v>0.67219685140465091</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.73168684359598202</v>
+        <v>0.73597949396028373</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>0.40083878022249864</v>
+        <v>0.40319041569470676</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18946,23 +18946,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.82889542009659811</v>
+        <v>0.83375837240766959</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.59645237446853105</v>
+        <v>0.59995163309940613</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827621763326994</v>
+        <v>0.67219685140465091</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.74564813927686302</v>
+        <v>0.75002269757967033</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>0.35852663155063286</v>
+        <v>0.36063003068785648</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18977,23 +18977,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.85815879620989921</v>
+        <v>0.86319343049561992</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.58558165932815964</v>
+        <v>0.58901714179616393</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827621763326994</v>
+        <v>0.67219685140465091</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.75892601488944866</v>
+        <v>0.76337847165125439</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>0.32301993336445184</v>
+        <v>0.32491502229049962</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19009,23 +19009,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.88653540335007031</v>
+        <v>0.89173651712635993</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.57564851169406728</v>
+        <v>0.57902571850742046</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827621763326994</v>
+        <v>0.67219685140465091</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.77155392456295702</v>
+        <v>0.77608046657248142</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>0.29322410271870541</v>
+        <v>0.29494438587313709</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19040,23 +19040,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.91405211330417524</v>
+        <v>0.91941466173798647</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.56657206910067737</v>
+        <v>0.56989602636479231</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827621763326994</v>
+        <v>0.67219685140465091</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.78356368481188787</v>
+        <v>0.78816068551854346</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>0.26822060847052653</v>
+        <v>0.26979420146695876</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19072,23 +19072,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.94073498356270135</v>
+        <v>0.94625407469471512</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.55827844323445652</v>
+        <v>0.56155374356779886</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827621763326994</v>
+        <v>0.67219685140465091</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.79498555469898258</v>
+        <v>0.799649565075637</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>0.24723865525527169</v>
+        <v>0.24868915161562039</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19104,23 +19104,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.96660928199521157</v>
+        <v>0.97228017210730067</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>0.55070011843362054</v>
+        <v>0.55393095835469519</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827621763326994</v>
+        <v>0.67219685140465091</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.80584831207412211</v>
+        <v>0.810576051927139</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>0.22963142178792492</v>
+        <v>0.23097862027183988</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19136,23 +19136,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>1.084684253531448</v>
+        <v>1.0910478642712429</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>0.52155563325920873</v>
+        <v>0.52461548871336794</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827621763326983</v>
+        <v>0.6721968514046508</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.8526877950265267</v>
+        <v>0.8576903321173498</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>0.17599462662739787</v>
+        <v>0.17702714949523338</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19168,23 +19168,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.1859209679120746</v>
+        <v>1.1928785128228476</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>0.50299040632409564</v>
+        <v>0.50594134355885012</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827621763326983</v>
+        <v>0.6721968514046508</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.88913182934246282</v>
+        <v>0.89434817579524484</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>0.15367490039095633</v>
+        <v>0.1545764781942488</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19200,23 +19200,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.2727206698746474</v>
+        <v>1.280187450089447</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>0.49116423581226037</v>
+        <v>0.49404579143164179</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827621763326983</v>
+        <v>0.6721968514046508</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.91748755732030485</v>
+        <v>0.92287026077007195</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>0.14438705651850378</v>
+        <v>0.14523414452642597</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19232,23 +19232,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.3471421710749396</v>
+        <v>1.3550455663348715</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>0.48363088814762811</v>
+        <v>0.48646824722598919</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827621763326972</v>
+        <v>0.67219685140465069</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.93955007932824186</v>
+        <v>0.94506221888030273</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>0.14052213259940072</v>
+        <v>0.14134654592454771</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.45126075738980537</v>
+        <v>0.45390820782787011</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.71700695181387952</v>
+        <v>0.72121347838989958</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.66827621763326994</v>
+        <v>0.67219685140465091</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.62136883967101897</v>
+        <v>0.62501427787907882</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.7675966488436381</v>
+        <v>0.7720999743621092</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>0.71700695181387952</v>
+        <v>0.72121347838989958</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>0.66827621763326994</v>
+        <v>0.67219685140465091</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>0.62136883967101897</v>
+        <v>0.62501427787907882</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.66629551997882908</v>
+        <v>0.67020453342030761</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>0.45126075738980537</v>
+        <v>0.45390820782787011</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>0.7675966488436381</v>
+        <v>0.7720999743621092</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16883903788744581</v>
+        <v>0.17996939953838226</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>0.66827621763326939</v>
+        <v>0.67219685140465046</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>2.6227184324110333E-2</v>
+        <v>2.5988175323389061E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.63910536203371593</v>
+        <v>0.64285485662853192</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.64023859934395666</v>
+        <v>0.64399474239992138</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.87153298843376326</v>
+        <v>0.8715329884337637</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20229,11 +20229,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.29451860001553737</v>
+        <v>0.29624647770900098</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>0.34392459257051061</v>
+        <v>0.34565247026397422</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.4618655811678718</v>
+        <v>0.46231646739552212</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20254,11 +20254,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.3691583318606303</v>
+        <v>0.37132410491178752</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>0.42596643843689541</v>
+        <v>0.42813221148805264</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33349575243522434</v>
+        <v>0.33401419142510247</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20300,11 +20300,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.45808541046915391</v>
+        <v>0.46077289968854113</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>0.52322569486949744</v>
+        <v>0.52591318408888466</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.18131543568258357</v>
+        <v>0.18190991533135603</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20325,11 +20325,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.51806059342226762</v>
+        <v>0.52109994422452466</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>0.58859472455593909</v>
+        <v>0.59163407535819612</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>7.9033349551387633E-2</v>
+        <v>7.9677054224906119E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>2384.5088333000003</v>
+        <v>2332.6716847500002</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.16883903788744581</v>
+        <v>0.17996939953838226</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20481,13 +20481,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0948992599999998</v>
+        <v>1.1013227999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>0.63910536203371593</v>
+        <v>0.64285485662853192</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>0.34392459257051061</v>
+        <v>0.34565247026397422</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>0.42596643843689541</v>
+        <v>0.42813221148805264</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20635,7 +20635,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>0.52322569486949744</v>
+        <v>0.52591318408888466</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>0.58859472455593909</v>
+        <v>0.59163407535819612</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20672,22 +20672,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20877,10 +20877,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20896,22 +20896,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.11460200453321724</v>
+        <v>0.11783600222796822</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.8695652173913038E-2</v>
+        <v>0.06</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21046,22 +21046,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21069,13 +21069,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.30792757413049093</v>
+        <v>-0.30973411940985324</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.24872544728709015</v>
+        <v>0.25018466633859132</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.4838467970553511E-4</v>
+        <v>3.50428578178419E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-5.8853742163695273E-2</v>
+        <v>-5.9199024493083445E-2</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21224,33 +21224,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21313,23 +21313,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21347,7 +21347,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>0.58117762919665827</v>
+        <v>0.58458727416093559</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>0.66827621763326939</v>
+        <v>0.67219685140465046</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21373,13 +21373,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>0.62 HKD</v>
+        <v>0.63 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>0.63910536203371593</v>
+        <v>0.64285485662853192</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21543,13 +21543,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21562,22 +21562,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21642,11 +21642,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>0.29451860001553737</v>
+        <v>0.29624647770900098</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>0.34392459257051061</v>
+        <v>0.34565247026397422</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21663,11 +21663,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>0.3691583318606303</v>
+        <v>0.37132410491178752</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>0.42596643843689541</v>
+        <v>0.42813221148805264</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21703,11 +21703,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>0.45808541046915391</v>
+        <v>0.46077289968854113</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>0.52322569486949744</v>
+        <v>0.52591318408888466</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21724,11 +21724,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>0.51806059342226762</v>
+        <v>0.52109994422452466</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>0.58859472455593909</v>
+        <v>0.59163407535819612</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21746,13 +21746,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21760,13 +21760,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21803,22 +21803,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21842,15 +21842,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21865,12 +21862,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD831AC5-2E4A-4436-9379-E405BF330E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260108C6-7676-4542-B9DF-3D549F3A2639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>0.45</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>2332.6716847500002</v>
+        <v>2358.5902590250003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.17996939953838226</v>
+        <v>0.17578932314043633</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.1013227999999999</v>
+        <v>1.1024826515674591</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>0.64285485662853192</v>
+        <v>0.64353187540368983</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>0.34565247026397422</v>
+        <v>0.34596446048294099</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>0.42813221148805264</v>
+        <v>0.42852326926431716</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>0.52591318408888466</v>
+        <v>0.52639844433224525</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>0.59163407535819612</v>
+        <v>0.5921828686703039</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11783600222796822</v>
+        <v>0.11666383567322229</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>0.06</v>
+        <v>5.9340659340659338E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.30973411940985324</v>
+        <v>-0.31006031405859114</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.25018466633859132</v>
+        <v>0.25044814683441602</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.50428578178419E-4</v>
+        <v>3.507976299547763E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-5.9199024493083445E-2</v>
+        <v>-5.9261369594220327E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.58458727416093559</v>
+        <v>0.58520292877759506</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.67219685140465046</v>
+        <v>0.67290477152738171</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.1764015250562416</v>
+        <v>0.17634515332240949</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.2666367030415219E-3</v>
+        <v>1.2257743075941147E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.5988175323388856E-2</v>
+        <v>2.5945315952382191E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.2233642926730453E-2</v>
+        <v>5.2188595919687976E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-2.2078819036575568E-2</v>
+        <v>-2.2117851462165421E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.64285485662853192</v>
+        <v>0.64353187540368983</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>0.29624647770900098</v>
+        <v>0.29655846792796775</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>0.34565247026397422</v>
+        <v>0.34596446048294099</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>0.37132410491178752</v>
+        <v>0.37171516268805205</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>0.42813221148805264</v>
+        <v>0.42852326926431716</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>0.46077289968854113</v>
+        <v>0.46125815993190172</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>0.52591318408888466</v>
+        <v>0.52639844433224525</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>0.52109994422452466</v>
+        <v>0.52164873753663243</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>0.59163407535819612</v>
+        <v>0.5921828686703039</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10176,11 +10176,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8841975685556493</v>
+        <v>1.8861819000371114</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.58458727416093559</v>
+        <v>0.58520292877759506</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10586,11 +10586,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>1605573.3558852</v>
+        <v>1607264.2559314843</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.30973411940985324</v>
+        <v>0.31006031405859114</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1296885.9713925745</v>
+        <v>1298251.7791527838</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.25018466633859138</v>
+        <v>0.25044814683441607</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10620,11 +10620,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>1816.5218263199997</v>
+        <v>1818.4348854953669</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>3.5042857817841905E-4</v>
+        <v>3.507976299547763E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10637,11 +10637,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2904275.8491040943</v>
+        <v>2907334.4699697634</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>0.56026921432662313</v>
+        <v>0.56085925852296203</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14224,12 +14224,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.06</v>
+        <v>5.9340659340659338E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.06</v>
+        <v>5.9340659340659338E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -15366,50 +15366,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.3026201002585704E-2</v>
+        <v>5.3082045231316141E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.9267641601448293E-2</v>
+        <v>3.9308996085040078E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.7937804363782218E-2</v>
+        <v>3.7977758337183379E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.4442552981250246E-2</v>
+        <v>-5.4499888832657099E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3975718611526624E-2</v>
+        <v>1.3990437056598266E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.0559122886245254E-2</v>
+        <v>4.0601837485683655E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.14945054376799821</v>
+        <v>0.14960793672077002</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>8.627779349958091E-2</v>
+        <v>8.6368656445510478E-2</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>5.9375484609521405E-2</v>
+        <v>5.9438015548582142E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>9.0216981245431566E-2</v>
+        <v>9.0311992723545828E-2</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1471893723367236E-2</v>
+        <v>1.1483975280124957E-2</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11783600222796822</v>
+        <v>0.11666383567322229</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.7261425780996202E-2</v>
+        <v>8.6393397989099063E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.4306231919516042E-2</v>
+        <v>8.3467600741062367E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.12098345106944498</v>
+        <v>-0.11977997545638923</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.1057152470059163E-2</v>
+        <v>3.0748213311204978E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.0131384191656116E-2</v>
+        <v>8.9234807660843199E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.33211231948444048</v>
+        <v>0.32880865213356048</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.19172842999906869</v>
+        <v>0.18982122295716589</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.131945521354492</v>
+        <v>0.13063300120567503</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.20048218054540348</v>
+        <v>0.19848789609570511</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>2.5493097163038301E-2</v>
+        <v>2.523950611016474E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21341280183342784</v>
+        <v>0.21106760620888468</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21572174227936</v>
+        <v>0.2133511736828835</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2971327964973702E-2</v>
+        <v>4.2499115569754213E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16108353458248065</v>
+        <v>0.15931338585080501</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13489253633810158</v>
+        <v>0.13341020077394661</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.37721124912368575</v>
+        <v>0.37306607056188701</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24045132611969475</v>
+        <v>0.23780900385464313</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17792130916377988</v>
+        <v>0.17596612994219987</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24418824291642527</v>
+        <v>0.24150485563162938</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6732437491169318E-2</v>
+        <v>2.6438674441815808E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-5.9199024493083445E-2</v>
+        <v>-5.9261369594220327E-2</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1013227999999999</v>
+        <v>1.1024826515674591</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>3484476.804110514</v>
+        <v>3488146.4601668697</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.67219685140465046</v>
+        <v>0.67290477152738171</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.64399474239992138</v>
+        <v>0.64467296163901089</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.67219685140465046</v>
+        <v>0.67290477152738171</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.67219685140465046</v>
+        <v>0.67290477152738171</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.67219685140465046</v>
+        <v>0.67290477152738171</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.67219685140465046</v>
+        <v>0.67290477152738171</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.67219685140465046</v>
+        <v>0.67290477152738171</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.70652771315935969</v>
+        <v>0.70727178862530049</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.65503142052729668</v>
+        <v>0.65572126297842326</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.67219685140465091</v>
+        <v>0.67290477152738226</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.68936228228200547</v>
+        <v>0.6900882800763416</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.58636969701787978</v>
+        <v>0.58698722878258736</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.73981824576998612</v>
+        <v>0.74059738096267547</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.63934645804729007</v>
+        <v>0.64001978197331388</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.67219685140465091</v>
+        <v>0.67290477152738226</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.70568744731221622</v>
+        <v>0.70643063785716931</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.51434691011988953</v>
+        <v>0.51488859151422761</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18884,23 +18884,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.7720999743621092</v>
+        <v>0.77291310686558512</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.62501427787907882</v>
+        <v>0.62567250795465912</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.67219685140465091</v>
+        <v>0.67290477152738226</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.72121347838989958</v>
+        <v>0.72197302008229269</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.45390820782787011</v>
+        <v>0.45438623856175825</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18915,23 +18915,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.80340346875447044</v>
+        <v>0.80424956834719374</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.61191820648994422</v>
+        <v>0.61256264451570208</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.67219685140465091</v>
+        <v>0.67290477152738226</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.73597949396028373</v>
+        <v>0.73675458639429814</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>0.40319041569470676</v>
+        <v>0.40361503328695858</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18946,23 +18946,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.83375837240766959</v>
+        <v>0.83463644008693594</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.59995163309940613</v>
+        <v>0.600583468599452</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.67219685140465091</v>
+        <v>0.67290477152738226</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.75002269757967033</v>
+        <v>0.75081257953019176</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>0.36063003068785648</v>
+        <v>0.36100982606335053</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18977,23 +18977,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.86319343049561992</v>
+        <v>0.86410249753153412</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.58901714179616393</v>
+        <v>0.5896374617016199</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.67219685140465091</v>
+        <v>0.67290477152738226</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.76337847165125439</v>
+        <v>0.76418241915593632</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>0.32491502229049962</v>
+        <v>0.32525720461696617</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19009,23 +19009,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.89173651712635993</v>
+        <v>0.8926756441444782</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.57902571850742046</v>
+        <v>0.57963551600476637</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.67219685140465091</v>
+        <v>0.67290477152738226</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.77608046657248142</v>
+        <v>0.77689779110769352</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>0.29494438587313709</v>
+        <v>0.29525500480181832</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19040,23 +19040,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.91941466173798647</v>
+        <v>0.92038293782975689</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.56989602636479231</v>
+        <v>0.5704962089810679</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.67219685140465091</v>
+        <v>0.67290477152738226</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.78816068551854346</v>
+        <v>0.78899073226460947</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>0.26979420146695876</v>
+        <v>0.27007833362826772</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19072,23 +19072,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.94625407469471512</v>
+        <v>0.94725061655487564</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.56155374356779886</v>
+        <v>0.56214514055848108</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.67219685140465091</v>
+        <v>0.67290477152738226</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.799649565075637</v>
+        <v>0.8004917112669907</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>0.24868915161562039</v>
+        <v>0.24895105711899457</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19104,23 +19104,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.97228017210730067</v>
+        <v>0.97330412319741522</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>0.55393095835469519</v>
+        <v>0.55451432745439233</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.67219685140465091</v>
+        <v>0.67290477152738226</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.810576051927139</v>
+        <v>0.81142970528324176</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>0.23097862027183988</v>
+        <v>0.23122187403428979</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19136,23 +19136,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>1.0910478642712429</v>
+        <v>1.0921968948511491</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>0.52461548871336794</v>
+        <v>0.52516798440027967</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.6721968514046508</v>
+        <v>0.67290477152738215</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.8576903321173498</v>
+        <v>0.85859360359788284</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>0.17702714949523338</v>
+        <v>0.17721358458658432</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19168,23 +19168,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.1928785128228476</v>
+        <v>1.1941347857456326</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>0.50594134355885012</v>
+        <v>0.50647417268067441</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.6721968514046508</v>
+        <v>0.67290477152738215</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.89434817579524484</v>
+        <v>0.89529005326618272</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>0.1545764781942488</v>
+        <v>0.15473926949442521</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19200,23 +19200,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.280187450089447</v>
+        <v>1.2815356719010973</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>0.49404579143164179</v>
+        <v>0.49456609282337594</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.6721968514046508</v>
+        <v>0.67290477152738215</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.92287026077007195</v>
+        <v>0.92384217610544461</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>0.14523414452642597</v>
+        <v>0.14538709700337238</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19232,23 +19232,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.3550455663348715</v>
+        <v>1.3564726245271581</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>0.48646824722598919</v>
+        <v>0.48698056837203663</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.67219685140465069</v>
+        <v>0.67290477152738204</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.94506221888030273</v>
+        <v>0.94605750554458934</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>0.14134654592454771</v>
+        <v>0.14149540420011009</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.45390820782787011</v>
+        <v>0.45438623856175825</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.72121347838989958</v>
+        <v>0.72197302008229269</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.67219685140465091</v>
+        <v>0.67290477152738226</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.62501427787907882</v>
+        <v>0.62567250795465912</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.7720999743621092</v>
+        <v>0.77291310686558512</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>0.72121347838989958</v>
+        <v>0.72197302008229269</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>0.67219685140465091</v>
+        <v>0.67290477152738226</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>0.62501427787907882</v>
+        <v>0.62567250795465912</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.67020453342030761</v>
+        <v>0.67091035534518362</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>0.45390820782787011</v>
+        <v>0.45438623856175825</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>0.7720999743621092</v>
+        <v>0.77291310686558512</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>0.45</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17996939953838226</v>
+        <v>0.17578932314043633</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>0.67219685140465046</v>
+        <v>0.67290477152738171</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>2.5988175323389061E-2</v>
+        <v>2.5945315952382468E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.64285485662853192</v>
+        <v>0.64353187540368983</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.64399474239992138</v>
+        <v>0.64467296163901089</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.8715329884337637</v>
+        <v>0.87153298843376337</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20229,11 +20229,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.29624647770900098</v>
+        <v>0.29655846792796775</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>0.34565247026397422</v>
+        <v>0.34596446048294099</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46231646739552212</v>
+        <v>0.46239732062080641</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20254,11 +20254,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.37132410491178752</v>
+        <v>0.37171516268805205</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>0.42813221148805264</v>
+        <v>0.42852326926431716</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33401419142510247</v>
+        <v>0.33410715825769621</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20300,11 +20300,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.46077289968854113</v>
+        <v>0.46125815993190172</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>0.52591318408888466</v>
+        <v>0.52639844433224525</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.18190991533135603</v>
+        <v>0.18201651782666761</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20325,11 +20325,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.52109994422452466</v>
+        <v>0.52164873753663243</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>0.59163407535819612</v>
+        <v>0.5921828686703039</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>7.9677054224906119E-2</v>
+        <v>7.9792483785165347E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>0.45</v>
+        <v>0.45500000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>2332.6716847500002</v>
+        <v>2358.5902590250003</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.17996939953838226</v>
+        <v>0.17578932314043633</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20481,13 +20481,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.1013227999999999</v>
+        <v>1.1024826515674591</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>0.64285485662853192</v>
+        <v>0.64353187540368983</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>0.34565247026397422</v>
+        <v>0.34596446048294099</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>0.42813221148805264</v>
+        <v>0.42852326926431716</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20635,7 +20635,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>0.52591318408888466</v>
+        <v>0.52639844433224525</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>0.59163407535819612</v>
+        <v>0.5921828686703039</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20672,22 +20672,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20877,10 +20877,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20896,22 +20896,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.11783600222796822</v>
+        <v>0.11666383567322229</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>0.06</v>
+        <v>5.9340659340659338E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21046,22 +21046,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21069,13 +21069,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.30973411940985324</v>
+        <v>-0.31006031405859114</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.25018466633859132</v>
+        <v>0.25044814683441602</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.50428578178419E-4</v>
+        <v>3.507976299547763E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-5.9199024493083445E-2</v>
+        <v>-5.9261369594220327E-2</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21224,33 +21224,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21313,23 +21313,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21347,7 +21347,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>0.58458727416093559</v>
+        <v>0.58520292877759506</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>0.67219685140465046</v>
+        <v>0.67290477152738171</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21373,13 +21373,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>0.64285485662853192</v>
+        <v>0.64353187540368983</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21543,13 +21543,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21562,22 +21562,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21642,11 +21642,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>0.29624647770900098</v>
+        <v>0.29655846792796775</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>0.34565247026397422</v>
+        <v>0.34596446048294099</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21663,11 +21663,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>0.37132410491178752</v>
+        <v>0.37171516268805205</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>0.42813221148805264</v>
+        <v>0.42852326926431716</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21703,11 +21703,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>0.46077289968854113</v>
+        <v>0.46125815993190172</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>0.52591318408888466</v>
+        <v>0.52639844433224525</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21724,11 +21724,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>0.52109994422452466</v>
+        <v>0.52164873753663243</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>0.59163407535819612</v>
+        <v>0.5921828686703039</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21746,13 +21746,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21760,13 +21760,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21803,22 +21803,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21842,12 +21842,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21862,15 +21865,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260108C6-7676-4542-B9DF-3D549F3A2639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9710841-674E-4BF1-BCDE-124E55335C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3249,10 +3249,10 @@
     <t>Historical Average or D&amp;A</t>
   </si>
   <si>
+    <t>寶勝國際</t>
+  </si>
+  <si>
     <t>3813.HK</t>
-  </si>
-  <si>
-    <t>寶勝國際</t>
   </si>
   <si>
     <t>IND_01</t>
@@ -5342,7 +5342,7 @@
         <v>535</v>
       </c>
       <c r="C4" s="425" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E4" s="435" t="s">
         <v>539</v>
@@ -5356,7 +5356,7 @@
         <v>349</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E5" s="438" t="s">
         <v>541</v>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>0.45500000000000002</v>
+        <v>0.47</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>2358.5902590250003</v>
+        <v>2436.34598185</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.17578932314043633</v>
+        <v>0.16328203707260031</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.1024826515674591</v>
+        <v>1.10486085128784</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>0.64353187540368983</v>
+        <v>0.64492005808753095</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C19" s="31" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v>Negative Growth Asset Play</v>
+        <v xml:space="preserve">Negative Growth </v>
       </c>
       <c r="D19" s="1" t="s">
         <v>348</v>
@@ -5538,13 +5538,13 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>0.34596446048294099</v>
+        <v>0.34660417600544841</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5553,13 +5553,13 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>0.42852326926431716</v>
+        <v>0.42932510763765497</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E23" s="448">
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>0.52639844433224525</v>
+        <v>0.52739343869829147</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>0.5921828686703039</v>
+        <v>0.59330813343522593</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11666383567322229</v>
+        <v>0.11318414929152036</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.9340659340659338E-2</v>
+        <v>5.7446808510638298E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.31006031405859114</v>
+        <v>-0.31072915483458613</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.25044814683441602</v>
+        <v>0.25098839634485026</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.507976299547763E-4</v>
+        <v>3.5155434646571876E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-5.9261369594220327E-2</v>
+        <v>-5.938920414327014E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.58520292877759506</v>
+        <v>0.58646528827105848</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.67290477152738171</v>
+        <v>0.67435631540175844</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>0.45 HKD</v>
+        <v>0.46 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.17634515332240949</v>
+        <v>0.17622993817199181</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.2257743075941147E-3</v>
+        <v>1.1422566841124871E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.5945315952382191E-2</v>
+        <v>2.585771692502627E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.2188595919687976E-2</v>
+        <v>5.2096525833418235E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-2.2117851462165421E-2</v>
+        <v>-2.2197628994799792E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.64353187540368983</v>
+        <v>0.64492005808753095</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6562,19 +6562,19 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>4.9405992554973223E-2</v>
+        <v>4.9405992554973237E-2</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>0.29655846792796775</v>
+        <v>0.29719818345047516</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>0.34596446048294099</v>
+        <v>0.34660417600544841</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6583,19 +6583,19 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>5.6808106576265109E-2</v>
+        <v>5.6808106576265137E-2</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>0.37171516268805205</v>
+        <v>0.37251700106138985</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>0.42852326926431716</v>
+        <v>0.42932510763765497</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>0.46125815993190172</v>
+        <v>0.462253154297948</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>0.52639844433224525</v>
+        <v>0.52739343869829147</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>0.52164873753663243</v>
+        <v>0.52277400230155446</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>0.5921828686703039</v>
+        <v>0.59330813343522593</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -10176,11 +10176,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.8861819000371114</v>
+        <v>1.890250641854389</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.58520292877759506</v>
+        <v>0.58646528827105848</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10585,12 +10585,12 @@
         <v>239</v>
       </c>
       <c r="C86" s="73">
-        <f>-DCF!F4*Exchange_Rate</f>
-        <v>1607264.2559314843</v>
+        <f>DCF!F4*Exchange_Rate</f>
+        <v>-1610731.3357976391</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.31006031405859114</v>
+        <v>-0.31072915483458613</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1298251.7791527838</v>
+        <v>1301052.278565428</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.25044814683441607</v>
+        <v>0.25098839634485026</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10620,11 +10620,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>1818.4348854953669</v>
+        <v>1822.3574881141631</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>3.507976299547763E-4</v>
+        <v>3.5155434646571876E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10637,11 +10637,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2907334.4699697634</v>
+        <v>-307856.69974409696</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>0.56085925852296203</v>
+        <v>-5.9389204143270147E-2</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14224,12 +14224,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.9340659340659338E-2</v>
+        <v>5.7446808510638298E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.9340659340659338E-2</v>
+        <v>5.7446808510638298E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -15366,50 +15366,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.3082045231316141E-2</v>
+        <v>5.3196550167014571E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.9308996085040078E-2</v>
+        <v>3.9393790746765585E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.7977758337183379E-2</v>
+        <v>3.8059681344434125E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.4499888832657099E-2</v>
+        <v>-5.4617452243018554E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3990437056598266E-2</v>
+        <v>1.402061626481411E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.0601837485683655E-2</v>
+        <v>4.0689420975925539E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.14960793672077002</v>
+        <v>0.14993066066819019</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>8.6368656445510478E-2</v>
+        <v>8.655496496865718E-2</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>5.9438015548582142E-2</v>
+        <v>5.9566231146130695E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>9.0311992723545828E-2</v>
+        <v>9.0506807540392892E-2</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1483975280124957E-2</v>
+        <v>1.1508747721452014E-2</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11666383567322229</v>
+        <v>0.11318414929152036</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.6393397989099063E-2</v>
+        <v>8.3816576056948061E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.3467600741062367E-2</v>
+        <v>8.0978045413689637E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.11977997545638923</v>
+        <v>-0.11620734519791183</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.0748213311204978E-2</v>
+        <v>2.9831098435774701E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>8.9234807660843199E-2</v>
+        <v>8.657323611899051E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.32880865213356048</v>
+        <v>0.31900140567700042</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.18982122295716589</v>
+        <v>0.18415949993331315</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13063300120567503</v>
+        <v>0.12673666201304404</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.19848789609570511</v>
+        <v>0.19256767561785723</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>2.523950611016474E-2</v>
+        <v>2.4486697279685138E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21106760620888468</v>
+        <v>0.2043314060107288</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2133511736828835</v>
+        <v>0.20654209367172766</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2499115569754213E-2</v>
+        <v>4.1142760817528018E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15931338585080501</v>
+        <v>0.15422891608960912</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13341020077394661</v>
+        <v>0.12915242840882066</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.37306607056188701</v>
+        <v>0.36115970660778424</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23780900385464313</v>
+        <v>0.23021935479545241</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17596612994219987</v>
+        <v>0.17035018962489562</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24150485563162938</v>
+        <v>0.23379725385615188</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6438674441815808E-2</v>
+        <v>2.5594886959630199E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-5.9261369594220327E-2</v>
+        <v>-5.938920414327014E-2</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1024826515674591</v>
+        <v>1.10486085128784</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>3488146.4601668697</v>
+        <v>3495670.8497111606</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.67290477152738171</v>
+        <v>0.67435631540175844</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16551,14 +16551,14 @@
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
-        <v>-1.1861621958951121E-2</v>
+        <v>-1.18616219589511E-2</v>
       </c>
       <c r="E16" s="312" t="s">
         <v>401</v>
       </c>
       <c r="F16" s="315">
         <f>Scenarios!C41</f>
-        <v>-1.1861621958951121E-2</v>
+        <v>-1.18616219589511E-2</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.64467296163901089</v>
+        <v>0.64606360579556732</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="D21" s="303">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
-        <v>-1.1861621958951121E-2</v>
+        <v>-1.18616219589511E-2</v>
       </c>
       <c r="E21" s="303">
         <f>$C$17</f>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="D22" s="303">
         <f t="shared" si="1"/>
-        <v>-1.1861621958951121E-2</v>
+        <v>-1.18616219589511E-2</v>
       </c>
       <c r="E22" s="303">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
@@ -16761,7 +16761,7 @@
       </c>
       <c r="D23" s="303">
         <f t="shared" si="1"/>
-        <v>-1.1861621958951121E-2</v>
+        <v>-1.18616219589511E-2</v>
       </c>
       <c r="E23" s="303">
         <f t="shared" si="6"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.67290477152738171</v>
+        <v>0.67435631540175844</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.67290477152738171</v>
+        <v>0.67435631540175844</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.67290477152738171</v>
+        <v>0.67435631540175844</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.67290477152738171</v>
+        <v>0.67435631540175844</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.67290477152738171</v>
+        <v>0.67435631540175844</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.70727178862530049</v>
+        <v>0.70879746666436128</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.65572126297842326</v>
+        <v>0.65713573977045803</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.67290477152738226</v>
+        <v>0.674356315401759</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.6900882800763416</v>
+        <v>0.6915768910330603</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.58698722878258736</v>
+        <v>0.58825343724525403</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.74059738096267547</v>
+        <v>0.74219494667658137</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.64001978197331388</v>
+        <v>0.64140038861085424</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.67290477152738226</v>
+        <v>0.674356315401759</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.70643063785716931</v>
+        <v>0.70795450142366789</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.51488859151422761</v>
+        <v>0.5159992737572775</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18884,23 +18884,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.77291310686558512</v>
+        <v>0.77458038183994693</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.62567250795465912</v>
+        <v>0.62702216563984114</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.67290477152738226</v>
+        <v>0.674356315401759</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.72197302008229269</v>
+        <v>0.72353041060634415</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.45438623856175825</v>
+        <v>0.45536640929184286</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18915,23 +18915,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.80424956834719374</v>
+        <v>0.80598444018017945</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.61256264451570208</v>
+        <v>0.6138840225054889</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.67290477152738226</v>
+        <v>0.674356315401759</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.73675458639429814</v>
+        <v>0.73834386269616203</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>0.40361503328695858</v>
+        <v>0.40448568386630318</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18946,23 +18946,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.83463644008693594</v>
+        <v>0.83643686038889031</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.600583468599452</v>
+        <v>0.60187900593517152</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.67290477152738226</v>
+        <v>0.674356315401759</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.75081257953019176</v>
+        <v>0.75243218076759766</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>0.36100982606335053</v>
+        <v>0.36178857162109507</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18977,23 +18977,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.86410249753153412</v>
+        <v>0.86596647998521559</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.5896374617016199</v>
+        <v>0.590909387064392</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.67290477152738226</v>
+        <v>0.674356315401759</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.76418241915593632</v>
+        <v>0.76583086089147989</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>0.32525720461696617</v>
+        <v>0.32595882707966178</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19009,23 +19009,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.8926756441444782</v>
+        <v>0.8946012626240768</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.57963551600476637</v>
+        <v>0.58088586585845836</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.67290477152738226</v>
+        <v>0.674356315401759</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.77689779110769352</v>
+        <v>0.77857366156873886</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>0.29525500480181832</v>
+        <v>0.29589190858335396</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19040,23 +19040,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.92038293782975689</v>
+        <v>0.92236832457691165</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.5704962089810679</v>
+        <v>0.57172684415047226</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.67290477152738226</v>
+        <v>0.674356315401759</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.78899073226460947</v>
+        <v>0.79069268878627186</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>0.27007833362826772</v>
+        <v>0.27066092802701175</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19072,23 +19072,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.94725061655487564</v>
+        <v>0.94929396040996361</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.56214514055848108</v>
+        <v>0.5633577613776739</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.67290477152738226</v>
+        <v>0.674356315401759</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.8004917112669907</v>
+        <v>0.80221847690923975</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>0.24895105711899457</v>
+        <v>0.24948807721050092</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19104,23 +19104,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.97330412319741522</v>
+        <v>0.97540366788443844</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>0.55451432745439233</v>
+        <v>0.55571048760858999</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.67290477152738226</v>
+        <v>0.674356315401759</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.81142970528324176</v>
+        <v>0.81318006561360134</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>0.23122187403428979</v>
+        <v>0.23172064995189037</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19136,23 +19136,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>1.0921968948511491</v>
+        <v>1.0945529068448463</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>0.52516798440027967</v>
+        <v>0.52630084064239646</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.67290477152738215</v>
+        <v>0.67435631540175889</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.85859360359788284</v>
+        <v>0.8604457026446064</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>0.17721358458658432</v>
+        <v>0.17759585753819249</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19168,23 +19168,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.1941347857456326</v>
+        <v>1.196710691143799</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>0.50647417268067441</v>
+        <v>0.507566703918365</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.67290477152738215</v>
+        <v>0.67435631540175889</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.89529005326618272</v>
+        <v>0.89722131136925609</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>0.15473926949442521</v>
+        <v>0.15507306239984678</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19200,23 +19200,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.2815356719010973</v>
+        <v>1.2843001124773188</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>0.49456609282337594</v>
+        <v>0.49563293677052578</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.67290477152738215</v>
+        <v>0.67435631540175889</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.92384217610544461</v>
+        <v>0.92583502488339708</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>0.14538709700337238</v>
+        <v>0.14570071604576623</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19232,23 +19232,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.3564726245271581</v>
+        <v>1.3593987139415977</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>0.48698056837203663</v>
+        <v>0.48803104934775693</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.67290477152738204</v>
+        <v>0.67435631540175878</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.94605750554458934</v>
+        <v>0.94809827570269711</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>0.14149540420011009</v>
+        <v>0.14180062835055404</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.45438623856175825</v>
+        <v>0.45536640929184286</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.72197302008229269</v>
+        <v>0.72353041060634415</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.67290477152738226</v>
+        <v>0.674356315401759</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.62567250795465912</v>
+        <v>0.62702216563984114</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.77291310686558512</v>
+        <v>0.77458038183994693</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>0.72197302008229269</v>
+        <v>0.72353041060634415</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>0.67290477152738226</v>
+        <v>0.674356315401759</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>0.62567250795465912</v>
+        <v>0.62702216563984114</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.67091035534518362</v>
+        <v>0.67235759700219655</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>0.45438623856175825</v>
+        <v>0.45536640929184286</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>0.77291310686558512</v>
+        <v>0.77458038183994693</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>0.45500000000000002</v>
+        <v>0.47</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17578932314043633</v>
+        <v>0.16328203707260031</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>0.67290477152738171</v>
+        <v>0.67435631540175844</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>2.5945315952382468E-2</v>
+        <v>2.5857716925026655E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.64353187540368983</v>
+        <v>0.64492005808753095</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20035,7 +20035,7 @@
       </c>
       <c r="C41" s="138">
         <f>DCF!C16</f>
-        <v>-1.1861621958951121E-2</v>
+        <v>-1.18616219589511E-2</v>
       </c>
       <c r="E41" s="97"/>
     </row>
@@ -20075,7 +20075,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="138">
-        <v>-1.1861621958951121E-2</v>
+        <v>-1.18616219589511E-2</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="221" t="s">
@@ -20088,7 +20088,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.64467296163901089</v>
+        <v>0.64606360579556732</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20144,14 +20144,14 @@
       </c>
       <c r="C53" s="217" t="str">
         <f>IF(F53&gt;50%,"Y","N")</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E53" s="126" t="s">
         <v>273</v>
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.87153298843376337</v>
+        <v>-9.2087698930290715E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20225,23 +20225,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>4.9405992554973223E-2</v>
+        <v>4.9405992554973237E-2</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.29655846792796775</v>
+        <v>0.29719818345047516</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>0.34596446048294099</v>
+        <v>0.34660417600544841</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46239732062080641</v>
+        <v>0.4625625739827649</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20250,23 +20250,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>5.6808106576265109E-2</v>
+        <v>5.6808106576265137E-2</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.37171516268805205</v>
+        <v>0.37251700106138985</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>0.42852326926431716</v>
+        <v>0.42932510763765497</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33410715825769621</v>
+        <v>0.33429717024030692</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20300,11 +20300,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.46125815993190172</v>
+        <v>0.462253154297948</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>0.52639844433224525</v>
+        <v>0.52739343869829147</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.18201651782666761</v>
+        <v>0.18223439931106677</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20325,11 +20325,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.52164873753663243</v>
+        <v>0.52277400230155446</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>0.5921828686703039</v>
+        <v>0.59330813343522593</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>7.9792483785165347E-2</v>
+        <v>8.0028406629740867E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>0.45500000000000002</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>2358.5902590250003</v>
+        <v>2436.34598185</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.17578932314043633</v>
+        <v>0.16328203707260031</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.1024826515674591</v>
+        <v>1.10486085128784</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>0.64353187540368983</v>
+        <v>0.64492005808753095</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20567,7 +20567,7 @@
       </c>
       <c r="C19" s="356" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v>Negative Growth Asset Play</v>
+        <v xml:space="preserve">Negative Growth </v>
       </c>
       <c r="D19" s="347" t="s">
         <v>363</v>
@@ -20603,14 +20603,14 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>0.34596446048294099</v>
+        <v>0.34660417600544841</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
       </c>
       <c r="E22" s="370">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20619,14 +20619,14 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>0.42852326926431716</v>
+        <v>0.42932510763765497</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
       </c>
       <c r="E23" s="372">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>0.52639844433224525</v>
+        <v>0.52739343869829147</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>0.5921828686703039</v>
+        <v>0.59330813343522593</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.11666383567322229</v>
+        <v>0.11318414929152036</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.9340659340659338E-2</v>
+        <v>5.7446808510638298E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.31006031405859114</v>
+        <v>-0.31072915483458613</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.25044814683441602</v>
+        <v>0.25098839634485026</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.507976299547763E-4</v>
+        <v>3.5155434646571876E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-5.9261369594220327E-2</v>
+        <v>-5.938920414327014E-2</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21347,7 +21347,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>0.58520292877759506</v>
+        <v>0.58646528827105848</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>0.67290477152738171</v>
+        <v>0.67435631540175844</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>0.45 HKD</v>
+        <v>0.46 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>0.64353187540368983</v>
+        <v>0.64492005808753095</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21638,19 +21638,19 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>4.9405992554973223E-2</v>
+        <v>4.9405992554973237E-2</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>0.29655846792796775</v>
+        <v>0.29719818345047516</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>0.34596446048294099</v>
+        <v>0.34660417600544841</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21659,19 +21659,19 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>5.6808106576265109E-2</v>
+        <v>5.6808106576265137E-2</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>0.37171516268805205</v>
+        <v>0.37251700106138985</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>0.42852326926431716</v>
+        <v>0.42932510763765497</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21703,11 +21703,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>0.46125815993190172</v>
+        <v>0.462253154297948</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>0.52639844433224525</v>
+        <v>0.52739343869829147</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21724,11 +21724,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>0.52164873753663243</v>
+        <v>0.52277400230155446</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>0.5921828686703039</v>
+        <v>0.59330813343522593</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9710841-674E-4BF1-BCDE-124E55335C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3551701B-5306-4B0C-90AD-C20FC42AFEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.16328203707260031</v>
+        <v>0.16697578761628093</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.10486085128784</v>
+        <v>1.1164044342041017</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>0.64492005808753095</v>
+        <v>0.65165818095270089</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,13 +5538,13 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>0.34660417600544841</v>
+        <v>0.34970930174976633</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5553,13 +5553,13 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>0.42932510763765497</v>
+        <v>0.43321716416627298</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E23" s="448">
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>0.52739343869829147</v>
+        <v>0.53222305829131278</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>0.59330813343522593</v>
+        <v>0.59877007466972609</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11318414929152036</v>
+        <v>0.11436669694956282</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.31072915483458613</v>
+        <v>-0.31397565212802536</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.25098839634485026</v>
+        <v>0.25361072236975124</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.5155434646571876E-4</v>
+        <v>3.5522738524093551E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-5.938920414327014E-2</v>
+        <v>-6.000970237303322E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.58646528827105848</v>
+        <v>0.59259267587355635</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.67435631540175844</v>
+        <v>0.6814019881965464</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.17622993817199181</v>
+        <v>0.17567769087655769</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>0.72 HKD</v>
+        <v>0.73 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.1422566841124871E-3</v>
+        <v>7.4191952950370841E-4</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>0.67 HKD</v>
+        <v>0.68 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.585771692502627E-2</v>
+        <v>2.5437818848990913E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.2096525833418235E-2</v>
+        <v>5.1655199626301329E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>0.77 HKD</v>
+        <v>0.78 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-2.2197628994799792E-2</v>
+        <v>-2.2580040813404229E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.64492005808753095</v>
+        <v>0.65165818095270089</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6562,19 +6562,19 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>4.9405992554973237E-2</v>
+        <v>4.9405992554973223E-2</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>0.29719818345047516</v>
+        <v>0.30030330919479309</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>0.34660417600544841</v>
+        <v>0.34970930174976633</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6583,19 +6583,19 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>5.6808106576265137E-2</v>
+        <v>5.6808106576265109E-2</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>0.37251700106138985</v>
+        <v>0.37640905759000787</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>0.42932510763765497</v>
+        <v>0.43321716416627298</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>0.462253154297948</v>
+        <v>0.46708277389096925</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>0.52739343869829147</v>
+        <v>0.53222305829131278</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>0.52277400230155446</v>
+        <v>0.52823594353605463</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>0.59330813343522593</v>
+        <v>0.59877007466972609</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10176,11 +10176,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.890250641854389</v>
+        <v>1.9099999749865471</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.58646528827105848</v>
+        <v>0.59259267587355635</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10586,11 +10586,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-1610731.3357976391</v>
+        <v>-1627560.2520443576</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.31072915483458613</v>
+        <v>-0.31397565212802536</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1301052.278565428</v>
+        <v>1314645.6689353602</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.25098839634485026</v>
+        <v>0.25361072236975124</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10620,11 +10620,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>1822.3574881141631</v>
+        <v>1841.3974737762453</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>3.5155434646571876E-4</v>
+        <v>3.5522738524093551E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10637,11 +10637,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-307856.69974409696</v>
+        <v>-311073.18563522119</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-5.9389204143270147E-2</v>
+        <v>-6.0009702373033186E-2</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15366,50 +15366,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.3196550167014571E-2</v>
+        <v>5.3752347566294517E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.9393790746765585E-2</v>
+        <v>3.9805376956324093E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.8059681344434125E-2</v>
+        <v>3.8457328782891077E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.4617452243018554E-2</v>
+        <v>-5.5188095222998661E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.402061626481411E-2</v>
+        <v>1.4167103622205149E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.0689420975925539E-2</v>
+        <v>4.1114543926297785E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.14993066066819019</v>
+        <v>0.15149713576873863</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>8.655496496865718E-2</v>
+        <v>8.7459290987418004E-2</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>5.9566231146130695E-2</v>
+        <v>6.0188578953497648E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>9.0506807540392892E-2</v>
+        <v>9.1452422398690086E-2</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1508747721452014E-2</v>
+        <v>1.162899108370896E-2</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11318414929152036</v>
+        <v>0.11436669694956282</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.3816576056948061E-2</v>
+        <v>8.4692291396434249E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.0978045413689637E-2</v>
+        <v>8.1824103793385269E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.11620734519791183</v>
+        <v>-0.11742147919786949</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.9831098435774701E-2</v>
+        <v>3.0142773664266275E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>8.657323611899051E-2</v>
+        <v>8.7477753034676142E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.31900140567700042</v>
+        <v>0.32233433142284817</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.18415949993331315</v>
+        <v>0.18608359784557024</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12673666201304404</v>
+        <v>0.12806080628403757</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.19256767561785723</v>
+        <v>0.19457962212487254</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>2.4486697279685138E-2</v>
+        <v>2.4742534220657364E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-5.938920414327014E-2</v>
+        <v>-6.000970237303322E-2</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.10486085128784</v>
+        <v>1.1164044342041017</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>3495670.8497111606</v>
+        <v>3532193.6084409724</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.67435631540175844</v>
+        <v>0.6814019881965464</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.64606360579556732</v>
+        <v>0.65281367644381882</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.67435631540175844</v>
+        <v>0.6814019881965464</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.67435631540175844</v>
+        <v>0.6814019881965464</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.67435631540175844</v>
+        <v>0.6814019881965464</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.67435631540175844</v>
+        <v>0.6814019881965464</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.67435631540175844</v>
+        <v>0.6814019881965464</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.70879746666436128</v>
+        <v>0.71620298050598152</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.65713573977045803</v>
+        <v>0.6640014920418299</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.674356315401759</v>
+        <v>0.68140198819654696</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.6915768910330603</v>
+        <v>0.69880248435126435</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.58825343724525403</v>
+        <v>0.59439950742296144</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.74219494667658137</v>
+        <v>0.74994939729088739</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.64140038861085424</v>
+        <v>0.64810173797971071</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.674356315401759</v>
+        <v>0.68140198819654696</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.70795450142366789</v>
+        <v>0.71535120796693907</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.5159992737572775</v>
+        <v>0.52139043264792428</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18884,23 +18884,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.77458038183994693</v>
+        <v>0.78267319538534208</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.62702216563984114</v>
+        <v>0.63357329137749463</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.674356315401759</v>
+        <v>0.68140198819654696</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.72353041060634415</v>
+        <v>0.73108985420282591</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.45536640929184286</v>
+        <v>0.46012407619334789</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18915,23 +18915,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.80598444018017945</v>
+        <v>0.81440536323450974</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.6138840225054889</v>
+        <v>0.62029788096241623</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.674356315401759</v>
+        <v>0.68140198819654696</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.73834386269616203</v>
+        <v>0.74605807719639661</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>0.40448568386630318</v>
+        <v>0.40871174909859831</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18946,23 +18946,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.83643686038889031</v>
+        <v>0.84517595023976355</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.60187900593517152</v>
+        <v>0.60816743601437229</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.674356315401759</v>
+        <v>0.68140198819654696</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.75243218076759766</v>
+        <v>0.76029358997349916</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>0.36178857162109507</v>
+        <v>0.36556853755055674</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18977,23 +18977,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.86596647998521559</v>
+        <v>0.87501409521455498</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.590909387064392</v>
+        <v>0.59708320659797798</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.674356315401759</v>
+        <v>0.68140198819654696</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.76583086089147989</v>
+        <v>0.77383225946780598</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>0.32595882707966178</v>
+        <v>0.32936444394380865</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19009,23 +19009,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.8946012626240768</v>
+        <v>0.90394805397798927</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.58088586585845836</v>
+        <v>0.58695495967204192</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.674356315401759</v>
+        <v>0.68140198819654696</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.77857366156873886</v>
+        <v>0.78670819688896521</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>0.29589190858335396</v>
+        <v>0.29898338637171218</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19040,23 +19040,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.92236832457691165</v>
+        <v>0.93200522611222836</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.57172684415047226</v>
+        <v>0.57770024453225866</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.674356315401759</v>
+        <v>0.68140198819654696</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.79069268878627186</v>
+        <v>0.79895384366713063</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>0.27066092802701175</v>
+        <v>0.27348879260491793</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19072,23 +19072,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.94929396040996361</v>
+        <v>0.95921218090906624</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.5633577613776739</v>
+        <v>0.56924372160732872</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.674356315401759</v>
+        <v>0.68140198819654696</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.80221847690923975</v>
+        <v>0.81060005319042028</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>0.24948807721050092</v>
+        <v>0.25209472790551035</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19104,23 +19104,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.97540366788443844</v>
+        <v>0.98559468253024241</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>0.55571048760858999</v>
+        <v>0.56151654914445559</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.674356315401759</v>
+        <v>0.68140198819654696</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.81318006561360134</v>
+        <v>0.8216761685412417</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>0.23172064995189037</v>
+        <v>0.23414166661929409</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19136,23 +19136,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>1.0945529068448463</v>
+        <v>1.1059887923879634</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>0.52630084064239646</v>
+        <v>0.53179963027348198</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.67435631540175889</v>
+        <v>0.68140198819654685</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.8604457026446064</v>
+        <v>0.86943563680857061</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>0.17759585753819249</v>
+        <v>0.1794513785340601</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19168,23 +19168,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.196710691143799</v>
+        <v>1.2092139209160306</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>0.507566703918365</v>
+        <v>0.51286975934420054</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.67435631540175889</v>
+        <v>0.68140198819654685</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.89722131136925609</v>
+        <v>0.9065954769847322</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>0.15507306239984678</v>
+        <v>0.15669326529852376</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19200,23 +19200,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.2843001124773188</v>
+        <v>1.2977184762653611</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>0.49563293677052578</v>
+        <v>0.50081130823239084</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.67435631540175889</v>
+        <v>0.68140198819654685</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.92583502488339708</v>
+        <v>0.93550814649329339</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>0.14570071604576623</v>
+        <v>0.14722299669737277</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19232,23 +19232,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.3593987139415977</v>
+        <v>1.3736017076962894</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>0.48803104934775693</v>
+        <v>0.49312999631224524</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.67435631540175878</v>
+        <v>0.68140198819654674</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.94809827570269711</v>
+        <v>0.95800400369150396</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>0.14180062835055404</v>
+        <v>0.14328216089742152</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.45536640929184286</v>
+        <v>0.46012407619334789</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.72353041060634415</v>
+        <v>0.73108985420282591</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.674356315401759</v>
+        <v>0.68140198819654696</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.62702216563984114</v>
+        <v>0.63357329137749463</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.77458038183994693</v>
+        <v>0.78267319538534208</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>0.72353041060634415</v>
+        <v>0.73108985420282591</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>0.674356315401759</v>
+        <v>0.68140198819654696</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>0.62702216563984114</v>
+        <v>0.63357329137749463</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.67235759700219655</v>
+        <v>0.67938238719303956</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>0.45536640929184286</v>
+        <v>0.46012407619334789</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>0.77458038183994693</v>
+        <v>0.78267319538534208</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16328203707260031</v>
+        <v>0.16697578761628093</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>0.67435631540175844</v>
+        <v>0.6814019881965464</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>2.5857716925026655E-2</v>
+        <v>2.543781884899118E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.64492005808753095</v>
+        <v>0.65165818095270089</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.64606360579556732</v>
+        <v>0.65281367644381882</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>-9.2087698930290715E-2</v>
+        <v>-9.2087698930290646E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20225,23 +20225,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>4.9405992554973237E-2</v>
+        <v>4.9405992554973223E-2</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.29719818345047516</v>
+        <v>0.30030330919479309</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>0.34660417600544841</v>
+        <v>0.34970930174976633</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.4625625739827649</v>
+        <v>0.46335469733763812</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20250,23 +20250,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>5.6808106576265137E-2</v>
+        <v>5.6808106576265109E-2</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.37251700106138985</v>
+        <v>0.37640905759000787</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>0.42932510763765497</v>
+        <v>0.43321716416627298</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33429717024030692</v>
+        <v>0.33520797125123936</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20300,11 +20300,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.462253154297948</v>
+        <v>0.46708277389096925</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>0.52739343869829147</v>
+        <v>0.53222305829131278</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.18223439931106677</v>
+        <v>0.18327878963596878</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20325,11 +20325,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.52277400230155446</v>
+        <v>0.52823594353605463</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>0.59330813343522593</v>
+        <v>0.59877007466972609</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.0028406629740867E-2</v>
+        <v>8.1159276180119866E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20473,7 +20473,7 @@
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.16328203707260031</v>
+        <v>0.16697578761628093</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20481,13 +20481,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.10486085128784</v>
+        <v>1.1164044342041017</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>0.64492005808753095</v>
+        <v>0.65165818095270089</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20603,14 +20603,14 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>0.34660417600544841</v>
+        <v>0.34970930174976633</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
       </c>
       <c r="E22" s="370">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20619,14 +20619,14 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>0.42932510763765497</v>
+        <v>0.43321716416627298</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
       </c>
       <c r="E23" s="372">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>0.52739343869829147</v>
+        <v>0.53222305829131278</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>0.59330813343522593</v>
+        <v>0.59877007466972609</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20672,22 +20672,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20877,10 +20877,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20896,22 +20896,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.11318414929152036</v>
+        <v>0.11436669694956282</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -21046,22 +21046,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21069,13 +21069,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.31072915483458613</v>
+        <v>-0.31397565212802536</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.25098839634485026</v>
+        <v>0.25361072236975124</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.5155434646571876E-4</v>
+        <v>3.5522738524093551E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-5.938920414327014E-2</v>
+        <v>-6.000970237303322E-2</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21224,33 +21224,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21313,23 +21313,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21347,7 +21347,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>0.58646528827105848</v>
+        <v>0.59259267587355635</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>0.67435631540175844</v>
+        <v>0.6814019881965464</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21373,13 +21373,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>0.72 HKD</v>
+        <v>0.73 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21469,7 +21469,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>0.67 HKD</v>
+        <v>0.68 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21513,7 +21513,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>0.77 HKD</v>
+        <v>0.78 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>0.64492005808753095</v>
+        <v>0.65165818095270089</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21543,13 +21543,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21562,22 +21562,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21638,19 +21638,19 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>4.9405992554973237E-2</v>
+        <v>4.9405992554973223E-2</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>0.29719818345047516</v>
+        <v>0.30030330919479309</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>0.34660417600544841</v>
+        <v>0.34970930174976633</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21659,19 +21659,19 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>5.6808106576265137E-2</v>
+        <v>5.6808106576265109E-2</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>0.37251700106138985</v>
+        <v>0.37640905759000787</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>0.42932510763765497</v>
+        <v>0.43321716416627298</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21703,11 +21703,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>0.462253154297948</v>
+        <v>0.46708277389096925</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>0.52739343869829147</v>
+        <v>0.53222305829131278</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21724,11 +21724,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>0.52277400230155446</v>
+        <v>0.52823594353605463</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>0.59330813343522593</v>
+        <v>0.59877007466972609</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21746,13 +21746,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21760,13 +21760,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21803,22 +21803,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21842,15 +21842,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21865,12 +21862,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3551701B-5306-4B0C-90AD-C20FC42AFEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DF2769-D4E9-447A-8038-F2CB15C6D113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>2436.34598185</v>
+        <v>2540.0202789499999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.16697578761628093</v>
+        <v>0.14969730456978969</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.1164044342041017</v>
+        <v>1.1151225151062012</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>0.65165818095270089</v>
+        <v>0.65090990994815057</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>0.34970930174976633</v>
+        <v>0.34936447640204732</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>0.43321716416627298</v>
+        <v>0.43278494986761579</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>0.53222305829131278</v>
+        <v>0.53168672727200972</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>0.59877007466972609</v>
+        <v>0.5981635241012494</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11436669694956282</v>
+        <v>0.10957270624930487</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.7446808510638298E-2</v>
+        <v>5.5102040816326532E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.31397565212802536</v>
+        <v>-0.31361512741815567</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.25361072236975124</v>
+        <v>0.25331951210716402</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.5522738524093551E-4</v>
+        <v>3.5481949294376608E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-6.000970237303322E-2</v>
+        <v>-5.9940795818047919E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.59259267587355635</v>
+        <v>0.59191222724293091</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.6814019881965464</v>
+        <v>0.68061956366001264</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.17567769087655769</v>
+        <v>0.17573845188277315</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>7.4191952950370841E-4</v>
+        <v>7.8596839837239189E-4</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.5437818848990913E-2</v>
+        <v>2.5484019746558961E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.1655199626301329E-2</v>
+        <v>5.1703757953532964E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-2.2580040813404229E-2</v>
+        <v>-2.2537964049566379E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.65165818095270089</v>
+        <v>0.65090990994815057</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>0.30030330919479309</v>
+        <v>0.29995848384707408</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>0.34970930174976633</v>
+        <v>0.34936447640204732</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>0.37640905759000787</v>
+        <v>0.37597684329135067</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>0.43321716416627298</v>
+        <v>0.43278494986761579</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>0.46708277389096925</v>
+        <v>0.46654644287166619</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>0.53222305829131278</v>
+        <v>0.53168672727200972</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>0.52823594353605463</v>
+        <v>0.52762939296757794</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>0.59877007466972609</v>
+        <v>0.5981635241012494</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10176,11 +10176,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.9099999749865471</v>
+        <v>1.9078068043309053</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.59259267587355635</v>
+        <v>0.59191222724293091</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10586,11 +10586,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-1627560.2520443576</v>
+        <v>-1625691.3947502114</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.31397565212802536</v>
+        <v>-0.31361512741815567</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1314645.6689353602</v>
+        <v>1313136.1179712582</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.25361072236975124</v>
+        <v>0.25331951210716397</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10620,11 +10620,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>1841.3974737762453</v>
+        <v>1839.2830764161681</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>3.5522738524093551E-4</v>
+        <v>3.5481949294376613E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10637,11 +10637,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-311073.18563522119</v>
+        <v>-310715.99370253697</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-6.0009702373033186E-2</v>
+        <v>-5.9940795818047933E-2</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14224,12 +14224,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.7446808510638298E-2</v>
+        <v>5.5102040816326532E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.7446808510638298E-2</v>
+        <v>5.5102040816326532E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -15366,50 +15366,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.3752347566294517E-2</v>
+        <v>5.3690626062159373E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.9805376956324093E-2</v>
+        <v>3.9759670157465114E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.8457328782891077E-2</v>
+        <v>3.8413169889652557E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.5188095222998661E-2</v>
+        <v>-5.5124725111706019E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4167103622205149E-2</v>
+        <v>1.4150836147678153E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.1114543926297785E-2</v>
+        <v>4.1067333867428599E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.15149713576873863</v>
+        <v>0.15132317813683652</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>8.7459290987418004E-2</v>
+        <v>8.7358865252826989E-2</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>6.0188578953497648E-2</v>
+        <v>6.0119467002244083E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>9.1452422398690086E-2</v>
+        <v>9.1347411523392263E-2</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>1.162899108370896E-2</v>
+        <v>1.1615638014424395E-2</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11436669694956282</v>
+        <v>0.10957270624930487</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.4692291396434249E-2</v>
+        <v>8.1142183994826769E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.1824103793385269E-2</v>
+        <v>7.8394224264597051E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.11742147919786949</v>
+        <v>-0.11249943900348168</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.0142773664266275E-2</v>
+        <v>2.8879257444241128E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>8.7477753034676142E-2</v>
+        <v>8.3810885443731831E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.32233433142284817</v>
+        <v>0.30882281252415617</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.18608359784557024</v>
+        <v>0.17828339847515712</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12806080628403757</v>
+        <v>0.12269278980049814</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.19457962212487254</v>
+        <v>0.18642328882324952</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>2.4742534220657364E-2</v>
+        <v>2.3705383702906931E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2043314060107288</v>
+        <v>0.19599134862253578</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20654209367172766</v>
+        <v>0.19811180413410615</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.1142760817528018E-2</v>
+        <v>3.9463464457628918E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15422891608960912</v>
+        <v>0.14793385829003325</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12915242840882066</v>
+        <v>0.12388090071866473</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.36115970660778424</v>
+        <v>0.34641849409318082</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23021935479545241</v>
+        <v>0.22082264643645436</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17035018962489562</v>
+        <v>0.16339712066061418</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23379725385615188</v>
+        <v>0.22425450880079875</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5594886959630199E-2</v>
+        <v>2.4550197695971825E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-6.000970237303322E-2</v>
+        <v>-5.9940795818047919E-2</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1164044342041017</v>
+        <v>1.1151225151062012</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>3532193.6084409724</v>
+        <v>3528137.7427480253</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.6814019881965464</v>
+        <v>0.68061956366001264</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.65281367644381882</v>
+        <v>0.65206407863359461</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.6814019881965464</v>
+        <v>0.68061956366001264</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.6814019881965464</v>
+        <v>0.68061956366001264</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.6814019881965464</v>
+        <v>0.68061956366001264</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.6814019881965464</v>
+        <v>0.68061956366001264</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.6814019881965464</v>
+        <v>0.68061956366001264</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.71620298050598152</v>
+        <v>0.71538059548980371</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.6640014920418299</v>
+        <v>0.66323904774511788</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.68140198819654696</v>
+        <v>0.68061956366001297</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.69880248435126435</v>
+        <v>0.69800007957490851</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.59439950742296144</v>
+        <v>0.59371698408553719</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.74994939729088739</v>
+        <v>0.74908826271869122</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.64810173797971071</v>
+        <v>0.6473575506853535</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.68140198819654696</v>
+        <v>0.68061956366001297</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.71535120796693907</v>
+        <v>0.71452980100445884</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.52139043264792428</v>
+        <v>0.52079174248457805</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18884,23 +18884,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.78267319538534208</v>
+        <v>0.78177448548609796</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.63357329137749463</v>
+        <v>0.63284578647223544</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.68140198819654696</v>
+        <v>0.68061956366001297</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.73108985420282591</v>
+        <v>0.73025037523116443</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.46012407619334789</v>
+        <v>0.45959573554671063</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18915,23 +18915,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.81440536323450974</v>
+        <v>0.81347021665449171</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.62029788096241623</v>
+        <v>0.61958561963880388</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.68140198819654696</v>
+        <v>0.68061956366001297</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.74605807719639661</v>
+        <v>0.74520141085936009</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>0.40871174909859831</v>
+        <v>0.40824244301143703</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18946,23 +18946,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.84517595023976355</v>
+        <v>0.84420547112081334</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.60816743601437229</v>
+        <v>0.60746910355790562</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.68140198819654696</v>
+        <v>0.68061956366001297</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.76029358997349916</v>
+        <v>0.75942057761065129</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>0.36556853755055674</v>
+        <v>0.36514877095386478</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18977,23 +18977,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.87501409521455498</v>
+        <v>0.87400935423967041</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.59708320659797798</v>
+        <v>0.596397601684451</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.68140198819654696</v>
+        <v>0.68061956366001297</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.77383225946780598</v>
+        <v>0.77294370123425649</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>0.32936444394380865</v>
+        <v>0.32898624894751055</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19009,23 +19009,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.90394805397798927</v>
+        <v>0.90291008938522899</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.58695495967204192</v>
+        <v>0.58628098458796096</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.68140198819654696</v>
+        <v>0.68061956366001297</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.78670819688896521</v>
+        <v>0.78580485377139164</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>0.29898338637171218</v>
+        <v>0.29864007663448588</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19040,23 +19040,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.93200522611222836</v>
+        <v>0.93093504467789168</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.57770024453225866</v>
+        <v>0.57703689623872056</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.68140198819654696</v>
+        <v>0.68061956366001297</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.79895384366713063</v>
+        <v>0.79803643940111468</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>0.27348879260491793</v>
+        <v>0.27317475721096868</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19072,23 +19072,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.95921218090906624</v>
+        <v>0.95811075890107966</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.56924372160732872</v>
+        <v>0.56859008357461294</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.68140198819654696</v>
+        <v>0.68061956366001297</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.81060005319042028</v>
+        <v>0.80966927608392769</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>0.25209472790551035</v>
+        <v>0.25180525839403128</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19104,23 +19104,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.98559468253024241</v>
+        <v>0.98446296663265609</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>0.56151654914445559</v>
+        <v>0.56087178389085945</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.68140198819654696</v>
+        <v>0.68061956366001297</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.8216761685412417</v>
+        <v>0.82073267320884125</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>0.23414166661929409</v>
+        <v>0.23387281183436345</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19136,23 +19136,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>1.1059887923879634</v>
+        <v>1.1047188331226756</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>0.53179963027348198</v>
+        <v>0.53118898767710954</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.68140198819654685</v>
+        <v>0.68061956366001286</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.86943563680857061</v>
+        <v>0.86843730133705777</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>0.1794513785340601</v>
+        <v>0.17924532224993991</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19168,23 +19168,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.2092139209160306</v>
+        <v>1.2078254326843672</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>0.51286975934420054</v>
+        <v>0.51228085310279203</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.68140198819654685</v>
+        <v>0.68061956366001286</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.9065954769847322</v>
+        <v>0.9055544724702298</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>0.15669326529852376</v>
+        <v>0.15651334117502116</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19200,23 +19200,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.2977184762653611</v>
+        <v>1.2962283620670876</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>0.50081130823239084</v>
+        <v>0.50023624819070855</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.68140198819654685</v>
+        <v>0.68061956366001286</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.93550814649329339</v>
+        <v>0.9344339428064492</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>0.14722299669737277</v>
+        <v>0.14705394687516291</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19232,23 +19232,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.3736017076962894</v>
+        <v>1.3720244600537179</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>0.49312999631224524</v>
+        <v>0.49256375638999794</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.68140198819654674</v>
+        <v>0.68061956366001275</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.95800400369150396</v>
+        <v>0.95690396898134722</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>0.14328216089742152</v>
+        <v>0.14311763616712178</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.46012407619334789</v>
+        <v>0.45959573554671063</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.73108985420282591</v>
+        <v>0.73025037523116443</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.68140198819654696</v>
+        <v>0.68061956366001297</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.63357329137749463</v>
+        <v>0.63284578647223544</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.78267319538534208</v>
+        <v>0.78177448548609796</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>0.73108985420282591</v>
+        <v>0.73025037523116443</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>0.68140198819654696</v>
+        <v>0.68061956366001297</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>0.63357329137749463</v>
+        <v>0.63284578647223544</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.67938238719303956</v>
+        <v>0.67860228167729875</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>0.46012407619334789</v>
+        <v>0.45959573554671063</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>0.78267319538534208</v>
+        <v>0.78177448548609796</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16697578761628093</v>
+        <v>0.14969730456978969</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>0.6814019881965464</v>
+        <v>0.68061956366001264</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>2.543781884899118E-2</v>
+        <v>2.5484019746559144E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.65165818095270089</v>
+        <v>0.65090990994815057</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.65281367644381882</v>
+        <v>0.65206407863359461</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>-9.2087698930290646E-2</v>
+        <v>-9.2087698930290715E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20229,11 +20229,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.30030330919479309</v>
+        <v>0.29995848384707408</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>0.34970930174976633</v>
+        <v>0.34936447640204732</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46335469733763812</v>
+        <v>0.46326754123335345</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20254,11 +20254,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.37640905759000787</v>
+        <v>0.37597684329135067</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>0.43321716416627298</v>
+        <v>0.43278494986761579</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33520797125123936</v>
+        <v>0.33510775722850794</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20300,11 +20300,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.46708277389096925</v>
+        <v>0.46654644287166619</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>0.53222305829131278</v>
+        <v>0.53168672727200972</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.18327878963596878</v>
+        <v>0.18316387698819614</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20325,11 +20325,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.52823594353605463</v>
+        <v>0.52762939296757794</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>0.59877007466972609</v>
+        <v>0.5981635241012494</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.1159276180119866E-2</v>
+        <v>8.1034848357283029E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>2436.34598185</v>
+        <v>2540.0202789499999</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.16697578761628093</v>
+        <v>0.14969730456978969</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20481,13 +20481,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.1164044342041017</v>
+        <v>1.1151225151062012</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>0.65165818095270089</v>
+        <v>0.65090990994815057</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>0.34970930174976633</v>
+        <v>0.34936447640204732</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>0.43321716416627298</v>
+        <v>0.43278494986761579</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20635,7 +20635,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>0.53222305829131278</v>
+        <v>0.53168672727200972</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>0.59877007466972609</v>
+        <v>0.5981635241012494</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20672,22 +20672,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20877,10 +20877,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20896,22 +20896,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.11436669694956282</v>
+        <v>0.10957270624930487</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.7446808510638298E-2</v>
+        <v>5.5102040816326532E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21046,22 +21046,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21069,13 +21069,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.31397565212802536</v>
+        <v>-0.31361512741815567</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.25361072236975124</v>
+        <v>0.25331951210716402</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.5522738524093551E-4</v>
+        <v>3.5481949294376608E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-6.000970237303322E-2</v>
+        <v>-5.9940795818047919E-2</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21224,33 +21224,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21313,23 +21313,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21347,7 +21347,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>0.59259267587355635</v>
+        <v>0.59191222724293091</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>0.6814019881965464</v>
+        <v>0.68061956366001264</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21373,13 +21373,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>0.65165818095270089</v>
+        <v>0.65090990994815057</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21543,13 +21543,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21562,22 +21562,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21642,11 +21642,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>0.30030330919479309</v>
+        <v>0.29995848384707408</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>0.34970930174976633</v>
+        <v>0.34936447640204732</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21663,11 +21663,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>0.37640905759000787</v>
+        <v>0.37597684329135067</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>0.43321716416627298</v>
+        <v>0.43278494986761579</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21703,11 +21703,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>0.46708277389096925</v>
+        <v>0.46654644287166619</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>0.53222305829131278</v>
+        <v>0.53168672727200972</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21724,11 +21724,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>0.52823594353605463</v>
+        <v>0.52762939296757794</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>0.59877007466972609</v>
+        <v>0.5981635241012494</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21746,13 +21746,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21760,13 +21760,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21803,22 +21803,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21842,12 +21842,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21862,15 +21865,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DF2769-D4E9-447A-8038-F2CB15C6D113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3516F42-C3FF-493B-B73D-285692B4BF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>0.49</v>
+        <v>0.495</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>2540.0202789499999</v>
+        <v>2565.938853225</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.14969730456978969</v>
+        <v>0.14660716436198734</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.1151225151062012</v>
+        <v>1.1182475392341613</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>0.65090990994815057</v>
+        <v>0.6527340226767171</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>0.34936447640204732</v>
+        <v>0.35020508134608719</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>0.43278494986761579</v>
+        <v>0.43383858898880945</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>0.53168672727200972</v>
+        <v>0.53299417902824031</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>0.5981635241012494</v>
+        <v>0.59964215497929929</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10957270624930487</v>
+        <v>0.10876987657240797</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.5102040816326532E-2</v>
+        <v>5.4545454545454543E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.31361512741815567</v>
+        <v>-0.31449400379882109</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.25331951210716402</v>
+        <v>0.25402941579639454</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.5481949294376608E-4</v>
+        <v>3.5581384061543362E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-5.9940795818047919E-2</v>
+        <v>-6.0108774161811061E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.59191222724293091</v>
+        <v>0.59357100461197421</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.68061956366001264</v>
+        <v>0.68252693484980209</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.17573845188277315</v>
+        <v>0.17559057547263676</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>7.8596839837239189E-4</v>
+        <v>6.7876419700028804E-4</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.5484019746558961E-2</v>
+        <v>2.5371578139493471E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.1703757953532964E-2</v>
+        <v>5.1585579065207089E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-2.2537964049566379E-2</v>
+        <v>-2.2640368718737668E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.65090990994815057</v>
+        <v>0.6527340226767171</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>0.29995848384707408</v>
+        <v>0.30079908879111394</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>0.34936447640204732</v>
+        <v>0.35020508134608719</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>0.37597684329135067</v>
+        <v>0.37703048241254433</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>0.43278494986761579</v>
+        <v>0.43383858898880945</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>0.46654644287166619</v>
+        <v>0.46785389462789684</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>0.53168672727200972</v>
+        <v>0.53299417902824031</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>0.52762939296757794</v>
+        <v>0.52910802384562783</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>0.5981635241012494</v>
+        <v>0.59964215497929929</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10176,11 +10176,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.9078068043309053</v>
+        <v>1.913153250317114</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.59191222724293091</v>
+        <v>0.59357100461197421</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10586,11 +10586,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-1625691.3947502114</v>
+        <v>-1630247.2393003751</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.31361512741815567</v>
+        <v>-0.31449400379882109</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1313136.1179712582</v>
+        <v>1316816.0562707421</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.25331951210716397</v>
+        <v>0.25402941579639454</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10620,11 +10620,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>1839.2830764161681</v>
+        <v>1844.4374912128255</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>3.5481949294376613E-4</v>
+        <v>3.5581384061543362E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10637,11 +10637,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-310715.99370253697</v>
+        <v>-311586.74553842022</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-5.9940795818047933E-2</v>
+        <v>-6.010877416181111E-2</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14224,12 +14224,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.5102040816326532E-2</v>
+        <v>5.4545454545454543E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.5102040816326532E-2</v>
+        <v>5.4545454545454543E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -15366,50 +15366,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.3690626062159373E-2</v>
+        <v>5.3841088903341945E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.9759670157465114E-2</v>
+        <v>3.9871092827959739E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.8413169889652557E-2</v>
+        <v>3.8520819122010816E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.5124725111706019E-2</v>
+        <v>-5.5279206878227294E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4150836147678153E-2</v>
+        <v>1.4190492511703852E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.1067333867428599E-2</v>
+        <v>4.1182421140322993E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.15132317813683652</v>
+        <v>0.15174724686147542</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>8.7358865252826989E-2</v>
+        <v>8.7603680112188248E-2</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>6.0119467002244083E-2</v>
+        <v>6.0287946054901558E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>9.1347411523392263E-2</v>
+        <v>9.1603403901960742E-2</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1615638014424395E-2</v>
+        <v>1.1648189728307843E-2</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10957270624930487</v>
+        <v>0.10876987657240797</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.1142183994826769E-2</v>
+        <v>8.054766227870655E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.8394224264597051E-2</v>
+        <v>7.7819836610122858E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.11249943900348168</v>
+        <v>-0.11167516541056019</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.8879257444241128E-2</v>
+        <v>2.8667661639805761E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>8.3810885443731831E-2</v>
+        <v>8.3196810384490893E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.30882281252415617</v>
+        <v>0.30656009466964734</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.17828339847515712</v>
+        <v>0.17697713153977424</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12269278980049814</v>
+        <v>0.12179383041394254</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.18642328882324952</v>
+        <v>0.18505738162012272</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>2.3705383702906931E-2</v>
+        <v>2.3531696420823926E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19599134862253578</v>
+        <v>0.19401163803038896</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19811180413410615</v>
+        <v>0.19611067479941818</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9463464457628918E-2</v>
+        <v>3.9064843604521553E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14793385829003325</v>
+        <v>0.14643957689316422</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12388090071866473</v>
+        <v>0.12262957848918325</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.34641849409318082</v>
+        <v>0.3429193173851689</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22082264643645436</v>
+        <v>0.21859211465426795</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16339712066061418</v>
+        <v>0.16174664469434535</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22425450880079875</v>
+        <v>0.22198931174220479</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4550197695971825E-2</v>
+        <v>2.4302215901063018E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-5.9940795818047919E-2</v>
+        <v>-6.0108774161811061E-2</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1151225151062012</v>
+        <v>1.1182475392341613</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>3528137.7427480253</v>
+        <v>3538025.0111185363</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.68061956366001264</v>
+        <v>0.68252693484980209</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.65206407863359461</v>
+        <v>0.65389142580944459</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.68061956366001264</v>
+        <v>0.68252693484980209</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.68061956366001264</v>
+        <v>0.68252693484980209</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.68061956366001264</v>
+        <v>0.68252693484980209</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.68061956366001264</v>
+        <v>0.68252693484980209</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.68061956366001264</v>
+        <v>0.68252693484980209</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.71538059548980371</v>
+        <v>0.71738538114455952</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.66323904774511788</v>
+        <v>0.66509771170242427</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.68061956366001297</v>
+        <v>0.68252693484980254</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.69800007957490851</v>
+        <v>0.69995615799718125</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.59371698408553719</v>
+        <v>0.59538081911291107</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.74908826271869122</v>
+        <v>0.75118751088492941</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.6473575506853535</v>
+        <v>0.64917170826705761</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.68061956366001297</v>
+        <v>0.68252693484980254</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.71452980100445884</v>
+        <v>0.7165322023890931</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.52079174248457805</v>
+        <v>0.52225121150153331</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18884,23 +18884,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.78177448548609796</v>
+        <v>0.78396533366347065</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.63284578647223544</v>
+        <v>0.63461927622355241</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.68061956366001297</v>
+        <v>0.68252693484980254</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.73025037523116443</v>
+        <v>0.73229683202056217</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.45959573554671063</v>
+        <v>0.46088370861086692</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18915,23 +18915,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.81347021665449171</v>
+        <v>0.81574988908508572</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.61958561963880388</v>
+        <v>0.62132194904160853</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.68061956366001297</v>
+        <v>0.68252693484980254</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.74520141085936009</v>
+        <v>0.74728976649524603</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>0.40824244301143703</v>
+        <v>0.40938650338792992</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18946,23 +18946,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.84420547112081334</v>
+        <v>0.84657127616059158</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.60746910355790562</v>
+        <v>0.60917147758398105</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.68061956366001297</v>
+        <v>0.68252693484980254</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.75942057761065129</v>
+        <v>0.76154878110054014</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>0.36514877095386478</v>
+        <v>0.36617206543861219</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18977,23 +18977,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.87400935423967041</v>
+        <v>0.87645868180956676</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.596397601684451</v>
+        <v>0.59806894888610262</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.68061956366001297</v>
+        <v>0.68252693484980254</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.77294370123425649</v>
+        <v>0.77510980198389634</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>0.32898624894751055</v>
+        <v>0.32990820142519878</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19009,23 +19009,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.90291008938522899</v>
+        <v>0.90544040849948226</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.58628098458796096</v>
+        <v>0.58792398093839071</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.68061956366001297</v>
+        <v>0.68252693484980254</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.78580485377139164</v>
+        <v>0.78800699667016538</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>0.29864007663448588</v>
+        <v>0.29947698686848806</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19040,23 +19040,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.93093504467789168</v>
+        <v>0.93354390104727902</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.57703689623872056</v>
+        <v>0.57865398691623904</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.68061956366001297</v>
+        <v>0.68252693484980254</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.79803643940111468</v>
+        <v>0.80027286014801557</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>0.27317475721096868</v>
+        <v>0.27394030332439517</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19072,23 +19072,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.95811075890107966</v>
+        <v>0.9607957726087788</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.56859008357461294</v>
+        <v>0.57018350286802599</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.68061956366001297</v>
+        <v>0.68252693484980254</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.80966927608392769</v>
+        <v>0.81193829674233431</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>0.25180525839403128</v>
+        <v>0.25251091853214952</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19104,23 +19104,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.98446296663265609</v>
+        <v>0.98722182988053631</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>0.56087178389085945</v>
+        <v>0.5624435733880736</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.68061956366001297</v>
+        <v>0.68252693484980254</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.82073267320884125</v>
+        <v>0.82303269797888956</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>0.23387281183436345</v>
+        <v>0.23452821800718804</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19136,23 +19136,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>1.1047188331226756</v>
+        <v>1.1078147019275408</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>0.53118898767710954</v>
+        <v>0.53267759397866876</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.68061956366001286</v>
+        <v>0.68252693484980242</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.86843730133705777</v>
+        <v>0.87087101376195697</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>0.17924532224993991</v>
+        <v>0.17974764011122146</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19168,23 +19168,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.2078254326843672</v>
+        <v>1.2112102478668882</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>0.51228085310279203</v>
+        <v>0.51371647116677288</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.68061956366001286</v>
+        <v>0.68252693484980242</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.9055544724702298</v>
+        <v>0.90809220221500331</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>0.15651334117502116</v>
+        <v>0.15695195483486016</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19200,23 +19200,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.2962283620670876</v>
+        <v>1.2998609179987739</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>0.50023624819070855</v>
+        <v>0.50163811240212874</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.68061956366001286</v>
+        <v>0.68252693484980242</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.9344339428064492</v>
+        <v>0.93705260450298655</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>0.14705394687516291</v>
+        <v>0.14746605148776942</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19232,23 +19232,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.3720244600537179</v>
+        <v>1.3758694272960941</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>0.49256375638999794</v>
+        <v>0.49394411917742742</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.68061956366001275</v>
+        <v>0.68252693484980231</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.95690396898134722</v>
+        <v>0.9595856007757898</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>0.14311763616712178</v>
+        <v>0.14351870964568594</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.45959573554671063</v>
+        <v>0.46088370861086692</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.73025037523116443</v>
+        <v>0.73229683202056217</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.68061956366001297</v>
+        <v>0.68252693484980254</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.63284578647223544</v>
+        <v>0.63461927622355241</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.78177448548609796</v>
+        <v>0.78396533366347065</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>0.73025037523116443</v>
+        <v>0.73229683202056217</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>0.68061956366001297</v>
+        <v>0.68252693484980254</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>0.63284578647223544</v>
+        <v>0.63461927622355241</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.67860228167729875</v>
+        <v>0.68050399962739194</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>0.45959573554671063</v>
+        <v>0.46088370861086692</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>0.78177448548609796</v>
+        <v>0.78396533366347065</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>0.49</v>
+        <v>0.495</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.14969730456978969</v>
+        <v>0.14660716436198734</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>0.68061956366001264</v>
+        <v>0.68252693484980209</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>2.5484019746559144E-2</v>
+        <v>2.5371578139493596E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.65090990994815057</v>
+        <v>0.6527340226767171</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.65206407863359461</v>
+        <v>0.65389142580944459</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>-9.2087698930290715E-2</v>
+        <v>-9.2087698930290771E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20229,11 +20229,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.29995848384707408</v>
+        <v>0.30079908879111394</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>0.34936447640204732</v>
+        <v>0.35020508134608719</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46326754123335345</v>
+        <v>0.46347965759472132</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20254,11 +20254,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.37597684329135067</v>
+        <v>0.37703048241254433</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>0.43278494986761579</v>
+        <v>0.43383858898880945</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33510775722850794</v>
+        <v>0.33535165332774619</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20300,11 +20300,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.46654644287166619</v>
+        <v>0.46785389462789684</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>0.53168672727200972</v>
+        <v>0.53299417902824031</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.18316387698819614</v>
+        <v>0.18344354589860401</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20325,11 +20325,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.52762939296757794</v>
+        <v>0.52910802384562783</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>0.5981635241012494</v>
+        <v>0.59964215497929929</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.1034848357283029E-2</v>
+        <v>8.1337674846026609E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>0.49</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>2540.0202789499999</v>
+        <v>2565.938853225</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.14969730456978969</v>
+        <v>0.14660716436198734</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20481,13 +20481,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.1151225151062012</v>
+        <v>1.1182475392341613</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>0.65090990994815057</v>
+        <v>0.6527340226767171</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>0.34936447640204732</v>
+        <v>0.35020508134608719</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>0.43278494986761579</v>
+        <v>0.43383858898880945</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20635,7 +20635,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>0.53168672727200972</v>
+        <v>0.53299417902824031</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>0.5981635241012494</v>
+        <v>0.59964215497929929</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20672,22 +20672,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20877,10 +20877,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20896,22 +20896,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10957270624930487</v>
+        <v>0.10876987657240797</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.5102040816326532E-2</v>
+        <v>5.4545454545454543E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21046,22 +21046,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21069,13 +21069,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.31361512741815567</v>
+        <v>-0.31449400379882109</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.25331951210716402</v>
+        <v>0.25402941579639454</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.5481949294376608E-4</v>
+        <v>3.5581384061543362E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-5.9940795818047919E-2</v>
+        <v>-6.0108774161811061E-2</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21224,33 +21224,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21313,23 +21313,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21347,7 +21347,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>0.59191222724293091</v>
+        <v>0.59357100461197421</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>0.68061956366001264</v>
+        <v>0.68252693484980209</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21373,13 +21373,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>0.65090990994815057</v>
+        <v>0.6527340226767171</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21543,13 +21543,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21562,22 +21562,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21642,11 +21642,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>0.29995848384707408</v>
+        <v>0.30079908879111394</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>0.34936447640204732</v>
+        <v>0.35020508134608719</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21663,11 +21663,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>0.37597684329135067</v>
+        <v>0.37703048241254433</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>0.43278494986761579</v>
+        <v>0.43383858898880945</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21703,11 +21703,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>0.46654644287166619</v>
+        <v>0.46785389462789684</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>0.53168672727200972</v>
+        <v>0.53299417902824031</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21724,11 +21724,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>0.52762939296757794</v>
+        <v>0.52910802384562783</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>0.5981635241012494</v>
+        <v>0.59964215497929929</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21746,13 +21746,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21760,13 +21760,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21803,22 +21803,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21842,15 +21842,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21865,12 +21862,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C689D1AB-DDC5-441D-8BD2-6F1456AD3457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBCB927-7286-45ED-90B9-ED38CE7BB138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4991,30 +4991,30 @@
     <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5024,6 +5024,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5033,16 +5042,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5412,7 +5412,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5430,14 +5430,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>2540.0202789499999</v>
+        <v>2488.1831304000002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15336461655127689</v>
+        <v>0.16185767838024809</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5445,13 +5445,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5486,7 +5486,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1192569189071655</v>
+        <v>1.1197439579010011</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>0.65773138014331023</v>
+        <v>0.65801758863055526</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>0.3525080110541946</v>
+        <v>0.35263990436628911</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>0.43672514925832173</v>
+        <v>0.4368904682401239</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>0.53657608693003112</v>
+        <v>0.53678122983783294</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>0.60369302691448079</v>
+        <v>0.60392502831448913</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5629,22 +5629,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5656,13 +5656,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5682,13 +5682,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5739,13 +5739,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5809,13 +5809,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5831,7 +5831,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5853,22 +5853,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10997895561389233</v>
+        <v>0.11231903765917024</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.5102040816326532E-2</v>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6003,13 +6003,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6028,13 +6028,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.31477787999222062</v>
+        <v>-0.31491485399645802</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.25425871397917943</v>
+        <v>0.25436935337406585</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.5613501392052911E-4</v>
+        <v>3.5628998427266134E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-6.0163030999120702E-2</v>
+        <v>-6.0189210638119515E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6203,31 +6203,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6277,22 +6277,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.59410678804589112</v>
+        <v>0.5943653106133131</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.68314301383959986</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6326,13 +6326,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.15001787792370821</v>
+        <v>0.14999608480076893</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>6.2286733462281908E-3</v>
+        <v>6.2119718741325599E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.7458146906633809E-2</v>
+        <v>2.7440748065488789E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.9671008272616939E-2</v>
+        <v>4.9652859975430633E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6463,17 +6463,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-1.4085936072824068E-2</v>
+        <v>-1.410198731324238E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.65773138014331023</v>
+        <v>0.65801758863055526</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6508,22 +6508,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6588,11 +6588,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>0.30310201849922136</v>
+        <v>0.30323391181131587</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>0.3525080110541946</v>
+        <v>0.35263990436628911</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6609,11 +6609,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>0.37991704268205662</v>
+        <v>0.38008236166385878</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>0.43672514925832173</v>
+        <v>0.4368904682401239</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6656,11 +6656,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>0.47143580252968759</v>
+        <v>0.47164094543748947</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>0.53657608693003112</v>
+        <v>0.53678122983783294</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6677,11 +6677,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>0.53315889578080933</v>
+        <v>0.53339089718081767</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>0.60369302691448079</v>
+        <v>0.60392502831448913</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6699,13 +6699,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6742,13 +6742,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6756,22 +6756,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6795,6 +6795,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6811,18 +6823,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10198,11 +10198,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.9148801470322496</v>
+        <v>1.9157133974543574</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.59410678804589112</v>
+        <v>0.5943653106133131</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10608,11 +10608,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-1631718.7725410813</v>
+        <v>-1632428.8067215956</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.31477787999222062</v>
+        <v>-0.31491485399645802</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10625,11 +10625,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1318004.6726670684</v>
+        <v>1318578.1957418895</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.25425871397917943</v>
+        <v>0.25436935337406585</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10642,11 +10642,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>1846.1023620454787</v>
+        <v>1846.905684161911</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>3.5613501392052916E-4</v>
+        <v>3.5628998427266134E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10659,11 +10659,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-311867.99751196738</v>
+        <v>-312003.70529554412</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-6.016303099912066E-2</v>
+        <v>-6.0189210638119509E-2</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14246,12 +14246,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.5102040816326532E-2</v>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.5102040816326532E-2</v>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -15404,50 +15404,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.3889688250807234E-2</v>
+        <v>5.3913138076401718E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.9907082239274312E-2</v>
+        <v>3.9924447604502256E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.8555589716575113E-2</v>
+        <v>3.8572366986659473E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.5329104334564096E-2</v>
+        <v>-5.5353180514795569E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4203301477687395E-2</v>
+        <v>1.4209481972571082E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.1219594214553595E-2</v>
+        <v>4.1237530712736843E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.15188422063610249</v>
+        <v>0.15195031228740122</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>8.7682755067315057E-2</v>
+        <v>8.7720909775213948E-2</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>6.0342364620684111E-2</v>
+        <v>6.0368622295802359E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>9.1686089184630767E-2</v>
+        <v>9.172598592314618E-2</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1658703899389411E-2</v>
+        <v>1.1663777125492074E-2</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15461,50 +15461,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10997895561389233</v>
+        <v>0.11231903765917024</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.1443024978110845E-2</v>
+        <v>8.3175932509379699E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.8684876972602277E-2</v>
+        <v>8.0359097888873909E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.11291653945829408</v>
+        <v>-0.11531912607249077</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.8986329546300805E-2</v>
+        <v>2.9603087442856422E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>8.4121620846027742E-2</v>
+        <v>8.5911522318201761E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.30996779721653572</v>
+        <v>0.31656315059875256</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.17894439809656135</v>
+        <v>0.18275189536502906</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12314768289935533</v>
+        <v>0.1257679631162549</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.18711446772373627</v>
+        <v>0.19109580400655454</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>2.3793273264060024E-2</v>
+        <v>2.4299535678108487E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15518,43 +15518,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19599134862253578</v>
+        <v>0.20007450171883859</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19811180413410615</v>
+        <v>0.2022391333869</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9463464457628918E-2</v>
+        <v>4.0285619967162845E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14793385829003325</v>
+        <v>0.15101581367107558</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12388090071866473</v>
+        <v>0.12646175281697022</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.34641849409318082</v>
+        <v>0.35363554605345537</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22082264643645436</v>
+        <v>0.22542311823721381</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16339712066061418</v>
+        <v>0.16680122734104363</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22425450880079875</v>
+        <v>0.22892647773414868</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4550197695971825E-2</v>
+        <v>2.5061660147971235E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-6.0163030999120702E-2</v>
+        <v>-6.0189210638119515E-2</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1192569189071655</v>
+        <v>1.1197439579010011</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16493,7 +16493,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>3541218.5889298045</v>
+        <v>3542759.532308728</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.68314301383959986</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16638,7 +16638,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.65871857818145207</v>
+        <v>0.6590052162429364</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18826,23 +18826,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.68314301383959986</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.68314301383959986</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.68314301383959986</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.68314301383959986</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.68314301383959986</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18857,23 +18857,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.71287525563314857</v>
+        <v>0.7131854596992292</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.66827689294282533</v>
+        <v>0.66856769025668983</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.68314301383959974</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.69800913473637427</v>
+        <v>0.69831286988504948</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.60881240935572767</v>
+        <v>0.60907733099997063</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18888,23 +18888,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.7417065204026505</v>
+        <v>0.74202927024794163</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.65469293165719467</v>
+        <v>0.65497781797893118</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.68314301383959997</v>
+        <v>0.68344028007086988</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.71214754342141828</v>
+        <v>0.71245743082720636</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.54643707692170918</v>
+        <v>0.54667485625516044</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18919,23 +18919,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.76966411048216754</v>
+        <v>0.76999902593154146</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.64228054745214291</v>
+        <v>0.64256003258759931</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.68314301383959997</v>
+        <v>0.68344028007086988</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.72559386217083111</v>
+        <v>0.72590960067429278</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.49409414061344209</v>
+        <v>0.4943091431825925</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18950,23 +18950,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.79677450086230528</v>
+        <v>0.79712121326109286</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.63093869521815593</v>
+        <v>0.63121324500391118</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.68314301383959974</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.73838196951292978</v>
+        <v>0.73870327269669667</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>0.45016999825685405</v>
+        <v>0.4503658874573605</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18981,23 +18981,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.82306336426122684</v>
+        <v>0.82342151612611247</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.62057504469199565</v>
+        <v>0.62084508478758094</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.68314301383959974</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.75054408558653407</v>
+        <v>0.75087068105366805</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>0.41331057809747962</v>
+        <v>0.41349042810751557</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.8485555954359385</v>
+        <v>0.84892484011643443</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.61110522882659968</v>
+        <v>0.61137114817965221</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.68314301383959986</v>
+        <v>0.68344028007086977</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.76211085332087114</v>
+        <v>0.76244248200855003</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>0.38237959614555689</v>
+        <v>0.38254598669505813</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.87327533475687114</v>
+        <v>0.87365533610704971</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.60245215698689047</v>
+        <v>0.60271431099944683</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.68314301383959997</v>
+        <v>0.68344028007086988</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.77311141564163977</v>
+        <v>0.77344783116843818</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>0.35642352737471283</v>
+        <v>0.35657862327201711</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19075,23 +19075,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.89724599106807823</v>
+        <v>0.8976364231282522</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.59454538738044305</v>
+        <v>0.59480410080214974</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.68314301383959986</v>
+        <v>0.68344028007086977</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.78357348889775458</v>
+        <v>0.78391445694287654</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>0.3346422109236547</v>
+        <v>0.33478782879114338</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19107,23 +19107,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.92049026385470345</v>
+        <v>0.92089081054275168</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.58732055361417868</v>
+        <v>0.58757612318597141</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.68314301383959974</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.79352343269378023</v>
+        <v>0.79386873040667849</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>0.31636418313255704</v>
+        <v>0.31650184740859205</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19139,23 +19139,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.94303016473870349</v>
+        <v>0.94344051955075103</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>0.58071884070887414</v>
+        <v>0.58097153757864772</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.68314301383959974</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.80298631630398631</v>
+        <v>0.80333573174288153</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>0.30102597799317432</v>
+        <v>0.30115696792673075</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19171,23 +19171,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>1.045888920977055</v>
+        <v>1.0463440342572425</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>0.55533017910477567</v>
+        <v>0.55557182822671436</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.68314301383959974</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.84378963725040079</v>
+        <v>0.84415680804826965</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>0.25430130834436659</v>
+        <v>0.25441196627397583</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19203,23 +19203,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.1340793511026532</v>
+        <v>1.1345728400029766</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>0.53915743625348955</v>
+        <v>0.53939204788808037</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.68314301383959974</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.87553716166877082</v>
+        <v>0.87591814724150352</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>0.23485790513713978</v>
+        <v>0.23496010236807047</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19235,23 +19235,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.2096932536051819</v>
+        <v>1.2102196455131817</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>0.52885529369030693</v>
+        <v>0.52908542239960732</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.68314301383959963</v>
+        <v>0.68344028007086954</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.90023871250622967</v>
+        <v>0.90063044683401827</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>0.22676697734417159</v>
+        <v>0.22686565384874813</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19267,23 +19267,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.2745241229355528</v>
+        <v>1.2750787256688196</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>0.52229276175814943</v>
+        <v>0.52252003481483311</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.68314301383959963</v>
+        <v>0.68344028007086954</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.91945805716235962</v>
+        <v>0.91985815469088028</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>0.22340012269155116</v>
+        <v>0.22349733412633477</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.49409414061344209</v>
+        <v>0.4943091431825925</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19358,7 +19358,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.72559386217083111</v>
+        <v>0.72590960067429278</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19386,7 +19386,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.68314301383959997</v>
+        <v>0.68344028007086988</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.64228054745214291</v>
+        <v>0.64256003258759931</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19442,7 +19442,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.76966411048216754</v>
+        <v>0.76999902593154146</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19802,7 +19802,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>0.72559386217083111</v>
+        <v>0.72590960067429278</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19826,7 +19826,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>0.68314301383959997</v>
+        <v>0.68344028007086988</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19849,7 +19849,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>0.64228054745214291</v>
+        <v>0.64256003258759931</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.68141756690898192</v>
+        <v>0.68171408232073682</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19912,7 +19912,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>0.49409414061344209</v>
+        <v>0.4943091431825925</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>0.76966411048216754</v>
+        <v>0.76999902593154146</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15336461655127689</v>
+        <v>0.16185767838024809</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20000,7 +20000,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>0.68314301383959986</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>2.7458146906633844E-2</v>
+        <v>2.7440748065488949E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.65773138014331023</v>
+        <v>0.65801758863055526</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20123,7 +20123,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.65871857818145207</v>
+        <v>0.6590052162429364</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20190,7 +20190,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>-9.1470519448246482E-2</v>
+        <v>-9.1470519448246565E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20268,11 +20268,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.30310201849922136</v>
+        <v>0.30323391181131587</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>0.3525080110541946</v>
+        <v>0.35263990436628911</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20280,7 +20280,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.4640547468217372</v>
+        <v>0.46408741884819249</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20293,11 +20293,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.37991704268205662</v>
+        <v>0.38008236166385878</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>0.43672514925832173</v>
+        <v>0.4368904682401239</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.33601290368240366</v>
+        <v>0.33605047070342586</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20339,11 +20339,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.47143580252968759</v>
+        <v>0.47164094543748947</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>0.53657608693003112</v>
+        <v>0.53678122983783294</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20351,7 +20351,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.18420178338895909</v>
+        <v>0.18424486045279653</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20364,11 +20364,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.53315889578080933</v>
+        <v>0.53339089718081767</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>0.60369302691448079</v>
+        <v>0.60392502831448913</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20376,7 +20376,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>8.2158697091592736E-2</v>
+        <v>8.2205341089197637E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20505,14 +20505,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>2540.0202789499999</v>
+        <v>2488.1831304000002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15336461655127689</v>
+        <v>0.16185767838024809</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20520,13 +20520,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20564,7 +20564,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1192569189071655</v>
+        <v>1.1197439579010011</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>0.65773138014331023</v>
+        <v>0.65801758863055526</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>0.3525080110541946</v>
+        <v>0.35263990436628911</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20658,7 +20658,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>0.43672514925832173</v>
+        <v>0.4368904682401239</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20674,7 +20674,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>0.53657608693003112</v>
+        <v>0.53678122983783294</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20690,7 +20690,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>0.60369302691448079</v>
+        <v>0.60392502831448913</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20711,22 +20711,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20916,10 +20916,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20935,22 +20935,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.10997895561389233</v>
+        <v>0.11231903765917024</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20994,7 +20994,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.5102040816326532E-2</v>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21085,22 +21085,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21108,13 +21108,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21135,7 +21135,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.31477787999222062</v>
+        <v>-0.31491485399645802</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21197,7 +21197,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.25425871397917943</v>
+        <v>0.25436935337406585</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21228,7 +21228,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.5613501392052911E-4</v>
+        <v>3.5628998427266134E-4</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>-6.0163030999120702E-2</v>
+        <v>-6.0189210638119515E-2</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21263,33 +21263,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21352,23 +21352,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>0.59410678804589112</v>
+        <v>0.5943653106133131</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>0.68314301383959986</v>
+        <v>0.68344028007086965</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21412,13 +21412,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>0.65773138014331023</v>
+        <v>0.65801758863055526</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21582,13 +21582,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21601,22 +21601,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21681,11 +21681,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>0.30310201849922136</v>
+        <v>0.30323391181131587</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>0.3525080110541946</v>
+        <v>0.35263990436628911</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21702,11 +21702,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>0.37991704268205662</v>
+        <v>0.38008236166385878</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>0.43672514925832173</v>
+        <v>0.4368904682401239</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21742,11 +21742,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>0.47143580252968759</v>
+        <v>0.47164094543748947</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>0.53657608693003112</v>
+        <v>0.53678122983783294</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21763,11 +21763,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>0.53315889578080933</v>
+        <v>0.53339089718081767</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>0.60369302691448079</v>
+        <v>0.60392502831448913</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21785,13 +21785,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21799,13 +21799,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21842,22 +21842,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21881,12 +21881,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21901,15 +21904,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3813.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3813.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBCB927-7286-45ED-90B9-ED38CE7BB138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C396C4FE-B864-48EB-AA67-A420171E5C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3249,10 +3249,10 @@
     <t>FCFE Margin</t>
   </si>
   <si>
-    <t>Long-term Projection</t>
-  </si>
-  <si>
     <t>FCFE and TV</t>
+  </si>
+  <si>
+    <t>Sales/Total Assets g Projection</t>
   </si>
   <si>
     <t>寶勝國際</t>
@@ -4985,12 +4985,10 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5412,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>0.48</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5430,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>2488.1831304000002</v>
+        <v>2514.1017046749998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16185767838024809</v>
+        <v>0.15788816581377163</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5486,7 +5484,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1197439579010011</v>
+        <v>1.1204719901561737</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5510,7 +5508,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>0.65801758863055526</v>
+        <v>0.65844541681896729</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5560,7 +5558,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>0.35263990436628911</v>
+        <v>0.3528370602134836</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5575,7 +5573,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>0.4368904682401239</v>
+        <v>0.43713758921537993</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5590,7 +5588,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>0.53678122983783294</v>
+        <v>0.537087880138302</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5605,7 +5603,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>0.60392502831448913</v>
+        <v>0.60427182704023641</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5902,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11231903765917024</v>
+        <v>0.11123338388096082</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5912,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6250000000000001E-2</v>
+        <v>5.5670103092783509E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6057,7 +6055,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.31491485399645802</v>
+        <v>-0.31511960452868876</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6128,7 +6126,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.25436935337406585</v>
+        <v>0.25453473858795966</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6165,7 +6163,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.5628998427266134E-4</v>
+        <v>3.5652163598099622E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6182,7 +6180,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-6.0189210638119515E-2</v>
+        <v>-6.0228344304748153E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6305,7 +6303,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.5943653106133131</v>
+        <v>0.59475175352682819</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6318,7 +6316,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961048</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6375,7 +6373,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>0.14999608480076893</v>
+        <v>0.14996354357783223</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6397,7 +6395,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>6.2119718741325599E-3</v>
+        <v>6.1870333466105239E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6419,7 +6417,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.7440748065488789E-2</v>
+        <v>2.7414768245059451E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6441,7 +6439,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.9652859975430633E-2</v>
+        <v>4.9625761088279104E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6463,7 +6461,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>-1.410198731324238E-2</v>
+        <v>-1.4125954931230545E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6481,7 +6479,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>0.65801758863055526</v>
+        <v>0.65844541681896729</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6588,11 +6586,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>0.30323391181131587</v>
+        <v>0.30343106765851036</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>0.35263990436628911</v>
+        <v>0.3528370602134836</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6609,11 +6607,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>0.38008236166385878</v>
+        <v>0.38032948263911481</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>0.4368904682401239</v>
+        <v>0.43713758921537993</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6656,11 +6654,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>0.47164094543748947</v>
+        <v>0.47194759573795853</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>0.53678122983783294</v>
+        <v>0.537087880138302</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6677,11 +6675,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>0.53339089718081767</v>
+        <v>0.53373769590656495</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>0.60392502831448913</v>
+        <v>0.60427182704023641</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -10198,11 +10196,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.9157133974543574</v>
+        <v>1.9169589510786229</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.5943653106133131</v>
+        <v>0.59475175352682819</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10608,11 +10606,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-1632428.8067215956</v>
+        <v>-1633490.1750970893</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.31491485399645802</v>
+        <v>-0.31511960452868876</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10625,11 +10623,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1318578.1957418895</v>
+        <v>1319435.5055319481</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.25436935337406585</v>
+        <v>0.25453473858795966</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10642,11 +10640,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>1846.905684161911</v>
+        <v>1848.1065005635928</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>3.5628998427266134E-4</v>
+        <v>3.5652163598099627E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10659,11 +10657,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-312003.70529554412</v>
+        <v>-312206.56306457758</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-6.0189210638119509E-2</v>
+        <v>-6.0228344304748098E-2</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10806,7 +10804,7 @@
       <c r="B4" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="459">
+      <c r="C4" s="458">
         <f>C100*C117</f>
         <v>18453923</v>
       </c>
@@ -14246,12 +14244,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6250000000000001E-2</v>
+        <v>5.5670103092783509E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.6250000000000001E-2</v>
+        <v>5.5670103092783509E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14939,7 +14937,9 @@
         <v>303</v>
       </c>
       <c r="C112" s="151"/>
-      <c r="E112" s="237"/>
+      <c r="E112" s="451" t="s">
+        <v>553</v>
+      </c>
       <c r="G112" s="251">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>2.3795513255742011</v>
@@ -14991,7 +14991,10 @@
         <v>304</v>
       </c>
       <c r="C113" s="151"/>
-      <c r="E113" s="237"/>
+      <c r="E113" s="459">
+        <f>(Normalized_FCF!E117/Normalized_FCF!C117)^(1/DCF!C15)-1</f>
+        <v>0</v>
+      </c>
       <c r="G113" s="251">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>6.4092597069164698</v>
@@ -15050,8 +15053,9 @@
         <v>327</v>
       </c>
       <c r="D115" s="52"/>
-      <c r="E115" s="451" t="s">
-        <v>552</v>
+      <c r="E115" s="451" t="str">
+        <f>DCF!F15&amp;"yrs Projection"</f>
+        <v>4yrs Projection</v>
       </c>
       <c r="F115" s="52"/>
       <c r="G115" s="22" t="str">
@@ -15165,7 +15169,7 @@
         <f>G117</f>
         <v>1.4656521003611329</v>
       </c>
-      <c r="E117" s="458">
+      <c r="E117" s="452">
         <f>C117</f>
         <v>1.4656521003611329</v>
       </c>
@@ -15404,50 +15408,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.3913138076401718E-2</v>
+        <v>5.3948191182265993E-2</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.9924447604502256E-2</v>
+        <v>3.995040557946692E-2</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>3.8572366986659473E-2</v>
+        <v>3.859744586931519E-2</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-5.5353180514795569E-2</v>
+        <v>-5.5389169903759729E-2</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.4209481972571082E-2</v>
+        <v>1.421872065712243E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.1237530712736843E-2</v>
+        <v>4.1264342424709666E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.15195031228740122</v>
+        <v>0.15204910695179588</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>8.7720909775213948E-2</v>
+        <v>8.7777943931387617E-2</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>6.0368622295802359E-2</v>
+        <v>6.0407872611842522E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>9.172598592314618E-2</v>
+        <v>9.1785624089459436E-2</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1663777125492074E-2</v>
+        <v>1.1671360650193936E-2</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15461,50 +15465,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11231903765917024</v>
+        <v>0.11123338388096082</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.3175932509379699E-2</v>
+        <v>8.237197026694211E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.0359097888873909E-2</v>
+        <v>7.9582362617144728E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-0.11531912607249077</v>
+        <v>-0.11420447402837058</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.9603087442856422E-2</v>
+        <v>2.9316949808499856E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>8.5911522318201761E-2</v>
+        <v>8.5081118401463235E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.31656315059875256</v>
+        <v>0.31350331330267195</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.18275189536502906</v>
+        <v>0.18098545140492292</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.1257679631162549</v>
+        <v>0.12455231466359283</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.19109580400655454</v>
+        <v>0.18924870946280298</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>2.4299535678108487E-2</v>
+        <v>2.4064661134420486E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15518,43 +15522,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20007450171883859</v>
+        <v>0.19801187798977843</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2022391333869</v>
+        <v>0.20015419386744746</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0285619967162845E-2</v>
+        <v>3.9870304297398289E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15101581367107558</v>
+        <v>0.14945894961261091</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12646175281697022</v>
+        <v>0.12515802340648602</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.35363554605345537</v>
+        <v>0.34998981877455382</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22542311823721381</v>
+        <v>0.22309916856466525</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16680122734104363</v>
+        <v>0.16508162705917723</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22892647773414868</v>
+        <v>0.22656641095338431</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5061660147971235E-2</v>
+        <v>2.4803292517579782E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16443,7 +16447,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-6.0189210638119515E-2</v>
+        <v>-6.0228344304748153E-2</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16468,7 +16472,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1197439579010011</v>
+        <v>1.1204719901561737</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16493,7 +16497,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>3542759.532308728</v>
+        <v>3545062.9546166956</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16515,7 +16519,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961048</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16638,7 +16642,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.6590052162429364</v>
+        <v>0.6594336865645366</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16672,7 +16676,7 @@
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="H20" s="121" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I20" s="121" t="s">
         <v>529</v>
@@ -18826,23 +18830,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961048</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961048</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961048</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961048</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961048</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18857,23 +18861,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>0.7131854596992292</v>
+        <v>0.71364915679258478</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>0.66856769025668983</v>
+        <v>0.66900237788312322</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961037</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>0.69831286988504948</v>
+        <v>0.69876689715609763</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>0.60907733099997063</v>
+        <v>0.60947333933717451</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18888,23 +18892,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>0.74202927024794163</v>
+        <v>0.74251172093607509</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>0.65497781797893118</v>
+        <v>0.65540366977705566</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>0.68344028007086988</v>
+        <v>0.68388463751961059</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>0.71245743082720636</v>
+        <v>0.71292065457261677</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>0.54667485625516044</v>
+        <v>0.54703029191135422</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18919,23 +18923,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>0.76999902593154146</v>
+        <v>0.77049966192370212</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>0.64256003258759931</v>
+        <v>0.64297781062186121</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>0.68344028007086988</v>
+        <v>0.68388463751961059</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>0.72590960067429278</v>
+        <v>0.72638157071699883</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>0.4943091431825925</v>
+        <v>0.49463053183374295</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18950,23 +18954,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>0.79712121326109286</v>
+        <v>0.79763948348746161</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>0.63121324500391118</v>
+        <v>0.63162364561291862</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961037</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>0.73870327269669667</v>
+        <v>0.73918356089627124</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>0.4503658874573605</v>
+        <v>0.4506587051951878</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18981,23 +18985,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>0.82342151612611247</v>
+        <v>0.82395688621595575</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>0.62084508478758094</v>
+        <v>0.62124874425276622</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961037</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>0.75087068105366805</v>
+        <v>0.75135888022760711</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>0.41349042810751557</v>
+        <v>0.41375927025374304</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -19012,23 +19016,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>0.84892484011643443</v>
+        <v>0.84947679189207115</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>0.61137114817965221</v>
+        <v>0.61176864790502783</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>0.68344028007086977</v>
+        <v>0.68388463751961048</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>0.76244248200855003</v>
+        <v>0.76293820490636011</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>0.38254598669505813</v>
+        <v>0.38279470946371935</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19044,23 +19048,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>0.87365533610704971</v>
+        <v>0.87422336709315285</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>0.60271431099944683</v>
+        <v>0.60310618224462353</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>0.68344028007086988</v>
+        <v>0.68388463751961059</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>0.77344783116843818</v>
+        <v>0.77395070949594391</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>0.35657862327201711</v>
+        <v>0.3568104626469164</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19075,23 +19079,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>0.8976364231282522</v>
+        <v>0.89822004607601968</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>0.59480410080214974</v>
+        <v>0.5951908290071446</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>0.68344028007086977</v>
+        <v>0.68388463751961048</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>0.78391445694287654</v>
+        <v>0.78442414043428854</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>0.33478782879114338</v>
+        <v>0.33500550028316556</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19107,23 +19111,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>0.92089081054275168</v>
+        <v>0.92148955296849688</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>0.58757612318597141</v>
+        <v>0.58795815192301459</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961037</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>0.79386873040667849</v>
+        <v>0.79438488594208534</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>0.31650184740859205</v>
+        <v>0.31670762976812994</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19139,23 +19143,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>0.94344051955075103</v>
+        <v>0.94405392328847448</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>0.58097153757864772</v>
+        <v>0.58134927216315702</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961037</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>0.80333573174288153</v>
+        <v>0.80385804250894077</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>0.30115696792673075</v>
+        <v>0.30135277339187622</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19171,23 +19175,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>1.0463440342572425</v>
+        <v>1.0470243435382811</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>0.55557182822671436</v>
+        <v>0.55593304849333003</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961037</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>0.84415680804826965</v>
+        <v>0.84470565975704304</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>0.25441196627397583</v>
+        <v>0.25457737919381562</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19203,23 +19207,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>1.1345728400029766</v>
+        <v>1.1353105136626884</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>0.53939204788808037</v>
+        <v>0.53974274842660552</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961037</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>0.87591814724150352</v>
+        <v>0.8764876494563475</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>0.23496010236807047</v>
+        <v>0.23511286812491658</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19235,23 +19239,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>1.2102196455131817</v>
+        <v>1.2110065030189179</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>0.52908542239960732</v>
+        <v>0.52942942180280173</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>0.68344028007086954</v>
+        <v>0.68388463751961026</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>0.90063044683401827</v>
+        <v>0.90121601642844129</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>0.22686565384874813</v>
+        <v>0.22701315677781267</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19267,23 +19271,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>1.2750787256688196</v>
+        <v>1.2759077530849723</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>0.52252003481483311</v>
+        <v>0.52285976555116342</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>0.68344028007086954</v>
+        <v>0.68388463751961026</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>0.91985815469088028</v>
+        <v>0.92045622570709174</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>0.22349733412633477</v>
+        <v>0.2236426470499196</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19330,7 +19334,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>0.4943091431825925</v>
+        <v>0.49463053183374295</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19358,7 +19362,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>0.72590960067429278</v>
+        <v>0.72638157071699883</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19386,7 +19390,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>0.68344028007086988</v>
+        <v>0.68388463751961059</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19414,7 +19418,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>0.64256003258759931</v>
+        <v>0.64297781062186121</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19442,7 +19446,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>0.76999902593154146</v>
+        <v>0.77049966192370212</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19802,7 +19806,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>0.72590960067429278</v>
+        <v>0.72638157071699883</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19826,7 +19830,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>0.68344028007086988</v>
+        <v>0.68388463751961059</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19849,7 +19853,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>0.64256003258759931</v>
+        <v>0.64297781062186121</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19865,7 +19869,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>0.68171408232073682</v>
+        <v>0.68215731743465091</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19912,7 +19916,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>0.4943091431825925</v>
+        <v>0.49463053183374295</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19935,7 +19939,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>0.76999902593154146</v>
+        <v>0.77049966192370212</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19980,7 +19984,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>0.48</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19991,7 +19995,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16185767838024809</v>
+        <v>0.15788816581377163</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20000,7 +20004,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961048</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20011,7 +20015,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>2.7440748065488949E-2</v>
+        <v>2.7414768245059517E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20020,7 +20024,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>0.65801758863055526</v>
+        <v>0.65844541681896729</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20123,7 +20127,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>0.6590052162429364</v>
+        <v>0.6594336865645366</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20190,7 +20194,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>-9.1470519448246565E-2</v>
+        <v>-9.1470519448246468E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20268,11 +20272,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>0.30323391181131587</v>
+        <v>0.30343106765851036</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>0.35263990436628911</v>
+        <v>0.3528370602134836</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20280,7 +20284,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.46408741884819249</v>
+        <v>0.46413620445855042</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20293,11 +20297,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>0.38008236166385878</v>
+        <v>0.38032948263911481</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>0.4368904682401239</v>
+        <v>0.43713758921537993</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20305,7 +20309,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.33605047070342586</v>
+        <v>0.33610656548078555</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20339,11 +20343,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>0.47164094543748947</v>
+        <v>0.47194759573795853</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>0.53678122983783294</v>
+        <v>0.537087880138302</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20351,7 +20355,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.18424486045279653</v>
+        <v>0.18430918278231601</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20364,11 +20368,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>0.53339089718081767</v>
+        <v>0.53373769590656495</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>0.60392502831448913</v>
+        <v>0.60427182704023641</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20376,7 +20380,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>8.2205341089197637E-2</v>
+        <v>8.2274989535883303E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20487,7 +20491,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>0.48</v>
+        <v>0.48499999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20505,14 +20509,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>2488.1831304000002</v>
+        <v>2514.1017046749998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16185767838024809</v>
+        <v>0.15788816581377163</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20564,7 +20568,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1197439579010011</v>
+        <v>1.1204719901561737</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20590,7 +20594,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>0.65801758863055526</v>
+        <v>0.65844541681896729</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20642,7 +20646,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>0.35263990436628911</v>
+        <v>0.3528370602134836</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20658,7 +20662,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>0.4368904682401239</v>
+        <v>0.43713758921537993</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20674,7 +20678,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>0.53678122983783294</v>
+        <v>0.537087880138302</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20690,7 +20694,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>0.60392502831448913</v>
+        <v>0.60427182704023641</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20984,7 +20988,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11231903765917024</v>
+        <v>0.11123338388096082</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20994,7 +20998,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.6250000000000001E-2</v>
+        <v>5.5670103092783509E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21135,7 +21139,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.31491485399645802</v>
+        <v>-0.31511960452868876</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21197,7 +21201,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.25436935337406585</v>
+        <v>0.25453473858795966</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21228,7 +21232,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.5628998427266134E-4</v>
+        <v>3.5652163598099622E-4</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21241,7 +21245,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>-6.0189210638119515E-2</v>
+        <v>-6.0228344304748153E-2</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21386,7 +21390,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>0.5943653106133131</v>
+        <v>0.59475175352682819</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21400,7 +21404,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>0.68344028007086965</v>
+        <v>0.68388463751961048</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21574,7 +21578,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>0.65801758863055526</v>
+        <v>0.65844541681896729</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21681,11 +21685,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>0.30323391181131587</v>
+        <v>0.30343106765851036</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>0.35263990436628911</v>
+        <v>0.3528370602134836</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21702,11 +21706,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>0.38008236166385878</v>
+        <v>0.38032948263911481</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>0.4368904682401239</v>
+        <v>0.43713758921537993</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21742,11 +21746,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>0.47164094543748947</v>
+        <v>0.47194759573795853</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>0.53678122983783294</v>
+        <v>0.537087880138302</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21763,11 +21767,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>0.53339089718081767</v>
+        <v>0.53373769590656495</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>0.60392502831448913</v>
+        <v>0.60427182704023641</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
